--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/00.고객심사/2026년09월08일_베트남_HILTI_Sagar,Rex/포장지도서/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C41D2699-AC96-4610-A53E-7C5346630DCA}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D630C33-327E-4B7A-B63B-F7531002ECF3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>바코드스캔</t>
   </si>
@@ -219,6 +219,14 @@
   </si>
   <si>
     <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQDE0JsK9kIqT6vANYh_Kw7mAUOOPi1X4KrzMAjpsK4H2hQ?e=oFcVjQ</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAnCVwYSltSTYO4yqPBtvrQAZlDcXZl5QcNqdhOE5vnS4M?e=WMJx8A</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>HILTI 125D-1.2T-10.5W-22.23H-Layered flange</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1219,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
@@ -1584,6 +1592,17 @@
       </c>
       <c r="C40" s="2" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" s="1">
+        <v>2259032</v>
+      </c>
+      <c r="B41" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1602,8 +1621,9 @@
     <hyperlink ref="C27" r:id="rId11" xr:uid="{03635319-FBCC-46EC-840B-8E887FA6C662}"/>
     <hyperlink ref="C12" r:id="rId12" xr:uid="{89FA1357-6F15-4D8E-AC48-C42955AC5363}"/>
     <hyperlink ref="C40" r:id="rId13" xr:uid="{0BF5B71A-BE82-463E-88C2-CC8C1C665DC8}"/>
+    <hyperlink ref="C41" r:id="rId14" xr:uid="{6A4DBA51-F261-4342-962F-FE2962A14FA5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D630C33-327E-4B7A-B63B-F7531002ECF3}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61111E7B-81B7-4005-82B7-9CEA69C3DFF7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
+    <workbookView xWindow="60" yWindow="744" windowWidth="22980" windowHeight="12216" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>바코드스캔</t>
   </si>
@@ -227,6 +227,10 @@
   </si>
   <si>
     <t>HILTI 125D-1.2T-10.5W-22.23H-Layered flange</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAXvQ5y5qzQRbiyxZzZJu1TAV-7gScR7gYaOClQwKa4ioA?e=k9sSsF</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1227,7 +1231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
@@ -1603,6 +1607,14 @@
       </c>
       <c r="C41" s="2" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" s="1">
+        <v>111111</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1622,8 +1634,9 @@
     <hyperlink ref="C12" r:id="rId12" xr:uid="{89FA1357-6F15-4D8E-AC48-C42955AC5363}"/>
     <hyperlink ref="C40" r:id="rId13" xr:uid="{0BF5B71A-BE82-463E-88C2-CC8C1C665DC8}"/>
     <hyperlink ref="C41" r:id="rId14" xr:uid="{6A4DBA51-F261-4342-962F-FE2962A14FA5}"/>
+    <hyperlink ref="C42" r:id="rId15" xr:uid="{3242C965-7F7C-45E4-8089-9D3F35658595}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId15"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61111E7B-81B7-4005-82B7-9CEA69C3DFF7}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72911F35-31C5-40C4-9DE2-C4F733DCDC19}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="744" windowWidth="22980" windowHeight="12216" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>바코드스캔</t>
   </si>
@@ -1231,7 +1231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
@@ -1615,6 +1615,22 @@
       </c>
       <c r="C42" s="2" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A43" s="1">
+        <v>222222</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A44" s="1">
+        <v>2488429</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1635,8 +1651,10 @@
     <hyperlink ref="C40" r:id="rId13" xr:uid="{0BF5B71A-BE82-463E-88C2-CC8C1C665DC8}"/>
     <hyperlink ref="C41" r:id="rId14" xr:uid="{6A4DBA51-F261-4342-962F-FE2962A14FA5}"/>
     <hyperlink ref="C42" r:id="rId15" xr:uid="{3242C965-7F7C-45E4-8089-9D3F35658595}"/>
+    <hyperlink ref="C43" r:id="rId16" xr:uid="{F3743072-623A-485C-8553-58DD85DB2A22}"/>
+    <hyperlink ref="C44" r:id="rId17" xr:uid="{E138173B-E4DB-4670-8954-EF8AF33888D1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia1-my.sharepoint.com/personal/icdide_ehwadia1_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72911F35-31C5-40C4-9DE2-C4F733DCDC19}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2D135F8-6526-4C99-BC7C-6FBAC28C618F}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="744" windowWidth="22980" windowHeight="12216" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
   <si>
     <t>바코드스캔</t>
   </si>
@@ -231,6 +231,10 @@
   </si>
   <si>
     <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAXvQ5y5qzQRbiyxZzZJu1TAV-7gScR7gYaOClQwKa4ioA?e=k9sSsF</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.5.pdf</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1231,15 +1235,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:C45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.69921875" customWidth="1"/>
-    <col min="3" max="3" width="105.3984375" customWidth="1"/>
+    <col min="2" max="2" width="19.75" customWidth="1"/>
+    <col min="3" max="3" width="105.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1250,7 +1254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>4000196031150</v>
       </c>
@@ -1261,7 +1265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>8801230160609</v>
       </c>
@@ -1272,7 +1276,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
@@ -1283,7 +1287,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>9702040100</v>
       </c>
@@ -1294,7 +1298,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1305,7 +1309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>26083025061</v>
       </c>
@@ -1316,7 +1320,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>2434817</v>
       </c>
@@ -1327,7 +1331,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>2314163</v>
       </c>
@@ -1335,7 +1339,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>2314164</v>
       </c>
@@ -1343,7 +1347,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>2314165</v>
       </c>
@@ -1351,7 +1355,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>2314166</v>
       </c>
@@ -1362,7 +1366,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>2314167</v>
       </c>
@@ -1370,7 +1374,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>2314168</v>
       </c>
@@ -1378,7 +1382,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>2314169</v>
       </c>
@@ -1386,7 +1390,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>2384228</v>
       </c>
@@ -1394,7 +1398,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>2384229</v>
       </c>
@@ -1402,7 +1406,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>2384232</v>
       </c>
@@ -1410,7 +1414,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>2384233</v>
       </c>
@@ -1418,7 +1422,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>2384234</v>
       </c>
@@ -1429,7 +1433,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>2384235</v>
       </c>
@@ -1437,7 +1441,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>2384236</v>
       </c>
@@ -1445,7 +1449,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>2384237</v>
       </c>
@@ -1453,7 +1457,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>2384238</v>
       </c>
@@ -1461,7 +1465,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>2390326</v>
       </c>
@@ -1469,7 +1473,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>2390327</v>
       </c>
@@ -1477,7 +1481,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>2390328</v>
       </c>
@@ -1488,7 +1492,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>2390329</v>
       </c>
@@ -1496,7 +1500,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>2384224</v>
       </c>
@@ -1504,7 +1508,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>2384225</v>
       </c>
@@ -1512,7 +1516,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>2384226</v>
       </c>
@@ -1520,7 +1524,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>2390320</v>
       </c>
@@ -1528,7 +1532,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>2390321</v>
       </c>
@@ -1536,7 +1540,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>2390322</v>
       </c>
@@ -1544,7 +1548,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>2299889</v>
       </c>
@@ -1552,7 +1556,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>2299890</v>
       </c>
@@ -1560,7 +1564,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>2299891</v>
       </c>
@@ -1568,7 +1572,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>2453626</v>
       </c>
@@ -1579,7 +1583,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>2453625</v>
       </c>
@@ -1590,7 +1594,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>2254450</v>
       </c>
@@ -1598,7 +1602,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>2259032</v>
       </c>
@@ -1609,7 +1613,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>111111</v>
       </c>
@@ -1617,7 +1621,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>222222</v>
       </c>
@@ -1625,12 +1629,20 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>2488429</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>333333</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1653,8 +1665,9 @@
     <hyperlink ref="C42" r:id="rId15" xr:uid="{3242C965-7F7C-45E4-8089-9D3F35658595}"/>
     <hyperlink ref="C43" r:id="rId16" xr:uid="{F3743072-623A-485C-8553-58DD85DB2A22}"/>
     <hyperlink ref="C44" r:id="rId17" xr:uid="{E138173B-E4DB-4670-8954-EF8AF33888D1}"/>
+    <hyperlink ref="C45" r:id="rId18" xr:uid="{B9530D14-BC89-4B26-B5C1-C78985E96158}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia1-my.sharepoint.com/personal/icdide_ehwadia1_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2D135F8-6526-4C99-BC7C-6FBAC28C618F}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{300D0682-E2E9-4930-96AF-FE489F5E6E6B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>바코드스캔</t>
   </si>
@@ -42,196 +42,6 @@
   </si>
   <si>
     <t>원드라이브 경로</t>
-  </si>
-  <si>
-    <t>HILTI빗각외경드레싱</t>
-  </si>
-  <si>
-    <t>실크스크린</t>
-  </si>
-  <si>
-    <t>이화 별색 페인트</t>
-  </si>
-  <si>
-    <t>PCD 용접 외관 기준</t>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAXkKmG-_hjRLUa22MKGBDAAamtdb-bmfELqF9Orm9Lmpg?e=NVECRj</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQDamsLEktjJSrYkJqHmsLB4Ab-WIrLkJofa4Dh-19l0axM?e=Zeu04D</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQDyPnOd3EVqT68K7o7gvGNqARrYcpvjmsACEIuzp0Pkucc?e=0IBKW0</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAf2d-0inNzSLBpZ6iuHzu9AVbFeZj96w8VHnVJ5EXimGM?e=UeZp2K</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>20240119409100X</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>P100035</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQDjRwHRmzQXRaNbWwiQM3IQAReLvKoQzNdxBBxKqCDeUiM?e=7vF83m</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>클리어런스 측정법</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQCbJBfYrTWWS73HC4n8QLlqAVlx0Mzy_BkTlZly81o5jWo?e=l85bkH</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>BOSCH DIABLO TU-3"</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>HILTI BS-14</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAIYCuHYaLORL3onZApx-wBAdrndDC57oMo2cJSdIrP2ks?e=de4bt6</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>V28004020_Cutting disc 100/20/16mm SPX metal</t>
-  </si>
-  <si>
-    <t>V28405057_Cutting disc 115/22mm SPX metal</t>
-  </si>
-  <si>
-    <t>V28005030_Cutting disc 125/22mm SPX metal</t>
-  </si>
-  <si>
-    <t>V28009012_Cutting disc 230/22mm SPX metal</t>
-  </si>
-  <si>
-    <t>V28012052_Cutting disc 300/25mm SPX metal</t>
-  </si>
-  <si>
-    <t>V28014025_Cutting disc 350/25mm SPX metal</t>
-  </si>
-  <si>
-    <t>V28016037_Cutting disc 400/25mm SPX metal</t>
-  </si>
-  <si>
-    <t>V28405057_Dia blade 115/22 SPX metal/PVC</t>
-  </si>
-  <si>
-    <t>V28005030_Dia blade 125/22 SPX metal/PVC</t>
-  </si>
-  <si>
-    <t>V28009012_Dia blade 230/22 SPX metal/PVC</t>
-  </si>
-  <si>
-    <t>V28012104_Dia blade 300/25 SPX metal/PVC</t>
-  </si>
-  <si>
-    <t>V28014173_Dia blade 350/25 SPX metal/PVC</t>
-  </si>
-  <si>
-    <t>V28016077_Dia blade 400/25 SPX metal/PVC</t>
-  </si>
-  <si>
-    <t>V28005110_Dia blade 125/22 SPX chamfer</t>
-  </si>
-  <si>
-    <t>V28009105_Dia blade 230/22 SPX chamfer</t>
-  </si>
-  <si>
-    <t>V28012107_Dia blade 300/25 SPX chamfer</t>
-  </si>
-  <si>
-    <t>V28012105_Dia blade 300/20 SPX metal/PVC</t>
-  </si>
-  <si>
-    <t>V28014174_Dia blade 350/20 SPX metal/PVC</t>
-  </si>
-  <si>
-    <t>V28016078_Dia blade 400/20 SPX metal/PVC</t>
-  </si>
-  <si>
-    <t>V28012106_Dia blade 300/20 SPX chamfer</t>
-  </si>
-  <si>
-    <t>V10012215_Dia blade 300/25 SPX granite</t>
-  </si>
-  <si>
-    <t>V10014366_Dia blade 350/25 SPX granite</t>
-  </si>
-  <si>
-    <t>V10016167_Dia blade 400/25 SPX granite</t>
-  </si>
-  <si>
-    <t>V10012214_Dia blade 300/20 SPX granite</t>
-  </si>
-  <si>
-    <t>V10014365_Dia blade 350/20 SPX granite</t>
-  </si>
-  <si>
-    <t>V10016166_Dia blade 400/20 SPX granite</t>
-  </si>
-  <si>
-    <t>V50105029_Diamond wire DS-W 10.5-100m SI SP-M/H</t>
-  </si>
-  <si>
-    <t>V50105030_Diamond wire DS-W 10.5-50m SI SP-M/H</t>
-  </si>
-  <si>
-    <t>V50105037_Diamond wire DS-W 10.5-25m SI SP-M/H</t>
-  </si>
-  <si>
-    <t>P118855HILTI(LI)BS-14(2)_2384234.pdf</t>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQB8fW-ZPPtXQIRteVPgSh3iAUG67d1mrWxlvaeh4HXxnu4?e=8IqRRb</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQDQMk7VJZc4Tpr3L1cxPSfyAQIrH1NIEGy8wjmOjnzSWiE?e=EyDctk</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>DS-W 10.5 VB CL 27.75</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>DS-W 10.5 VB-SPX-H C&amp;S</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQBYeb7Z9whsTJPfUmsnjFt0AQlrU9M_IKktEipgRtay0fg?e=j27RHj</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQArz5Fb_foGRL2fCjFEAMHzAS-BdQ8OsjPa75qkL8_oCRA?e=BhhHGe</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQDE0JsK9kIqT6vANYh_Kw7mAUOOPi1X4KrzMAjpsK4H2hQ?e=oFcVjQ</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAnCVwYSltSTYO4yqPBtvrQAZlDcXZl5QcNqdhOE5vnS4M?e=WMJx8A</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>HILTI 125D-1.2T-10.5W-22.23H-Layered flange</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAXvQ5y5qzQRbiyxZzZJu1TAV-7gScR7gYaOClQwKa4ioA?e=k9sSsF</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.5.pdf</t>
@@ -843,7 +653,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -853,11 +663,8 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1235,11 +1042,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.75" customWidth="1"/>
+    <col min="2" max="2" width="19.75" style="3" customWidth="1"/>
     <col min="3" max="3" width="105.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1247,7 +1054,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -1255,419 +1062,22 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>4000196031150</v>
+      <c r="A2" s="1">
+        <v>333333</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="B2" s="3">
+        <v>8801753103824</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>8801230160609</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>9702040100</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
-        <v>26083025061</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>2434817</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>2314163</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
-        <v>2314164</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
-        <v>2314165</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
-        <v>2314166</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
-        <v>2314167</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
-        <v>2314168</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
-        <v>2314169</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>2384228</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>2384229</v>
-      </c>
-      <c r="B17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>2384232</v>
-      </c>
-      <c r="B18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
-        <v>2384233</v>
-      </c>
-      <c r="B19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
-        <v>2384234</v>
-      </c>
-      <c r="B20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
-        <v>2384235</v>
-      </c>
-      <c r="B21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
-        <v>2384236</v>
-      </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
-        <v>2384237</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
-        <v>2384238</v>
-      </c>
-      <c r="B24" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
-        <v>2390326</v>
-      </c>
-      <c r="B25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
-        <v>2390327</v>
-      </c>
-      <c r="B26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
-        <v>2390328</v>
-      </c>
-      <c r="B27" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="4">
-        <v>2390329</v>
-      </c>
-      <c r="B28" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
-        <v>2384224</v>
-      </c>
-      <c r="B29" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="4">
-        <v>2384225</v>
-      </c>
-      <c r="B30" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
-        <v>2384226</v>
-      </c>
-      <c r="B31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="4">
-        <v>2390320</v>
-      </c>
-      <c r="B32" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
-        <v>2390321</v>
-      </c>
-      <c r="B33" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
-        <v>2390322</v>
-      </c>
-      <c r="B34" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="4">
-        <v>2299889</v>
-      </c>
-      <c r="B35" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
-        <v>2299890</v>
-      </c>
-      <c r="B36" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
-        <v>2299891</v>
-      </c>
-      <c r="B37" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
-        <v>2453626</v>
-      </c>
-      <c r="B38" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
-        <v>2453625</v>
-      </c>
-      <c r="B39" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
-        <v>2254450</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
-        <v>2259032</v>
-      </c>
-      <c r="B41" t="s">
-        <v>57</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
-        <v>111111</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
-        <v>222222</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
-        <v>2488429</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
-        <v>333333</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{02CACEB8-149A-40E6-97F1-171D6C7C02C7}"/>
-    <hyperlink ref="C4" r:id="rId2" xr:uid="{76EDF735-7D54-4D5E-A122-602E991AB92D}"/>
-    <hyperlink ref="C3" r:id="rId3" xr:uid="{D48176E5-F1A0-43FA-BBE6-CAB7C1A3E4D4}"/>
-    <hyperlink ref="C2" r:id="rId4" xr:uid="{E221CE52-5D4B-47BE-8BB9-1B70CD524B11}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{DEAA650C-81B6-4189-9899-65C790140C23}"/>
-    <hyperlink ref="C7" r:id="rId6" xr:uid="{9D742E63-421D-4B15-ABA5-71740F93A294}"/>
-    <hyperlink ref="C8" r:id="rId7" xr:uid="{EA7565F5-47D8-44A0-A014-697F13F23F50}"/>
-    <hyperlink ref="C20" r:id="rId8" display="../../../../../../../:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAv2rp4HVTlT6AXXf-COyjcAekvmjjC3cGEGeaGIr1Vw6g?e=m7cmwH" xr:uid="{C9B83105-B6A6-416A-81FD-9941FE1FBD77}"/>
-    <hyperlink ref="C38" r:id="rId9" xr:uid="{1E52F091-1AB2-4194-A718-08968B95F4B3}"/>
-    <hyperlink ref="C39" r:id="rId10" xr:uid="{1A373658-EA00-46F5-A334-939B1092C9A3}"/>
-    <hyperlink ref="C27" r:id="rId11" xr:uid="{03635319-FBCC-46EC-840B-8E887FA6C662}"/>
-    <hyperlink ref="C12" r:id="rId12" xr:uid="{89FA1357-6F15-4D8E-AC48-C42955AC5363}"/>
-    <hyperlink ref="C40" r:id="rId13" xr:uid="{0BF5B71A-BE82-463E-88C2-CC8C1C665DC8}"/>
-    <hyperlink ref="C41" r:id="rId14" xr:uid="{6A4DBA51-F261-4342-962F-FE2962A14FA5}"/>
-    <hyperlink ref="C42" r:id="rId15" xr:uid="{3242C965-7F7C-45E4-8089-9D3F35658595}"/>
-    <hyperlink ref="C43" r:id="rId16" xr:uid="{F3743072-623A-485C-8553-58DD85DB2A22}"/>
-    <hyperlink ref="C44" r:id="rId17" xr:uid="{E138173B-E4DB-4670-8954-EF8AF33888D1}"/>
-    <hyperlink ref="C45" r:id="rId18" xr:uid="{B9530D14-BC89-4B26-B5C1-C78985E96158}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{B9530D14-BC89-4B26-B5C1-C78985E96158}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia1-my.sharepoint.com/personal/icdide_ehwadia1_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{300D0682-E2E9-4930-96AF-FE489F5E6E6B}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A6C9895-13B7-43F3-A60F-A1B3EC4789CD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>바코드스캔</t>
   </si>
@@ -46,6 +46,18 @@
   <si>
     <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.5.pdf</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.6.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.7.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.8.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.9.pdf</t>
   </si>
 </sst>
 </file>
@@ -1042,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
@@ -1072,12 +1084,72 @@
         <v>3</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>333334</v>
+      </c>
+      <c r="B3" s="3">
+        <v>8801753103825</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>333335</v>
+      </c>
+      <c r="B4" s="3">
+        <v>8801753103826</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>333336</v>
+      </c>
+      <c r="B5" s="3">
+        <v>8801753103827</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>333337</v>
+      </c>
+      <c r="B6" s="3">
+        <v>8801753103828</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>333338</v>
+      </c>
+      <c r="B7" s="3">
+        <v>8801753103829</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{B9530D14-BC89-4B26-B5C1-C78985E96158}"/>
+    <hyperlink ref="C3" r:id="rId2" display="\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.5.pdf" xr:uid="{7774E7AC-90BB-40FC-86F1-6EAD201BB75F}"/>
+    <hyperlink ref="C4" r:id="rId3" display="\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.5.pdf" xr:uid="{883EFB8A-EA5D-4607-9FEB-76CD77940AAD}"/>
+    <hyperlink ref="C5" r:id="rId4" display="\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.5.pdf" xr:uid="{A634768E-9AE2-400B-AC13-5B0F2027DDB5}"/>
+    <hyperlink ref="C6" r:id="rId5" display="\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.5.pdf" xr:uid="{0BB1E6E4-44F6-4CA5-9E31-FBE67457E7A6}"/>
+    <hyperlink ref="C7" r:id="rId6" display="\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.5.pdf" xr:uid="{C4478594-3DA8-4C3F-AA0D-EFA2A545BD59}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia1-my.sharepoint.com/personal/icdide_ehwadia1_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A6C9895-13B7-43F3-A60F-A1B3EC4789CD}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C14E16B5-F0C5-4209-9DB6-473E814D28C9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -33,31 +33,729 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
-  <si>
-    <t>바코드스캔</t>
-  </si>
-  <si>
-    <t>문서명</t>
-  </si>
-  <si>
-    <t>원드라이브 경로</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="239">
+  <si>
+    <t>Package Code</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Box bar-code</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKU/PART No.2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKU/PART No.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>File path</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>File name</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2608F01401</t>
+  </si>
+  <si>
+    <t>CDD045DIA101F</t>
+  </si>
+  <si>
+    <t>P114888 SCINTILLA BS-4.5</t>
+  </si>
+  <si>
+    <t>2608F01403</t>
+  </si>
+  <si>
+    <t>CANADA_CDD050DIA101F</t>
+  </si>
+  <si>
+    <t>P114889 SCINTILLA BS-5</t>
+  </si>
+  <si>
+    <t>2608F01466</t>
+  </si>
+  <si>
+    <t>DDD070DIA101F</t>
+  </si>
+  <si>
+    <t>P114886 SCINTILLA BS-7</t>
+  </si>
+  <si>
+    <t>2608F01467</t>
+  </si>
+  <si>
+    <t>CDD070DIA101F CANADA</t>
+  </si>
+  <si>
+    <t>P114891 SCINTILLA DIABLO BS-7</t>
+  </si>
+  <si>
+    <t>2608F01582</t>
+  </si>
+  <si>
+    <t>DDD045DIA101F</t>
+  </si>
+  <si>
+    <t>P114880 SCINTILLA BS-4.5</t>
+  </si>
+  <si>
+    <t>2608F01584</t>
+  </si>
+  <si>
+    <t>DDD050DIA101F</t>
+  </si>
+  <si>
+    <t>P114882 SCINTILLA BS-5</t>
+  </si>
+  <si>
+    <t>2608F01684</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DDD045DIA101F</t>
+  </si>
+  <si>
+    <t>P114887 SCINTILLA BS-4.5</t>
+  </si>
+  <si>
+    <t>2608F01767</t>
+  </si>
+  <si>
+    <t>DDX045DIA101F</t>
+  </si>
+  <si>
+    <t>P114881 BS-4.5</t>
+  </si>
+  <si>
+    <t>2608F01769</t>
+  </si>
+  <si>
+    <t>DDX050DIA101F</t>
+  </si>
+  <si>
+    <t>P114883 SCINTILLA BS-5</t>
+  </si>
+  <si>
+    <t>2608F02317</t>
+  </si>
+  <si>
+    <t>DMADS0900 (US)</t>
+  </si>
+  <si>
+    <t>P104097 SCINTILLA LES-9</t>
+  </si>
+  <si>
+    <t>2608F02318</t>
+  </si>
+  <si>
+    <t>DMADST0900 (US)</t>
+  </si>
+  <si>
+    <t>P104098 SCINTILLA LES-9</t>
+  </si>
+  <si>
+    <t>2608F02319</t>
+  </si>
+  <si>
+    <t>DMADST1000 (US)</t>
+  </si>
+  <si>
+    <t>P104922 SCINTILLA LES-10</t>
+  </si>
+  <si>
+    <t>2608F02320</t>
+  </si>
+  <si>
+    <t>DMADST1200 (US)</t>
+  </si>
+  <si>
+    <t>P102326 SCINTILLA LES-12</t>
+  </si>
+  <si>
+    <t>2608F02321</t>
+  </si>
+  <si>
+    <t>DMADST1400 (US)</t>
+  </si>
+  <si>
+    <t>P104923 SCINTILLA BS-14</t>
+  </si>
+  <si>
+    <t>2608F02460</t>
+  </si>
+  <si>
+    <t>P114892 SCINTILLA BS-4.5 đóng 2 PCS HỘP</t>
+  </si>
+  <si>
+    <t>2608F02525</t>
+  </si>
+  <si>
+    <t>DMADS0400 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106971 SCINTILLA LES-4</t>
+  </si>
+  <si>
+    <t>2608F02526</t>
+  </si>
+  <si>
+    <t>DMADS0450 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106972 SCINTILLA LES 4.5</t>
+  </si>
+  <si>
+    <t>2608F02528</t>
+  </si>
+  <si>
+    <t>DMADS0600 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106974 SCINTILLA LES-6</t>
+  </si>
+  <si>
+    <t>2608F02529</t>
+  </si>
+  <si>
+    <t>DMADS0700 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106975 SCINTILLA LES-7</t>
+  </si>
+  <si>
+    <t>2608F02532</t>
+  </si>
+  <si>
+    <t>DMADS1200 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106977 SCINTILLA LES-12</t>
+  </si>
+  <si>
+    <t>2608F02534</t>
+  </si>
+  <si>
+    <t>DMADST0400 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106962 SCINTILLA LES-4</t>
+  </si>
+  <si>
+    <t>2608F02535</t>
+  </si>
+  <si>
+    <t>DMADST0450 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106963 SCINTILLA LES 4.5</t>
+  </si>
+  <si>
+    <t>2608F02536</t>
+  </si>
+  <si>
+    <t>DMADST0500 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106964 SCINTILLA LES-5</t>
+  </si>
+  <si>
+    <t>2608F02538</t>
+  </si>
+  <si>
+    <t>DMADST0700 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106968 SCINTILLA LES-7</t>
+  </si>
+  <si>
+    <t>2608F02539</t>
+  </si>
+  <si>
+    <t>DMADST0900 (CANADA)</t>
+  </si>
+  <si>
+    <t>P108429 SCINTILLA AG LES-9</t>
+  </si>
+  <si>
+    <t>2608F02540</t>
+  </si>
+  <si>
+    <t>DMADST1000 (CANADA)</t>
+  </si>
+  <si>
+    <t>P108138 SCINTILLA LES-10</t>
+  </si>
+  <si>
+    <t>2608F02541</t>
+  </si>
+  <si>
+    <t>DMADST1200 (CANADA)</t>
+  </si>
+  <si>
+    <t>P107871 SCINTILLA LES-12</t>
+  </si>
+  <si>
+    <t>2608F02542</t>
+  </si>
+  <si>
+    <t>DMADST1400 (CANADA)</t>
+  </si>
+  <si>
+    <t>P107872 SCINTILLA LES-14</t>
+  </si>
+  <si>
+    <t>2608F06256</t>
+  </si>
+  <si>
+    <t>DDSDI0450 (US)</t>
+  </si>
+  <si>
+    <t>P136591 SCINTILLA BS-4.5</t>
+  </si>
+  <si>
+    <t>2608F06257</t>
+  </si>
+  <si>
+    <t>DDSDI0900 (US)</t>
+  </si>
+  <si>
+    <t>P136593 SCINTILLA BS-9</t>
+  </si>
+  <si>
+    <t>2608F06258</t>
+  </si>
+  <si>
+    <t>DDSDI1400 (US)</t>
+  </si>
+  <si>
+    <t>P136595 SCINTILLA BS-14</t>
+  </si>
+  <si>
+    <t>2608F06259</t>
+  </si>
+  <si>
+    <t>DDSDI0450 (CA)</t>
+  </si>
+  <si>
+    <t>P136592 SCINTILLA BS-4.5</t>
+  </si>
+  <si>
+    <t>2608F06260</t>
+  </si>
+  <si>
+    <t>DDSDI0900 (CA)</t>
+  </si>
+  <si>
+    <t>P136594 SCINTILLA BS-9</t>
+  </si>
+  <si>
+    <t>2608F06261</t>
+  </si>
+  <si>
+    <t>DDSDI1400 (CA)</t>
+  </si>
+  <si>
+    <t>P136596 SCINTILLA BS-14</t>
+  </si>
+  <si>
+    <t>2610075118</t>
+  </si>
+  <si>
+    <t>P126084 SCINTILLA LES-12</t>
+  </si>
+  <si>
+    <t>2610075119</t>
+  </si>
+  <si>
+    <t>P126085 SCINTILLA LES-14</t>
+  </si>
+  <si>
+    <t>P004828 SCINTILLA PD-6D</t>
+  </si>
+  <si>
+    <t>P004832 SCINTILLA PD-8D</t>
+  </si>
+  <si>
+    <t>P004834 SCINTILLA PD-10D</t>
+  </si>
+  <si>
+    <t>P115095 SCINTILLA PD-7D</t>
+  </si>
+  <si>
+    <t>P119314 SCINTILLA EDS-524</t>
+  </si>
+  <si>
+    <t>P124601</t>
+  </si>
+  <si>
+    <t>LES-5 LAP RAP</t>
+  </si>
+  <si>
+    <t>TM 31094</t>
+  </si>
+  <si>
+    <t>P119646 SCINTILLA AG LES-4.5</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608576669_P112705 SCINTILLA BEC-D25.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608576669_P123939 SCINTILLA BEC-D25.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587113_P123637 SCINTILLA PD-14.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587114_P123638 SCINTILLA PD-16D.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587115_P123639 SCINTILLA BEC-D20.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587116_P123640 SCINTILLA BEC-D22.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587117_P123641 SCINTILLA BEC-D25.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587118_P123642 SCINTILLA BEC-D27.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587119_P123643 SCINTILLA BEC-D30.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587120_P123644 SCINTILLA BEC-D32.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587121_P123645 SCINTILLA BEC-D35.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587122_P123646 SCINTILLA BEC-D38.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587123_P123653 SCINTILLA BEC-D40 BOSCH PRO.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587124_P123647 SCINTILLA BEC-D45.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587125_P123648 SCINTILLA BEC-D51.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587126_P123649 SCINTILLA BEC D55.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587127_P123046 SCINTILLA BEC-D57.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587129_P123048 SCINTILLA BEC-D65.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587131_P123049 SCINTILLA BEC-D68.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587132_P123651 SCINTILLA BEC-D70.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587133_P123652 SCINTILLA BEC-D75.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608587135_P123051 SCINTILLA BEC-D83.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608599011_P122637 SCINTILLA BMC-D20.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608599014_P131998 SCINTILLA BEC-D40.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608599022_P123741 SCINTILLA BEC-D68.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608599026_P095437 SCINTILLA BEC-D83.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608599028_P131999 SCINTILLA PD-16.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608599035_P095423 SCINTILLA BEC-D35.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608599037_P096706 SCINTILLA BMC-D20.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608599037_P127561 SCINTILLA BEC-DONG THEO SET.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608599038_P096523 BMC-D20.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608599053_P122266 SCINTILLA PD-6D.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608599054_P122267 SCINTILLA PD-7D.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608599056_P122269 SCINTILLA PD-10D.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608599057_P122270 SCINTILLA PD-12.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608599058_P122271 SCINTILLA PD-14D.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608615210_DMADST0450 (US)_P102318 SCINTILLA LES-4.5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608615211_DMADST0500(US)_P102350 SCINTILLA LES-5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608615212_DMADST0600 (US)_P102319 SCINTILLA LES-6.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608615213_DMADST0700 (US)_P102320 SCINTILLA LES-7.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608615214_DMADS0400 (US)_P102363 SCINTILLA LES 4.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608615215_DMADS0450 (USA)_P102321 SCINTILLA LES-4.5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608615218_ DMADS0700 (US)_P102324 SCINTILLA LES-7.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608615219_DMADS1000 (US)_P102403 SCINTILLA LES-10.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608615220_DMADS1200 (US)_P105649 SCINTILLA LES-12.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608615221_DMADS1400 (US)_P102327 SCINTILLA LES-14.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900531_P101325 SCINTILLA BS-4.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900531_P119003 SCINTILLA BS-4.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900532_P100203 SCINTILLA BS-4.5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900533_P100180 BS-5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900535_P101327 SCINTILLA BS-7.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900536_P100181 SCINTILLA BS-9.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900537_P111100 SCINTILLA BS-14.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900659_P102337 SCINTILLA LES-4.5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900660_P102102 SCINTILLA LES-5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900660_P124706 SCINTILLA LES-5 BOSCH EXPERT.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900661_P102338 SCINTILLA 6inch.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900662_P102339 SCINTILLA LES 7.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900663_P102103 SCINTILLA LES-9.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900663_P124707 SCINTILLA LES-9 BOSCH EXPERT.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900664_P102402 SCINTILLA LES-12.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900665_P102340 SCINTILLA LES-12.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900665_P124708 SCINTILLA LES-12.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900666_P102104 SCINTILLA LES-14.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900666_P124709 SCINTILLA LES-14 EXPERT.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900667_P102341 SCINTILLA LES 16.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900668_P102342 SCINTILLA LES-18.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608900669_P103894 SCINTILLA LES-4.5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608901391_P106844 SCINTILLA BS-5 + WHEEL.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608901392_P109920 SCINTILLA BS-9+WHEEL.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608902380_P131335 SCINTILLA AG BS-4.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608902472_P131337 SCINTILLA AG BS-4.5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608902473_P131338 SCINTILLA AG BS-5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608902474_P131339 SCINTILLA AG BS-7.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608902475_P131340 SCINTILLA AG BS-9.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608902738_P131336 SCINTILLA AG BS-4.pdf</t>
   </si>
   <si>
     <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.5.pdf</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.6.pdf</t>
-  </si>
-  <si>
-    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.7.pdf</t>
-  </si>
-  <si>
-    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.8.pdf</t>
-  </si>
-  <si>
-    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.9.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01403_CANADA_CDD050DIA101F_P114889 SCINTILLA BS-5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01466_DDD070DIA101F_P114886 SCINTILLA BS-7.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01467_CDD070DIA101F CANADA_P114891 SCINTILLA DIABLO BS-7.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01582_DDD045DIA101F_P114880 SCINTILLA BS-4.5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01584_DDD050DIA101F_P114882 SCINTILLA BS-5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01684_ DDD045DIA101F_P114887 SCINTILLA BS-4.5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01767_DDX045DIA101F_P114881 BS-4.5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01769_DDX050DIA101F_P114883 SCINTILLA BS-5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02317_DMADS0900 (US)_P104097 SCINTILLA LES-9.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02318_DMADST0900 (US)_P104098 SCINTILLA LES-9.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02319_DMADST1000 (US)_P104922 SCINTILLA LES-10.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02320_DMADST1200 (US)_P102326 SCINTILLA LES-12.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02321_DMADST1400 (US)_P104923 SCINTILLA BS-14.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02460_CDD045DIA101F_P114892 SCINTILLA BS-4.5 đóng 2 PCS HỘP.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02525_DMADS0400 (CANADA)_P106971 SCINTILLA LES-4.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02526_DMADS0450 (CANADA)_P106972 SCINTILLA LES 4.5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02528_DMADS0600 (CANADA)_P106974 SCINTILLA LES-6.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02529_DMADS0700 (CANADA)_P106975 SCINTILLA LES-7.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02532_DMADS1200 (CANADA)_P106977 SCINTILLA LES-12.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02534_DMADST0400 (CANADA)_P106962 SCINTILLA LES-4.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02535_DMADST0450 (CANADA)_P106963 SCINTILLA LES 4.5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02536_DMADST0500 (CANADA)_P106964 SCINTILLA LES-5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02538_DMADST0700 (CANADA)_P106968 SCINTILLA LES-7.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02539_DMADST0900 (CANADA)_P108429 SCINTILLA AG LES-9.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02540_DMADST1000 (CANADA)_P108138 SCINTILLA LES-10.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02541_DMADST1200 (CANADA)_P107871 SCINTILLA LES-12.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F02542_DMADST1400 (CANADA)_P107872 SCINTILLA LES-14.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F06256_DDSDI0450 (US)_P136591 SCINTILLA BS-4.5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F06257_DDSDI0900 (US)_P136593 SCINTILLA BS-9.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F06258_DDSDI1400 (US)_P136595 SCINTILLA BS-14.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F06259_DDSDI0450 (CA)_P136592 SCINTILLA BS-4.5.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F06260_DDSDI0900 (CA)_P136594 SCINTILLA BS-9.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F06261_DDSDI1400 (CA)_P136596 SCINTILLA BS-14.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2610075118_P126084 SCINTILLA LES-12.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2610075119_P126085 SCINTILLA LES-14.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_P004828 SCINTILLA PD-6D.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_P004832 SCINTILLA PD-8D.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_P004834 SCINTILLA PD-10D.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_P115095 SCINTILLA PD-7D.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_P119314 SCINTILLA EDS-524.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_P124601_LES-5 LAP RAP.pdf</t>
+  </si>
+  <si>
+    <t>\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_TM 31094_P119646 SCINTILLA AG LES-4.5.pdf</t>
   </si>
 </sst>
 </file>
@@ -67,7 +765,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,10 +928,16 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color theme="10"/>
+      <color rgb="FF0563C1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -661,23 +1365,22 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -722,7 +1425,7 @@
     <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="42" builtinId="8"/>
+    <cellStyle name="표준 2" xfId="42" xr:uid="{A5FF40A0-58E6-4029-9DCA-82A542877A1D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1054,102 +1757,1134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="105.375" customWidth="1"/>
+    <col min="1" max="2" width="21.875" style="1" customWidth="1"/>
+    <col min="3" max="5" width="21.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="105.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>333333</v>
-      </c>
-      <c r="B2" s="3">
-        <v>8801753103824</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>333334</v>
-      </c>
-      <c r="B3" s="3">
-        <v>8801753103825</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>333335</v>
-      </c>
-      <c r="B4" s="3">
-        <v>8801753103826</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>333336</v>
-      </c>
-      <c r="B5" s="3">
-        <v>8801753103827</v>
-      </c>
-      <c r="C5" s="2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>333337</v>
-      </c>
-      <c r="B6" s="3">
-        <v>8801753103828</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>333338</v>
-      </c>
-      <c r="B7" s="3">
-        <v>8801753103829</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>7</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="F36" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="5"/>
+      <c r="F37" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="F38" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="F39" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="F40" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="F41" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="F42" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="5"/>
+      <c r="F43" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="F44" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F45" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F46" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F47" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F48" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F49" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="50" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F50" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="51" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F51" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="52" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F52" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="53" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F53" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="54" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F54" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="55" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F55" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="56" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F56" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="57" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F57" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="58" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F58" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="59" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F59" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="60" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F60" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="61" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F61" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="62" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F62" s="6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="63" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F63" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="64" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F64" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="65" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F65" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="66" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F66" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="67" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F67" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="68" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F68" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="69" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F69" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="70" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F70" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="71" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F71" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="72" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F72" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="73" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F73" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="74" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F74" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="75" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F75" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="76" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F76" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="77" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F77" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="78" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F78" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="79" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F79" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="80" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F80" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="81" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F81" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="82" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F82" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="83" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F83" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="84" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F84" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="85" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F85" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="86" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F86" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="87" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F87" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="88" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F88" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="89" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F89" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="90" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F90" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="91" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F91" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="92" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F92" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="93" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F93" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="94" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F94" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="95" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F95" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="96" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F96" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="97" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F97" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="98" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F98" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="99" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F99" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="100" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F100" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="101" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F101" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="102" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F102" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="103" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F103" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="104" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F104" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="105" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F105" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="106" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F106" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="107" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F107" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="108" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F108" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="109" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F109" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="110" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F110" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="111" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F111" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="112" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F112" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="113" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F113" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="114" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F114" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="115" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F115" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="116" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F116" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="117" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F117" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="118" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F118" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="119" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F119" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="120" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F120" s="6" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{B9530D14-BC89-4B26-B5C1-C78985E96158}"/>
-    <hyperlink ref="C3" r:id="rId2" display="\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.5.pdf" xr:uid="{7774E7AC-90BB-40FC-86F1-6EAD201BB75F}"/>
-    <hyperlink ref="C4" r:id="rId3" display="\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.5.pdf" xr:uid="{883EFB8A-EA5D-4607-9FEB-76CD77940AAD}"/>
-    <hyperlink ref="C5" r:id="rId4" display="\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.5.pdf" xr:uid="{A634768E-9AE2-400B-AC13-5B0F2027DDB5}"/>
-    <hyperlink ref="C6" r:id="rId5" display="\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.5.pdf" xr:uid="{0BB1E6E4-44F6-4CA5-9E31-FBE67457E7A6}"/>
-    <hyperlink ref="C7" r:id="rId6" display="\\130.1.1.78\ehwa_ppwr\Packaging Instruction\PI_VN\Customer SKU\SCINTILLA change SKU share one drive 23.09.2026 119\SCINTILLA_2608F01401_CDD045DIA101F_P114888 SCINTILLA BS-4.5.pdf" xr:uid="{C4478594-3DA8-4C3F-AA0D-EFA2A545BD59}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="F8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="F9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="F10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="F11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="F12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="F13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="F14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="F15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="F16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="F17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="F18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="F19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="F20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="F21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="F22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="F23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="F24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="F25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="F26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="F27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="F28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="F29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="F30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="F31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="F32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="F33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="F34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="F35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="F36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="F37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="F38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="F39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="F40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="F41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="F42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="F43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="F44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="F45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="F46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="F47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="F48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="F49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="F50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="F51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="F52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="F53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="F54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="F55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="F56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="F57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="F58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="F59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="F60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="F61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="F62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="F63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="F64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="F65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="F66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="F67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="F68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="F69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="F70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="F71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="F72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="F73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="F74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="F75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="F76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="F77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="F78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="F79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="F80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="F81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="F82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="F83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="F84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="F85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="F86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="F87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="F88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="F89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="F90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="F91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="F92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="F93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="F94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="F95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="F96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="F97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="F98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="F99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="F100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="F101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="F102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="F103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="F104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="F105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="F106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="F107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="F108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="F109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="F110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="F111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="F112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="F113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="F114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="F115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="F116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="F117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="F118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="F119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="F120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId120"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia1-my.sharepoint.com/personal/icdide_ehwadia1_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C30535F-3529-4F07-83C2-322DBDB9E821}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C27B58C-80A5-4575-83E3-09779DE1B019}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="754">
   <si>
     <t>Package Code</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -342,6 +342,1965 @@
   </si>
   <si>
     <t>P122270 SCINTILLA PD-12</t>
+  </si>
+  <si>
+    <t>2164058</t>
+  </si>
+  <si>
+    <t>P110977 GT LES 4.5 HILTI</t>
+  </si>
+  <si>
+    <t>2164059</t>
+  </si>
+  <si>
+    <t>P110978 GT LES-5 HILTI</t>
+  </si>
+  <si>
+    <t>2200887</t>
+  </si>
+  <si>
+    <t>P104127 GT HILTI BS-14</t>
+  </si>
+  <si>
+    <t>2200899</t>
+  </si>
+  <si>
+    <t>P110225 GT HILTI BS-12</t>
+  </si>
+  <si>
+    <t>2205729</t>
+  </si>
+  <si>
+    <t>P110224 GT BS-9(HILTI)</t>
+  </si>
+  <si>
+    <t>2238557</t>
+  </si>
+  <si>
+    <t>P103660 HILTI(LI) PCD-5</t>
+  </si>
+  <si>
+    <t>2254450</t>
+  </si>
+  <si>
+    <t>P111279 HILTI(LI) BS-4</t>
+  </si>
+  <si>
+    <t>2254451</t>
+  </si>
+  <si>
+    <t>P111280 HILTI(LI) BS-5</t>
+  </si>
+  <si>
+    <t>2258800</t>
+  </si>
+  <si>
+    <t>P111275 HILTI(LI) BS-4</t>
+  </si>
+  <si>
+    <t>2258801</t>
+  </si>
+  <si>
+    <t>P111277 HILTI(LI) BS-5</t>
+  </si>
+  <si>
+    <t>2314163</t>
+  </si>
+  <si>
+    <t>P109660 HILTI(LI) BS-4</t>
+  </si>
+  <si>
+    <t>2314165</t>
+  </si>
+  <si>
+    <t>P109476 HILTI(LI) BS-5</t>
+  </si>
+  <si>
+    <t>2314166</t>
+  </si>
+  <si>
+    <t>P109477 HILTI (LI) BS-9</t>
+  </si>
+  <si>
+    <t>2314167</t>
+  </si>
+  <si>
+    <t>P109478 HILTI(LI) BS-12</t>
+  </si>
+  <si>
+    <t>2314168</t>
+  </si>
+  <si>
+    <t>P109479 HILTI(LI) BS-14</t>
+  </si>
+  <si>
+    <t>2314169</t>
+  </si>
+  <si>
+    <t>P109480 HILTI (LI) BS-16</t>
+  </si>
+  <si>
+    <t>2384224</t>
+  </si>
+  <si>
+    <t>P118841 HILTI(LI) LES-12</t>
+  </si>
+  <si>
+    <t>2384225</t>
+  </si>
+  <si>
+    <t>P118842 HILTI(LI) LES-14</t>
+  </si>
+  <si>
+    <t>2384226</t>
+  </si>
+  <si>
+    <t>P118844 HILTI (LI) LES-16</t>
+  </si>
+  <si>
+    <t>2384227</t>
+  </si>
+  <si>
+    <t>P131456 HILTI BS-4</t>
+  </si>
+  <si>
+    <t>2384228</t>
+  </si>
+  <si>
+    <t>P118851 HILTI(LI) BS-4</t>
+  </si>
+  <si>
+    <t>2384229</t>
+  </si>
+  <si>
+    <t>P118852 HILTI (LI) BS-5</t>
+  </si>
+  <si>
+    <t>2384232</t>
+  </si>
+  <si>
+    <t>P118853 HILTI(LI) BS-9</t>
+  </si>
+  <si>
+    <t>2384233</t>
+  </si>
+  <si>
+    <t>P118854 HILTI BS-12</t>
+  </si>
+  <si>
+    <t>2384234</t>
+  </si>
+  <si>
+    <t>P118855 HILTI(LI) BS-14</t>
+  </si>
+  <si>
+    <t>2384236</t>
+  </si>
+  <si>
+    <t>P118837 HILTI(LI) BS-5</t>
+  </si>
+  <si>
+    <t>2384237</t>
+  </si>
+  <si>
+    <t>P118838 HILTI(LI) BS-9</t>
+  </si>
+  <si>
+    <t>2384238</t>
+  </si>
+  <si>
+    <t>P118839 HILTI(LI) BS-12</t>
+  </si>
+  <si>
+    <t>2390320</t>
+  </si>
+  <si>
+    <t>P118724 HILTI(LI) LES-12</t>
+  </si>
+  <si>
+    <t>2390321</t>
+  </si>
+  <si>
+    <t>P118725 HILTI(LI) LES-14</t>
+  </si>
+  <si>
+    <t>2390322</t>
+  </si>
+  <si>
+    <t>P118843 HILTI(LI) LES-16</t>
+  </si>
+  <si>
+    <t>2390326</t>
+  </si>
+  <si>
+    <t>P118726 HILTI(LI) BS-12</t>
+  </si>
+  <si>
+    <t>2390327</t>
+  </si>
+  <si>
+    <t>P118727 HILTI(LI) BS-14</t>
+  </si>
+  <si>
+    <t>2390328</t>
+  </si>
+  <si>
+    <t>P118856 HILTI(LI) BS-16</t>
+  </si>
+  <si>
+    <t>2390329</t>
+  </si>
+  <si>
+    <t>P119453 HILTI(LI) BS-12</t>
+  </si>
+  <si>
+    <t>2434705</t>
+  </si>
+  <si>
+    <t>P126121 HILTI(LI) BS-5</t>
+  </si>
+  <si>
+    <t>2434709</t>
+  </si>
+  <si>
+    <t>P126122 HILTI BS-7</t>
+  </si>
+  <si>
+    <t>2434729</t>
+  </si>
+  <si>
+    <t>P126123 HILTI(LI) BS-9</t>
+  </si>
+  <si>
+    <t>2434791</t>
+  </si>
+  <si>
+    <t>P126124 HILTI(LI) BS-12</t>
+  </si>
+  <si>
+    <t>2434834</t>
+  </si>
+  <si>
+    <t>P126126 HILTI(LI) BS-16</t>
+  </si>
+  <si>
+    <t>P092387 HILTI(LI) BS-24</t>
+  </si>
+  <si>
+    <t>P119461 HILTI(LI) BS-3</t>
+  </si>
+  <si>
+    <t>P127128 HILTI(LI) LES-14</t>
+  </si>
+  <si>
+    <t>P128087 HILTI(LI) BEC-D25</t>
+  </si>
+  <si>
+    <t>P128087 HILTI(LI) PD-14D</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAX6IrNzQFWQo0wsxiRHz5SARyOaa9ICLwZqv40GUOmK6s</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAqfn0r_Mj_Qb6wbfyKiEwAASGXJwD2gXnbI37D1pLFjMk</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAAiiIm1aKCTLtPlKFTK-T1ASmJ3awMLS-xRD97TR-v85M</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAdPyMd9zT2SJ1uWMaPn2__AWC8U2ASQGTh-tCeiN1B3XE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCA7LU8Aq1CTpRM3mxry43ZAWWa1WumtypeXM3AgqxcA5k</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCGxLCfdhdlQLn2Xw8bFLm3Ac4qWn6a6H9QaDGmg0Mh2z4</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAB8rziYUyTSLlIEvlgy0dnARgSoDW4FLxv4I3gTQpba6M</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBLQsGLeLbJQoLqYnmB_3jEAfqR7wBdeJZbYw5jj6ylKlo</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQC0uP5gQRn_Qp-0HwEXOhPTAeSH3vD1NXGqgvt-oLjPFQY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBjYtzZCYYcR5RLLmqUjMO-AQQqg0gYQraXb3kiNW2qB8c</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBbVIxedp5HRZfZ6VA9qmaZAdcmGWzfVTlXIfQVfSgkvCM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCkI79PcolKTrhNHknRei4UATqxgcrveF2T4fMW6UQDrnQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCOZQyNukP8ToPX28mK49EKAT_UN-3V2parp3P6HA1yaXU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAZpFI-toXQRYvrgiZEjM5xAZw3H4uh_zTjJ4cg7NQE4Xw</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD5nRa7H1I3SLfCR7Nvqz7rAdmm9cHM2Vu97YkZER46El4</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDrHmRjh6mpTIn3Np2OgTirASEs0H7gXtyWCwTJSgXQ7ZI</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCwDYXFCV0xTZt7JoZ_lwvbAd3WfJAkOvPGpr2LOUEEX6g</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQC6x3IUntfSSau018Ckd_y_AX4Adgi7nlCfshMrqyd8w_I</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBeI9QnfE8qQq3D5nt3B0ulAeI61FHlLzfVY87Ayly_1pE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDPmj9qNKskQ4bMd4qasA4NAXYLxgks12GcK38_G25566M</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD-4JNL817xRpsdJoDBlunJAbckhDRvfqPSuqMlOrEh1lA</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCxKkzL3dY_SojkB3VyjjLdAeXKULOhagLWO_2rk8pxaeU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBbYo1Z1CQDQqo0tPz5NailAblALjWuICDjeFGps93MCcg</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAx7LaDhn3FS5odHTLEd8bkAbxcQ17PQTelTRpXfGCMK18</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAX8AGGLiAERITfPxUtRCoMAa3ESjPNuTCKJHPXDKBSMww</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQB18d0wCm28RYnnpTsANWE-AQPUyOEkhoV2IJA1T4d_QuU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBSSRn24JAVTZwRM9norEAbAUZBT5Q_VBABJpOnlgRFcp0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDCYRgE_sPXTJXbPiSO3PIdAauTJ7SI-wK5mFUEnU6sPt4</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDHBghs1LxOSrbfHfdV8VuuAdCCzISv0IrGyINJhsMgQOA</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDDnBNYJEsRQIxGfEShOWyMARiZ195BeqHp2ATl6_8ev4o</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDKzJklzJTVTJdGpOx0KIvyAUm69ucAeuBG0ip5dksWyos</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBMUsrQJ_akQZ-PNzMsOPd9AY9CplaHdpir86EauBi4rCQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDuIuNkIaSwTb7rmEX8pBKdAZSyqNnrRlM4AoanY5k0hsM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQArPt-H5A_BRYJsy_ewa5CUARir_ic2UKY1TEWbX17_4I8</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDksy5hycs0TLLEA0DgZhWYAQUugifHm51ScCqkTmhtIbk</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDeVOZTHBPiQ7KG-UB7PxXYAZeCF9wGxB1pDQQnLHafmG0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDGxftk_9imS5HKEaqTJEKXAQM0WNJZQ7fm2QYkIwyglgw</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDxHv_Au2roTIXDvc36dH_0AfuL3nuNh_iROtjItwPObao</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD0hLbOieqISZvZDT9k6BftAWUgd9UHRVvwor1wcj_llis</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA-iwWD1GDDRaI7glMwJQljAZQYf2u3w5IHUgeTawg3O7g</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBcYNpSTBfiQ6Ph68w2eGHFASnEPHw_wkYRw0d4pIShGEI</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD4tWEfBaEhSLTdzUW0UHGuAW3Csh5jOrPexxL9B36A-oM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBuuMHR42VmR4xz_y5rgbX_Af9Vkajfl26hregi5jvYBZ4</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAaUx6CgywIRaqoMvaZ1avQAcIdxMuybhv54Q0Oo2gmt1E</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCE8dvTFwT_RpbbMlJYjYNVAWxaDzrj1gxsgeW1DGoJBxw</t>
+  </si>
+  <si>
+    <t>P110674 BS-5</t>
+  </si>
+  <si>
+    <t>5526 711 150</t>
+  </si>
+  <si>
+    <t>5526 961 126</t>
+  </si>
+  <si>
+    <t>P103592</t>
+  </si>
+  <si>
+    <t>5527 961 126</t>
+  </si>
+  <si>
+    <t>0668 050 230</t>
+  </si>
+  <si>
+    <t>0668 300 125</t>
+  </si>
+  <si>
+    <t>0664 006 125</t>
+  </si>
+  <si>
+    <t>0666 796 350</t>
+  </si>
+  <si>
+    <t>0668 420 076</t>
+  </si>
+  <si>
+    <t>0668 450 230</t>
+  </si>
+  <si>
+    <t>5526 664 125</t>
+  </si>
+  <si>
+    <t>5526 711 125</t>
+  </si>
+  <si>
+    <t>5527 164 125</t>
+  </si>
+  <si>
+    <t>P115374 BCU-5</t>
+  </si>
+  <si>
+    <t>P115431 BS-14</t>
+  </si>
+  <si>
+    <t>0668 430 076</t>
+  </si>
+  <si>
+    <t>0668 115 401</t>
+  </si>
+  <si>
+    <t>5527 962 128</t>
+  </si>
+  <si>
+    <t>5526 860 115</t>
+  </si>
+  <si>
+    <t>0664 006 115</t>
+  </si>
+  <si>
+    <t>0668 440 125</t>
+  </si>
+  <si>
+    <t>0668 450 125</t>
+  </si>
+  <si>
+    <t>P078090 BS-4.5</t>
+  </si>
+  <si>
+    <t>5526 860 350</t>
+  </si>
+  <si>
+    <t>0667 410 232</t>
+  </si>
+  <si>
+    <t>5526 860 230</t>
+  </si>
+  <si>
+    <t>5526 860 300</t>
+  </si>
+  <si>
+    <t>5526 860 355</t>
+  </si>
+  <si>
+    <t>5527 160 140</t>
+  </si>
+  <si>
+    <t>5527 160 150</t>
+  </si>
+  <si>
+    <t>5527 164 230</t>
+  </si>
+  <si>
+    <t>5527 260 125</t>
+  </si>
+  <si>
+    <t>5527 260 230</t>
+  </si>
+  <si>
+    <t>5527 961 129</t>
+  </si>
+  <si>
+    <t>P113632 BS-14</t>
+  </si>
+  <si>
+    <t>P114263  PS-7</t>
+  </si>
+  <si>
+    <t>0666 112 300</t>
+  </si>
+  <si>
+    <t>0668 300 115</t>
+  </si>
+  <si>
+    <t>0668 300 230</t>
+  </si>
+  <si>
+    <t>0668 760 230</t>
+  </si>
+  <si>
+    <t>0668 270 501</t>
+  </si>
+  <si>
+    <t>0668 515 514</t>
+  </si>
+  <si>
+    <t>0668 900 650</t>
+  </si>
+  <si>
+    <t>0666 310 100</t>
+  </si>
+  <si>
+    <t>666 999 451</t>
+  </si>
+  <si>
+    <t>0664 006 150</t>
+  </si>
+  <si>
+    <t>0666 850 230</t>
+  </si>
+  <si>
+    <t>0666 110 350</t>
+  </si>
+  <si>
+    <t>0668 125 110</t>
+  </si>
+  <si>
+    <t>0668 230 110</t>
+  </si>
+  <si>
+    <t>0664 006 180</t>
+  </si>
+  <si>
+    <t>0664 006 309</t>
+  </si>
+  <si>
+    <t>0668 111 351</t>
+  </si>
+  <si>
+    <t>0668 001 125</t>
+  </si>
+  <si>
+    <t>0668 001 180</t>
+  </si>
+  <si>
+    <t>0668 122 400</t>
+  </si>
+  <si>
+    <t>0668 515 126</t>
+  </si>
+  <si>
+    <t>668 998 351</t>
+  </si>
+  <si>
+    <t>0668 115 110</t>
+  </si>
+  <si>
+    <t>0668 180 110</t>
+  </si>
+  <si>
+    <t>0666 850 115</t>
+  </si>
+  <si>
+    <t>0666 793 230</t>
+  </si>
+  <si>
+    <t>P078213 BS-9</t>
+  </si>
+  <si>
+    <t>P010334 LES-9</t>
+  </si>
+  <si>
+    <t>P105662 LES-5</t>
+  </si>
+  <si>
+    <t>P010232 LES-20</t>
+  </si>
+  <si>
+    <t>P010233 LES-20</t>
+  </si>
+  <si>
+    <t>P076234 LES-26</t>
+  </si>
+  <si>
+    <t>P010478 EDS-411</t>
+  </si>
+  <si>
+    <t>P046442 LES-18</t>
+  </si>
+  <si>
+    <t>P107122 PLES-6</t>
+  </si>
+  <si>
+    <t>P060705 BS-4.5</t>
+  </si>
+  <si>
+    <t>P095656 BS-3</t>
+  </si>
+  <si>
+    <t>P044305 BS-9</t>
+  </si>
+  <si>
+    <t>P010315 BS-9</t>
+  </si>
+  <si>
+    <t>P040065 LES-14</t>
+  </si>
+  <si>
+    <t>P085433 LES-5</t>
+  </si>
+  <si>
+    <t>P010268 LES-9</t>
+  </si>
+  <si>
+    <t>P107123 PLES-7</t>
+  </si>
+  <si>
+    <t>P107132 PLES-12</t>
+  </si>
+  <si>
+    <t>P036562 LES-14</t>
+  </si>
+  <si>
+    <t>P044304 UAB BS-5</t>
+  </si>
+  <si>
+    <t>P056733 BCU-5</t>
+  </si>
+  <si>
+    <t>P056235 BCU-7</t>
+  </si>
+  <si>
+    <t>P010468 LES-16</t>
+  </si>
+  <si>
+    <t>P135316 LES-5</t>
+  </si>
+  <si>
+    <t>P135317 LES-14</t>
+  </si>
+  <si>
+    <t>P010273 LES-4.5</t>
+  </si>
+  <si>
+    <t>P010267 LES-7</t>
+  </si>
+  <si>
+    <t>P060706 BS-5</t>
+  </si>
+  <si>
+    <t>P010316 BS-4.5</t>
+  </si>
+  <si>
+    <t>P097812 LES-9</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH(HU)</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH(PL)</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH(PT)</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH(RO)</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH</t>
+  </si>
+  <si>
+    <t>UAB WURTH LIETUVA</t>
+  </si>
+  <si>
+    <t>WURTH (ES)TH (ES)</t>
+  </si>
+  <si>
+    <t>WURTH CO BRASIL</t>
+  </si>
+  <si>
+    <t>WURTH ES TH ES</t>
+  </si>
+  <si>
+    <t>WURTH INTERNATION AG</t>
+  </si>
+  <si>
+    <t>WURTH LIETUVA</t>
+  </si>
+  <si>
+    <t>WURTH PORTUGAL TECNICA DE</t>
+  </si>
+  <si>
+    <t>WURTH PORTUGAL</t>
+  </si>
+  <si>
+    <t>WURTH ROMANIA S.R</t>
+  </si>
+  <si>
+    <t>WURTH ROMANIA</t>
+  </si>
+  <si>
+    <t>WURTH(ES) TH(ES)</t>
+  </si>
+  <si>
+    <t>WURTH(ES)TH(ES)</t>
+  </si>
+  <si>
+    <t>WURTH</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH (CH)</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH (DE)</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH (DK)</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH (RO)</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH CH</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH DE</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH GMBH&amp;C</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH GMBH</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH HU</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH PL</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH PT</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH(CH) RECA</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH(CH)</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH(CN)</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH(CO)</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH(DE)</t>
+  </si>
+  <si>
+    <t>ADOLF WURTH(DK)</t>
+  </si>
+  <si>
+    <t>P095381 LES-6</t>
+  </si>
+  <si>
+    <t>P103587 PLES-5</t>
+  </si>
+  <si>
+    <t>P103590  PLES-5</t>
+  </si>
+  <si>
+    <t>P092402 LES-5</t>
+  </si>
+  <si>
+    <t>P056518 LES-9</t>
+  </si>
+  <si>
+    <t>P043102 BS-5</t>
+  </si>
+  <si>
+    <t>P107121 PLES-5</t>
+  </si>
+  <si>
+    <t>P095978 LES-14</t>
+  </si>
+  <si>
+    <t>P116073 BS-9</t>
+  </si>
+  <si>
+    <t>P107786 PLES-5</t>
+  </si>
+  <si>
+    <t>P095370 LES 5</t>
+  </si>
+  <si>
+    <t>P095165 LES-5</t>
+  </si>
+  <si>
+    <t>P095657 BS-3</t>
+  </si>
+  <si>
+    <t>P010352 LES-16</t>
+  </si>
+  <si>
+    <t>P098227 BS-5</t>
+  </si>
+  <si>
+    <t>P061858 BS-4.5</t>
+  </si>
+  <si>
+    <t>P107120 PLES-4.5</t>
+  </si>
+  <si>
+    <t>P110591 BS-5</t>
+  </si>
+  <si>
+    <t>P110592 BS-5</t>
+  </si>
+  <si>
+    <t>P045197 BS-14</t>
+  </si>
+  <si>
+    <t>P103596 BS-9 W</t>
+  </si>
+  <si>
+    <t>P010153 BS-4.5</t>
+  </si>
+  <si>
+    <t>P010149 BS-9</t>
+  </si>
+  <si>
+    <t>P010216 BS-9</t>
+  </si>
+  <si>
+    <t>P038483 BS-12</t>
+  </si>
+  <si>
+    <t>P010151 BS-14</t>
+  </si>
+  <si>
+    <t>P010152 BS-14</t>
+  </si>
+  <si>
+    <t>P079070 LES-5.5</t>
+  </si>
+  <si>
+    <t>P079071 LES-6</t>
+  </si>
+  <si>
+    <t>P095166 LES-9</t>
+  </si>
+  <si>
+    <t>P079074 LES-5</t>
+  </si>
+  <si>
+    <t>P079075 LES-9</t>
+  </si>
+  <si>
+    <t>P095655 LES-5 LAP RAP</t>
+  </si>
+  <si>
+    <t>P094853 BS-5</t>
+  </si>
+  <si>
+    <t>P010259 PLES-12</t>
+  </si>
+  <si>
+    <t>P076584 BS-4.5</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAQBVFL1M4sQ6ZCUeJWSIicAcmZdLk1LD3OrYzXpl0PBUY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD86Kt4xvjiRK2GTxG-j-JTAVAoAx0SOCNsPVdCx-2U-IM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQC2EI92oaaZRYey9ViSi-4QAc5XZ-PK41LvP3TZ9Y3gfN0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBehmeoe9UdQ53JGi21qenTAVdPuVY3CsUu3NJT9kAwWwM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBu-13clYAdSp_Ysl20KLbxAXOX3h-m5ZMoBUdrcOU2GXw</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBN8BWDLLLARanxJsWqsvBKAZ5_4b3UBZ-MTcfNHx2LClY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBWgFyC4k4eQ7GgYkXy4tn1ASQtmMnMxXMKws-rqvO-I1I</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD6UbV2xTUcSLkk9NqpwsW0AVtiKIuIppBvwLX-_Zi4caY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA_ht2cU-oETp-7E6QomMs6ARCuiJKNOvIZi62SZHLJPc0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBPVpMY8GsfQq78QH-SjK1BASjwpliTdvOx6EMnxETgiOM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCBxY58bFStR4lrrbVHZAi3AQo_qOKr9GurH4BPxWvlNQY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDaa4RBUuuhQ46XRm_Ib_64AW_rtg1CP8pLQbY5Hf3y704</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQChd1Mv3lKASJPsqr13T9RsASdt7nmSUX2p3s4P9JNvYkM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCRcry9c_etQ4xRgSzaN9-ZAbMJHSY12kh0DufrlJzF5aA</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA8J00-LYJpSoChMLMzPZ-PAYhK7KoIx6jMAQgXXPIIt-A</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDeZO6tqQrUTpPzEL0TeigAASVtUV89J2xq97shB3SI4O4</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCXkVX4xEBwT44zvGqZ9rIGAUH7YLrHwI3mjdN_a-8Z6j0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCEDwp5LNQASIodTNYjX5keAZMRZRQPfHzR3pbaqTeu248</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDlIMUf1Uw0SY6POkCq1K2BAeKnbFXHrd3pttTaDrv4TDI</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQB3KoqCNSvVT62dI14QTgswAQFQTwpz9MoPsuGFKGM6PKo</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDuj_X-esNqQa9pYX6L-NYvATnR76Ro8Sp8Gx4f-w__vRI</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQARfabvd8WOTJmCxqyNU5jfASkCEM7AsN6u2tcbEbG3FKE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBVkTTRUl7_RI0r8qtr2MLDAW-baE25uwnh9vNcPLTiU08</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDsQoN-P5qjRL6Z8eZhIusNAVmNFHJ5zkIpQ7scV5jYb6E</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAOMGcB_5DPS7XOgUE2pu8zAUv5FivE523mMWP8IAjPbGA</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA5C2mpT6AJS4iCsAYChoVjAZh2XaUE7xGhUUnM27cIoeQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDvvsVb1aYdQqGuw2ENSCmgARcPy9rZQicLPeTCBhOS7BE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBvWw13uticRbXq_gVH6X9qAZ_o-lB7rznhlk3WyJiYyS0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA8DMbWsXhWS4v0K8lhHxZiAYrdXZMgR4JqDFtog6zpO-c</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCnWtN_h_yTRLW0Z6ORTLtoAXtCgPmPw69q51mYRWQ6_Uk</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBxHe2jm5QqT4pU9F3pTx9aAdEH0CM9zADMyUjQzsXbOOU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCbc1YUQVfnSpW1krjBNatEAb-JNUdv8_4mV9pAAgkhotk</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQABXVqscWz6S6of-akDYdSvAeIf0qIVE-vh1WQfwQ4ykAM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAlqnXPcjZWT5PbGIb_7jhZAWQr2v-gbtcE7-HHbFqqcRY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBmy9kg_6ByTaMvxWH-6ggoAVVb8OLFgr6kAOHE7-TXp8s</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDPnAqn7B3dTL32OVb4dsVUATy9u-yrezlqGUGe3W5LDlA</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAA2WkjhG7ARJF7_ffFVW7gAWDmrMY5DrKPs3jAR6krhDs</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQB5E51kThJFSKvqnCh-gQLjAa0P4PLAmL-PH2rO8KWEcWs</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCT-X80lSE6Q59fvvGrHyzOASNaN_ah8TMUzvZHwHOAZTg</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCTkBM_Hlk8RITAEvZvoj2OAdfgUJlDtJOcOv0liLz1af8</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDHnroh8G6_R4_z3clvoT30AdrlBXYFG_QTg7os43sBEOI</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDTdhRvAfEoTq5-YweIAP5vAV6fEc6ZkmOMzEc0Q5OMFik</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCklOCJlTMzQK2KSNKcwRK3Ae2kCR0DtcOJ-JsHWRpJ12Q</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDiZMqhJfX2QJg6wg2kh6EkAR7XQzdgN9Kv3rx1dDjTFiY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDMC80S36q1QLO5vocTEFXOARNlghEuSVlC1EN97IEE8JI</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCpH8kHxLPHRKnsLxl0ToZBAZ9-DRBqmrqz44bWcVnMOl4</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBVXpz6yO7gQofPM5IAVwwuAT0tZxi3Kw8g_yIq847l35g</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCUhUfRB8KYTqUBTLMt4qb-ARGuDdHdW8-K8vsy4Q9ecFg</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCyoWhAAvYRTq7MEX7auD5XAbNAiljSGHmHWMMh2LEyCTo</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBMK_zDoFLpR4PVN0ckru1iAbvpYn0YOqpzmyykQlKQuvo</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDO4nArrz36Tb5lpXORzOafAQGMuDlo6BODoVU7o8UtSww</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD2kHtsa-XUSolHNyDvx0H0AVnS2PvICoastZvWKGmiezY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCv3JG84aj6T7ohrwNlknN6Af6wuAeYXP-IilrG3wV57hc</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBRMNXI7edGTK_9upoXWTYpAY7PZdtku6dUYXNFRyhLn8Y</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBvCvpHEL2rTY-2Fx4d1ZXmAfRlmAo1MuHxiFl2eDtYJlY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQB7kdx-oEM7RLN3fyIozaRFAewjpEAIJXWLIldVbk38fbc</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAq62BmaJfaQrcfrhza4ln8AQIrBdQalKDcqmXlVTZeg3Y</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA_VKnaMV0UQ4qY3-3C8vHgAdWXuszmGMGzcMcG2nLuSW0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBmfJBe_o16Q6DaVBEEspC4AXCpQavCNEdRVU0nof6LOHY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCg-A4xCZLOQ7-l9yN2GC46AdDkOXHW12GmpzntRNAvsHw</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAh_OAS5v9bSo0Nl26GsvkJAdjxZftUWSLtRjYKQoUqnC0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD2hur0bLPgTJERTBTRVBozAcEbb8R7ub2GVkAOQQc0IVU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQB8bHNh9szYQ7ugW_yywhRpAYJgtuSB_Mc6IGx0BxGXtIY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBWbx9YXARCR77RKmbg3bUNAUI-ftPYt_CBFIw74mIorMg</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAwMbgZNIvmSoJPxbYWeFD6Adjgw5qU5IO8iZtQPUUJ6_4</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAWaMtjvpYJSLHSE-ejb30jAcyhweA-KrZGtg8zTtMLMK0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQB6DKVf5KdgRqAb5pCVIUfAAWo7z_zB7yqcrTekiyRqSi0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAqTOGkzsk3Qpfs97Z4yekpAT-GPnbExb5dpRyZw7PAs5I</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAtXAmJkkJKT7wzW4MXg-cdASrWpblaHkokc8pNHTrn6Nk</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDtZ53LlOWLQ4N-dQdG5_l9AQXvlQkjZ_cyTN1a7VFzfmA</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCofR0txpAWQoEjHh9UTOAVAY1haeaD5T074-xWWG50xdU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCiJAnx1ctqRZWEzHOMVGayAQkCWSEoheVguu1WmKsieoQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA7RxJWHi1tSp8nwFLpciSQAU4fINUQY_4QFAd5-8jcGj4</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQApV0N6rml4R7z7aom6nCicAbKiir8e1D-psMX6YYhpa2c</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAiUS6-kWxiT5RRhZSpsDAJASJ-iAzd8KtdMByp_j9d9lo</t>
+  </si>
+  <si>
+    <t>881322850</t>
+  </si>
+  <si>
+    <t>881322852</t>
+  </si>
+  <si>
+    <t>881322853</t>
+  </si>
+  <si>
+    <t>881340060</t>
+  </si>
+  <si>
+    <t>881340090</t>
+  </si>
+  <si>
+    <t>881340190</t>
+  </si>
+  <si>
+    <t>881340390</t>
+  </si>
+  <si>
+    <t>881343890</t>
+  </si>
+  <si>
+    <t>881343920</t>
+  </si>
+  <si>
+    <t>881343930</t>
+  </si>
+  <si>
+    <t>881343940</t>
+  </si>
+  <si>
+    <t>881343960</t>
+  </si>
+  <si>
+    <t>881343980</t>
+  </si>
+  <si>
+    <t>881343990</t>
+  </si>
+  <si>
+    <t>881344204</t>
+  </si>
+  <si>
+    <t>881344460</t>
+  </si>
+  <si>
+    <t>881344500</t>
+  </si>
+  <si>
+    <t>881344501</t>
+  </si>
+  <si>
+    <t>881344520</t>
+  </si>
+  <si>
+    <t>881344540</t>
+  </si>
+  <si>
+    <t>881345000</t>
+  </si>
+  <si>
+    <t>881345001</t>
+  </si>
+  <si>
+    <t>881345002</t>
+  </si>
+  <si>
+    <t>881345003</t>
+  </si>
+  <si>
+    <t>881345010</t>
+  </si>
+  <si>
+    <t>881345030</t>
+  </si>
+  <si>
+    <t>881345031</t>
+  </si>
+  <si>
+    <t>BRDR (A&amp;O)</t>
+  </si>
+  <si>
+    <t>BRDR(A&amp;O)</t>
+  </si>
+  <si>
+    <t>P023006 (BRDR A&amp;O)</t>
+  </si>
+  <si>
+    <t>P040052 BRDR(A&amp;O) PD-6D</t>
+  </si>
+  <si>
+    <t>P079551 BRDR A&amp;O PD-8D</t>
+  </si>
+  <si>
+    <t>P022836 BRDR A&amp;O LES-5</t>
+  </si>
+  <si>
+    <t>P022845 BRDR(A&amp;O) LES-9</t>
+  </si>
+  <si>
+    <t>P035791 BRDR (A&amp;O) LES-16</t>
+  </si>
+  <si>
+    <t>P055045 BRDR(A&amp;O) BS-5</t>
+  </si>
+  <si>
+    <t>P022847 BRDR (A&amp;O) LES-9</t>
+  </si>
+  <si>
+    <t>P022857 BRDR A&amp;O LES-14</t>
+  </si>
+  <si>
+    <t>P022858 BRDR (A&amp;O) LES-14</t>
+  </si>
+  <si>
+    <t>P022862 BRDR(A&amp;O)LES-16</t>
+  </si>
+  <si>
+    <t>P022865 BRDR A&amp;O LES-18</t>
+  </si>
+  <si>
+    <t>P022866 BRDR(A&amp;O) LES-20</t>
+  </si>
+  <si>
+    <t>P103569 BRDR(A&amp;O) LES-24</t>
+  </si>
+  <si>
+    <t>P056542 BRDR (A&amp;O) LES-14</t>
+  </si>
+  <si>
+    <t>P022844 BRDR(A&amp;O) LES-9</t>
+  </si>
+  <si>
+    <t>P036797 BRDR (A&amp;O) LES-12</t>
+  </si>
+  <si>
+    <t>P022849 BRDR (A&amp;O) LES-12</t>
+  </si>
+  <si>
+    <t>P035129 BRDR) A&amp;O LES-14</t>
+  </si>
+  <si>
+    <t>P035128 BRDR (A&amp;O) LES-16</t>
+  </si>
+  <si>
+    <t>P033645 BRDR (A&amp;O) LES-5</t>
+  </si>
+  <si>
+    <t>P022840 BRDR A&amp;O LES-6</t>
+  </si>
+  <si>
+    <t>P022842 BRDR (A&amp;O) LES-7</t>
+  </si>
+  <si>
+    <t>P035160 BRDR(A&amp;O) LES-6</t>
+  </si>
+  <si>
+    <t>P022846 BRDR(A&amp;O) LES-9</t>
+  </si>
+  <si>
+    <t>P033644 BRDR (A&amp;O) LES-14</t>
+  </si>
+  <si>
+    <t>P022864 BRDR A&amp;O LES-16</t>
+  </si>
+  <si>
+    <t>P022862 BRDR(A&amp;O) LES-16</t>
+  </si>
+  <si>
+    <t>CARAT NEDERLAND B.V</t>
+  </si>
+  <si>
+    <t>CAB3502000</t>
+  </si>
+  <si>
+    <t>CAB3504000</t>
+  </si>
+  <si>
+    <t>CAM3502000</t>
+  </si>
+  <si>
+    <t>CAM3504000</t>
+  </si>
+  <si>
+    <t>CAM4004000</t>
+  </si>
+  <si>
+    <t>CAM5004000</t>
+  </si>
+  <si>
+    <t>CER3504000ZZ</t>
+  </si>
+  <si>
+    <t>CER3504000</t>
+  </si>
+  <si>
+    <t>CNAM300500</t>
+  </si>
+  <si>
+    <t>CNAM350400</t>
+  </si>
+  <si>
+    <t>CNAM400400</t>
+  </si>
+  <si>
+    <t>CNAM500400</t>
+  </si>
+  <si>
+    <t>CNCB300500</t>
+  </si>
+  <si>
+    <t>CNCM450400</t>
+  </si>
+  <si>
+    <t>CNCM500400</t>
+  </si>
+  <si>
+    <t>CNEB500400</t>
+  </si>
+  <si>
+    <t>CNEC350400</t>
+  </si>
+  <si>
+    <t>CNEM300500</t>
+  </si>
+  <si>
+    <t>CNEM350400</t>
+  </si>
+  <si>
+    <t>CNEM400400</t>
+  </si>
+  <si>
+    <t>CNEM450400</t>
+  </si>
+  <si>
+    <t>CNEM500400</t>
+  </si>
+  <si>
+    <t>CNEM600400</t>
+  </si>
+  <si>
+    <t>CRB3002000</t>
+  </si>
+  <si>
+    <t>CRB3502000</t>
+  </si>
+  <si>
+    <t>CRB3504000</t>
+  </si>
+  <si>
+    <t>CRB4002000</t>
+  </si>
+  <si>
+    <t>CRB4004000</t>
+  </si>
+  <si>
+    <t>CRB4504000</t>
+  </si>
+  <si>
+    <t>CRB5004000</t>
+  </si>
+  <si>
+    <t>CRB6004000</t>
+  </si>
+  <si>
+    <t>CRBM350200</t>
+  </si>
+  <si>
+    <t>CRBM500400</t>
+  </si>
+  <si>
+    <t>CRBM600400</t>
+  </si>
+  <si>
+    <t>CRSA330000</t>
+  </si>
+  <si>
+    <t>CRSC330000</t>
+  </si>
+  <si>
+    <t>CSM1253000</t>
+  </si>
+  <si>
+    <t>CSM1403000</t>
+  </si>
+  <si>
+    <t>CSM1509000</t>
+  </si>
+  <si>
+    <t>CSM1803000</t>
+  </si>
+  <si>
+    <t>CSM2303000</t>
+  </si>
+  <si>
+    <t>CUS1253000</t>
+  </si>
+  <si>
+    <t>P134331 PLES-14</t>
+  </si>
+  <si>
+    <t>P134332 PLES-14</t>
+  </si>
+  <si>
+    <t>P113107 PLES-14</t>
+  </si>
+  <si>
+    <t>P134042 PLES-14</t>
+  </si>
+  <si>
+    <t>P134369 PLES-14</t>
+  </si>
+  <si>
+    <t>P136625 PLES-14</t>
+  </si>
+  <si>
+    <t>P134046 PLES-16</t>
+  </si>
+  <si>
+    <t>P112406 PLES-20</t>
+  </si>
+  <si>
+    <t>P134048 PLES-20</t>
+  </si>
+  <si>
+    <t>P135180 LES-14</t>
+  </si>
+  <si>
+    <t>P134370 LES-14</t>
+  </si>
+  <si>
+    <t>P134054 PLES-12</t>
+  </si>
+  <si>
+    <t>P134055 PLES-14</t>
+  </si>
+  <si>
+    <t>P134057 PLES-16</t>
+  </si>
+  <si>
+    <t>P134059 PLES-20</t>
+  </si>
+  <si>
+    <t>P112315 PLES-12</t>
+  </si>
+  <si>
+    <t>P134359 PLES-12</t>
+  </si>
+  <si>
+    <t>P112218 PLES-18</t>
+  </si>
+  <si>
+    <t>P134363 PLES-18</t>
+  </si>
+  <si>
+    <t>P112220 PLES-20</t>
+  </si>
+  <si>
+    <t>P134368 PLES-20</t>
+  </si>
+  <si>
+    <t>P119816 LES 14</t>
+  </si>
+  <si>
+    <t>P112526 PLES-12</t>
+  </si>
+  <si>
+    <t>P134373 PLES-12</t>
+  </si>
+  <si>
+    <t>P134374 PLES-14</t>
+  </si>
+  <si>
+    <t>P134376 PLES-16</t>
+  </si>
+  <si>
+    <t>P134377 PLES-18</t>
+  </si>
+  <si>
+    <t>P134378 PLES-20</t>
+  </si>
+  <si>
+    <t>P134379 PLES-24</t>
+  </si>
+  <si>
+    <t>P134380 PLES-12</t>
+  </si>
+  <si>
+    <t>P112201 PLES-14</t>
+  </si>
+  <si>
+    <t>P134381 PLES-14</t>
+  </si>
+  <si>
+    <t>P112323 PLES-14</t>
+  </si>
+  <si>
+    <t>P134383 PLES-16</t>
+  </si>
+  <si>
+    <t>P112324 PLES-16</t>
+  </si>
+  <si>
+    <t>P134384 PLES-18</t>
+  </si>
+  <si>
+    <t>P112232 PLES-24</t>
+  </si>
+  <si>
+    <t>P134385 PLES-20</t>
+  </si>
+  <si>
+    <t>P112050 PLES-24</t>
+  </si>
+  <si>
+    <t>P112531 PLES-14</t>
+  </si>
+  <si>
+    <t>P112219 PLES-20</t>
+  </si>
+  <si>
+    <t>P134392 PLES-24</t>
+  </si>
+  <si>
+    <t>P134393 PLES-13</t>
+  </si>
+  <si>
+    <t>P134394 PLES-13</t>
+  </si>
+  <si>
+    <t>P134395 PLES-5</t>
+  </si>
+  <si>
+    <t>P134396 PLES-5.5</t>
+  </si>
+  <si>
+    <t>P112544 PLES-6</t>
+  </si>
+  <si>
+    <t>P134397 PLES-6</t>
+  </si>
+  <si>
+    <t>P135973 PLES-7</t>
+  </si>
+  <si>
+    <t>P112202 PLES-9</t>
+  </si>
+  <si>
+    <t>P134398 PLES-9</t>
+  </si>
+  <si>
+    <t>P126583 EDS-510</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCeX-66k-UIRIVGZFLNah6hAVomnuvTlncwQ3mbCfSgCz4</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAW9Gu4qEgrTLIIDoMPMYlrAeRwpt6Mi4Z0r2UQ6IHz6JM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDZC-1kaRCcT5LUyScqhZ4YAayJaMgWK5ZRpXqlbGfx_sw</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBX3W92wtouTLFyvuXh3kbdAWKpRHvaDhpRmHizNaz4Qxg</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAeR6Gk1VRfQ5JXDcDhZ0-MAWElXkSEk8TYWvONu8e9CCQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDmoL8Uv_qAQJmZcPz711pdAfdIRLCPdkGlK1BaFiU6Nww</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBNHWd-MZ9eRo9cjD-S3Y7uAf-V2xn2mv3NIzquxEhYmgY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDfQR-UvAtvSY2dFVDb6eyPAdGmKXD4VMg0BktuIsyPGvE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDPpLjeiGwVTJqyJWZqOo56AaWIMXK_-SJs1kN_-coDJdQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDM7i9M6tPGSpqo-ua5b35EAYgS1OzQhF5Lhde84Xc6WGU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA6JQXg7DVAQL9vPQiZ1IhqAXEPewiaCqnPtYrR0pAVI5o</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQC5JATnJDPZRren1tcJFrRmAU4KYZJrT-foQ3lTLXHUwjk</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDjUTS10FHyT5yib0QLbHbxAbrub217ynz5Of3jleicIzs</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDYBeFn8th7SJeJM_oXfNGgASefNDb_gBPdcMgbvZz70DU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQARP4Wdf-sdTrQdaIWn8TKJAcuQ3shtmJj25w--VSQike4</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDOG3QJwTbqQL6-vhhaz3IAASHjnO-TdhBzQna3NA4N1o8</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBeMyyoozHJSJRfOjMJLK8IAYSmpVVijXshnc_sD_oVqNU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDiB95f9xLYSoR9Q4DY-SuoAfcnzHxIzpIAXZAsnxfmt94</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD9nz_DmGd5QIt5OT9imQixARaFqJ7nxkuZy0eW9QOfFkU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCwXO3V7TcUT4oVABKJeV_yAatKfpwbOyqiej9r3sjcE6c</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAaFNMZTLh7QrtxvfQXTyx8AUK0JrhTBmSodpYCoz_6SxM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBjr3cM04D7TpS9XuaTi9cjAQKTazDCEZ6c0O4rt3V6P80</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDHS45qPNCNQKEj3xfCGAHaAXh0HaQhhIDNZ0AqCXTNPPw</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAHPK2n42sgQJyoEXyGIgccAVJty1EdOaFcEDCxfVf4o00</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBtB4tBomsQRoJy6iwDx78SAUuB5ddGtU3zNrHqBa6gUkE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCuaHpFbnVmSJv-U9_6jcGCAYc-GM-KwPKiBgmpTWBYvLc</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBL1wI7O2iOQ4TYHcqIasboAUPDZ7ca0PRGLqP-XXK4S8s</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAG5xtmTiMeRpAqZhPr8PjyAX8geVP89Qh2wE2-VCXjbkQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAF3Aj_aOTuQJkALWP9KOQgATrO7AT9CInXQ9HGUsnqW14</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBWczs-xfNQQZBLsmbujyEuAZKQLc-e5ycuDFsPCbWr60g</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAIGtr12UHpT47knkNgm6b2ARcFiOhkHhRQDc1YWRI_bvc</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAUKjRnK1fTTobdBYBGrkMHAZx3jMgf50FsMUH07I48jYs</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD5s8EQOEAdT5WZCpIzxUjaATKLiyHZQVG48CZ6l5uLNlU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDylCGel3mvTLKoLqODjPHFAUlNsPS2z3Ss_ic3KPUf6lw</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBoDNu29csCTqnq0DEori_hAVkhf1ISBY3taM6cx_URP0A</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAw3nHO6vhxRo4q738rVYU1AYxYQNpDGLLHMCdcAu8LO0M</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCCe8zQcpYTQ7-f0RqyXN7_AXCLlk8IRP8ooH6UCjXdpfc</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCt8jXh7RzDQ4zz9R7ZAInCAZy3VL5qcfuoSsnqgsCZAvk</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBpG0Wjml_tQKl9bTd5koyWASLT545kOYixKF56xCcvf98</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDkqHFBYOgdQJpvKm-UDDMHAUbGLzzb0qZ4mdYIN_lSyis</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAVeOhfxTfiTY0mvpZbZkuDAeF3cw58fsMYAxShbsMrk90</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBVjDTBnE12RLmG2CqnpcG4AQotPfVWNF-8XULjsAHjiL8</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBc9NCrxpyBSaSnPc7j3KvYAXBBq7kv0O9ybPCv6QR8_lE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAUBH2s5CaURa-7FYMnQ-gHAQ-Sh4iXDcdP-n8VYLUTWxA</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD-YxuSog7xQL52E_Z52WMpAWPBwk5AetCcTIu1u_X04Nk</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCXhMDmKJ_OR4VTfHvtW5T0AY7sYCcfZOFkc2OQ1CGFHoo</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDAEyiAmIykQr_u-Ucg1YX7AWyBZdvZv1g0UwOvQNk9OLM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAo7eTLrEVkSr-p0s8eBvEWAd2UfiLKolnB_fEJdPRe__I</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCDvMXj5lY_Sr48ISAgS3mfAc5Zcklr6yjEbHWQ-UGPfyg</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCLq5y83ZGjQKzA2lnsnfheAUpmX03bgi-vHLEAk30y55U</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCSPfg13Ym8TJDXze03yt2CAZ0dLDa3UGfGg1-WmqfnpuM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBPPAoqvzwfR6lH7ebdN0O_Aa0KAd-0-wFO8Ih2b2og7-A</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAhBNrOViAOTJNOA1lVHH_LAX0rj-b99zbpa72Dy9gESvA</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA3S_vT-QGzQ54wGYN2oTd-AfeYTsFoVJLmo_jVP3GcYJc</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBEf5F4cvEiT5mnhZh1DiiMAQsAxGV_-5dvgjagtSHSUvM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA8DhK2uKH3So0W_Ot1Lk2WAabUZ-nY4DYuJ0BTVcjc1Po</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAWwJSF0PBzT4YWtuhS_hWKAf-eMbzyT3Yw3tQuHxt-QHU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBXySYileONQohq3fRFvMYgARIk1aK6eR0ZeRh9xoCKlXc</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBmLdLH8vgCRKWxIJrBRm1SAZvNUmhEsMnIlKvA1G0_wMQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDUNUHWLSHARKvFg6yj_OikAaD4vJof_jlR9_P0Iagj3wE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDrTPDmghLrQZ9JhOnEI41WAdO-JwYik403UyqzElxUABc</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCxivKEFSRQQbOY6y1U6wEZAbUcxdj-DWhn1FC373g-BmI</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCrC8Iid1fCQpZAWHp8DaLKAbSmq4VaTQ0rTVDIf4RP3T0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDnzfvw53SlTK9uR53hCf3jAYllbbxZ4norbuzjVbDICH8</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCREU_OFMksS5pyGeKBV3TSAQ61t2Vu7p1EwFRh3CzLtR4</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAHEwCx9rfOSLPvUxDVVv8rATDwkE7ECsoqREl0FHXmqq0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBlqyIIhGJrTb3LjacnQcOzAbb6bVyic6g4UNv35DeFYMM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAr38l3mNaoTbCjMmcNxAMsAUxN7DnGJ3Iv9G8xKu-fNyo</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQClB7QDrgfWTpjBUSGeSLsaAW1jXVplgj5wgtG8P8x0PZ0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDDfwO7DUz4RIufl8fuYURFAT_sk5rBrDDmXSwoCrX9-go</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBRsPRcaw6KT40leF0qWVbAAQQp3Be1y_GGh_QcEU3IO8U</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCEynZ1pMKaT6onk11OyebeAbdWDbEF32J-Qk_vAvbk6UE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD2SNZtsbcMR6Jfrop9CrhDAYOsYcOHjucnjR37AJYyeBU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDGj2WkJ3cESrdRq96-kB0mAVYqnWQO9wlCFsQqE_Z6M00</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA9M-grLq1rSJxDVCD8ikOGAbzBaQxDrdZOaD-ZDelvKr0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAYbXr31UErRJVfPCjoKfbQAaA38KBHjT2YK61AvKEZRIE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDN9WAS0DwzRaMHBulaRdvlAZduPmH5XfS_yChVkSZeX_w</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD8jTaCTgjMSKS_JlnKLdZMAd7H29lTOHy5wiVfzzpR7AQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAEhgyhuQ3IT5c1w94mI8hNAcIQljv4VvCb5sbGopYRYe8</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBFhKuvglziS5Z4Qt9XqNIvAYh1SljWEEi5_-JMTvPZG4k</t>
+  </si>
+  <si>
+    <t>WACKER NEUSON</t>
+  </si>
+  <si>
+    <t>5100000522</t>
+  </si>
+  <si>
+    <t>P119304 LES-14</t>
+  </si>
+  <si>
+    <t>5100000525</t>
+  </si>
+  <si>
+    <t>P119763 LES-14</t>
+  </si>
+  <si>
+    <t>5100000526</t>
+  </si>
+  <si>
+    <t>P119783 LES-16</t>
+  </si>
+  <si>
+    <t>5100000531</t>
+  </si>
+  <si>
+    <t>P119765 LES-14</t>
+  </si>
+  <si>
+    <t>5100000537</t>
+  </si>
+  <si>
+    <t>P119766 LES-14</t>
+  </si>
+  <si>
+    <t>5100000539</t>
+  </si>
+  <si>
+    <t>P123093 LES-12</t>
+  </si>
+  <si>
+    <t>5100000540</t>
+  </si>
+  <si>
+    <t>P119755 LES-14</t>
+  </si>
+  <si>
+    <t>5100000544</t>
+  </si>
+  <si>
+    <t>P119803 LES-16</t>
+  </si>
+  <si>
+    <t>5100000547</t>
+  </si>
+  <si>
+    <t>P119756 LES-18</t>
+  </si>
+  <si>
+    <t>5100000548</t>
+  </si>
+  <si>
+    <t>P119769 LES-20</t>
+  </si>
+  <si>
+    <t>5100000552</t>
+  </si>
+  <si>
+    <t>P119770 LES-14</t>
+  </si>
+  <si>
+    <t>5100000553</t>
+  </si>
+  <si>
+    <t>P119771 LES-16</t>
+  </si>
+  <si>
+    <t>5100000554</t>
+  </si>
+  <si>
+    <t>P119781 LES-18</t>
+  </si>
+  <si>
+    <t>5100000569</t>
+  </si>
+  <si>
+    <t>P119806 LES-14</t>
+  </si>
+  <si>
+    <t>5100000571</t>
+  </si>
+  <si>
+    <t>P119757  LES-18</t>
+  </si>
+  <si>
+    <t>5100000572</t>
+  </si>
+  <si>
+    <t>P119786 LES-20</t>
+  </si>
+  <si>
+    <t>5100000574</t>
+  </si>
+  <si>
+    <t>P123773 LES-16</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQC7o8Cslm35R6o4rmWbOKQOAcdgBV2PVdWkMl4fjJqS_SM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA6zihtycJNT58RYA_Ju0QxAYTsjUqTdcHS41v4Idf9eB0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCLdzLH2WRzSpRppTfeKvBKAW06HLZ-Rb_S2W2ovdk1CaI</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBqPfdcoCvDQqDYxlQ2JEXgASzcMlFhDEnkNTosvIAsEtQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBIf1bPuMF4S6Fefk092hhzASMBN1hKPYRlyON5myEsiHU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDcol5LpUQRQrFWUQ3UmXD-AaS94u4ixCm-sbkzLqj2DiE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCIF143FlsDTomLNiPTgXLtAWIQP0NHB6z_scO8zIbVdJw</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCZ8oa8JtrrTp0RCKuzFSsSARqF4vN-CQFT2mjUTSh_V68</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDuXBexNxCjTrUbZDQ8J-yEAegVszlDiczH6nq8EOE5qfQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBb4OlV4tijTLFpaZteRstfAW1eePf2j_4SCXP7_4fzQ-U</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCGMsnAryoNQqXtDoC-HjiSAbdMCe0p_9fgRRZyj5-ifvM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAONfCaHMHfQKiy-iSLPBonATYnYkYOaADgjsaqncU2Sms</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDhN66uZaNJTLXUalNQ7DxoAeWDS8YY3FDbm0AGj5_ZX0w</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCVDrsTzU9aSJVNP8Z2qIKTAU9Sor8YRN8FRzFd_UZ90yY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDhDZ22hW_GS7wzE1yckM-CAbpg5ZmH0Q99cRFoUyZpTwA</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBR1uOwa9RvR48Lp51_A9XJAS9U9jbnWNVMV9lieg_rl7k</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAJkyQIpQq4QYgSdnZk7BFlAVKwCUwQSrHIluAaB_x7GYc</t>
   </si>
 </sst>
 </file>
@@ -953,7 +2912,7 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -965,7 +2924,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
   <cellStyles count="43">
@@ -1343,7 +3301,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F250"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="21.875" style="1" customWidth="1"/>
@@ -1372,13 +3330,13 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="C2" s="5"/>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="s">
@@ -1386,13 +3344,13 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="6"/>
+      <c r="C3" s="5"/>
       <c r="D3" s="3"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="s">
@@ -1400,13 +3358,13 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="3"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="s">
@@ -1414,13 +3372,13 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="3"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
@@ -1428,13 +3386,13 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="5"/>
       <c r="D6" s="3"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
@@ -1442,13 +3400,13 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="3"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
@@ -1456,13 +3414,13 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="3"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4" t="s">
@@ -1470,13 +3428,13 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="6"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="3"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
@@ -1484,13 +3442,13 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5"/>
       <c r="D10" s="3"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4" t="s">
@@ -1498,13 +3456,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="6"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="3"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="s">
@@ -1512,13 +3470,13 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="4" t="s">
@@ -1526,769 +3484,3221 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="6"/>
+      <c r="C13" s="5"/>
       <c r="F13" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5"/>
       <c r="F14" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="5"/>
       <c r="F15" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="5"/>
       <c r="F16" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="6"/>
+      <c r="C17" s="5"/>
       <c r="F17" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5"/>
       <c r="F18" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="6"/>
+      <c r="C19" s="5"/>
       <c r="F19" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="5"/>
       <c r="F20" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="6"/>
+      <c r="C21" s="5"/>
       <c r="F21" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="6"/>
+      <c r="C22" s="5"/>
       <c r="F22" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="6"/>
+      <c r="C23" s="5"/>
       <c r="F23" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5"/>
       <c r="F24" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="6"/>
+      <c r="C25" s="5"/>
       <c r="F25" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5"/>
       <c r="F26" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="6"/>
+      <c r="C27" s="5"/>
       <c r="F27" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5"/>
       <c r="F28" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="6"/>
+      <c r="C29" s="5"/>
       <c r="F29" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5"/>
       <c r="F30" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="6"/>
+      <c r="C31" s="5"/>
       <c r="F31" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C32" s="6"/>
+      <c r="C32" s="5"/>
       <c r="F32" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="6"/>
+      <c r="C33" s="5"/>
       <c r="F33" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="F34" s="5"/>
+      <c r="A34" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="F34" s="4" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="F35" s="5"/>
+      <c r="A35" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="F35" s="4" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="F36" s="5"/>
+      <c r="A36" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="F36" s="4" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="F37" s="5"/>
+      <c r="A37" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="5"/>
+      <c r="F37" s="4" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="F38" s="5"/>
+      <c r="A38" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="5"/>
+      <c r="F38" s="4" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="F39" s="5"/>
+      <c r="A39" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" s="5"/>
+      <c r="F39" s="4" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="F40" s="5"/>
+      <c r="A40" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="5"/>
+      <c r="F40" s="4" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="F41" s="5"/>
+      <c r="A41" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="F41" s="4" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="F42" s="5"/>
+      <c r="A42" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="F42" s="4" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="F43" s="5"/>
+      <c r="A43" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C43" s="5"/>
+      <c r="F43" s="4" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="F44" s="5"/>
+      <c r="A44" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="F44" s="4" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="F45" s="5"/>
+      <c r="A45" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="F45" s="4" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="F46" s="5"/>
+      <c r="A46" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C46" s="5"/>
+      <c r="F46" s="4" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="F47" s="5"/>
+      <c r="A47" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C47" s="5"/>
+      <c r="F47" s="4" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="F48" s="5"/>
+      <c r="A48" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" s="5"/>
+      <c r="F48" s="4" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="F49" s="5"/>
+      <c r="A49" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C49" s="5"/>
+      <c r="F49" s="4" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="F50" s="5"/>
+      <c r="A50" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" s="5"/>
+      <c r="F50" s="4" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="F51" s="5"/>
+      <c r="A51" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C51" s="5"/>
+      <c r="F51" s="4" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="F52" s="5"/>
+      <c r="A52" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C52" s="5"/>
+      <c r="F52" s="4" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="F53" s="5"/>
+      <c r="A53" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C53" s="5"/>
+      <c r="F53" s="4" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="F54" s="5"/>
+      <c r="A54" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" s="5"/>
+      <c r="F54" s="4" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="F55" s="5"/>
+      <c r="A55" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C55" s="5"/>
+      <c r="F55" s="4" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="F56" s="5"/>
+      <c r="A56" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C56" s="5"/>
+      <c r="F56" s="4" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="F57" s="5"/>
+      <c r="A57" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C57" s="5"/>
+      <c r="F57" s="4" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="F58" s="5"/>
+      <c r="A58" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C58" s="5"/>
+      <c r="F58" s="4" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="F59" s="5"/>
+      <c r="A59" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C59" s="5"/>
+      <c r="F59" s="4" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="F60" s="5"/>
+      <c r="A60" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C60" s="5"/>
+      <c r="F60" s="4" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="F61" s="5"/>
+      <c r="A61" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C61" s="5"/>
+      <c r="F61" s="4" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="F62" s="5"/>
+      <c r="A62" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C62" s="5"/>
+      <c r="F62" s="4" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="F63" s="5"/>
+      <c r="A63" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C63" s="5"/>
+      <c r="F63" s="4" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="F64" s="5"/>
+      <c r="A64" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C64" s="5"/>
+      <c r="F64" s="4" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="F65" s="5"/>
+      <c r="A65" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C65" s="5"/>
+      <c r="F65" s="4" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="F66" s="5"/>
+      <c r="A66" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C66" s="5"/>
+      <c r="F66" s="4" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="F67" s="5"/>
+      <c r="A67" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C67" s="5"/>
+      <c r="F67" s="4" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="F68" s="5"/>
+      <c r="A68" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C68" s="5"/>
+      <c r="F68" s="4" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="F69" s="5"/>
+      <c r="A69" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C69" s="5"/>
+      <c r="F69" s="4" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="F70" s="5"/>
+      <c r="A70" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C70" s="5"/>
+      <c r="F70" s="4" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="F71" s="5"/>
+      <c r="A71" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C71" s="5"/>
+      <c r="F71" s="4" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="F72" s="5"/>
+      <c r="A72" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C72" s="5"/>
+      <c r="F72" s="4" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="F73" s="5"/>
+      <c r="A73" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C73" s="5"/>
+      <c r="F73" s="4" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="F74" s="5"/>
+      <c r="A74" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B74" s="3"/>
+      <c r="C74" s="5"/>
+      <c r="F74" s="4" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="F75" s="5"/>
+      <c r="A75" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="5"/>
+      <c r="F75" s="4" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="F76" s="5"/>
+      <c r="A76" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B76" s="3"/>
+      <c r="C76" s="5"/>
+      <c r="F76" s="4" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="F77" s="5"/>
+      <c r="A77" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B77" s="3"/>
+      <c r="C77" s="5"/>
+      <c r="F77" s="4" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="F78" s="5"/>
+      <c r="A78" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B78" s="3"/>
+      <c r="C78" s="5"/>
+      <c r="F78" s="4" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="F79" s="5"/>
+      <c r="A79" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B79" s="3"/>
+      <c r="C79" s="5"/>
+      <c r="E79" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>395</v>
+      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="F80" s="5"/>
+      <c r="A80" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="5"/>
+      <c r="E80" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="F81" s="5"/>
+      <c r="A81" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C81" s="5"/>
+      <c r="E81" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="F82" s="5"/>
+      <c r="A82" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C82" s="5"/>
+      <c r="E82" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="F83" s="5"/>
+      <c r="A83" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C83" s="5"/>
+      <c r="E83" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>399</v>
+      </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="F84" s="5"/>
+      <c r="A84" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C84" s="5"/>
+      <c r="E84" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="F85" s="5"/>
+      <c r="A85" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C85" s="5"/>
+      <c r="E85" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>401</v>
+      </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="F86" s="5"/>
+      <c r="A86" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C86" s="5"/>
+      <c r="E86" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="6"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6"/>
-      <c r="F87" s="5"/>
+      <c r="A87" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C87" s="5"/>
+      <c r="E87" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="F88" s="5"/>
+      <c r="A88" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C88" s="5"/>
+      <c r="E88" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="F89" s="5"/>
+      <c r="A89" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C89" s="5"/>
+      <c r="E89" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>405</v>
+      </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="F90" s="5"/>
+      <c r="A90" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C90" s="5"/>
+      <c r="E90" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="6"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6"/>
-      <c r="F91" s="5"/>
+      <c r="A91" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C91" s="5"/>
+      <c r="E91" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="F92" s="5"/>
+      <c r="A92" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C92" s="5"/>
+      <c r="E92" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="F93" s="5"/>
+      <c r="A93" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B93" s="3"/>
+      <c r="C93" s="5"/>
+      <c r="E93" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="F94" s="5"/>
+      <c r="A94" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B94" s="3"/>
+      <c r="C94" s="5"/>
+      <c r="E94" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="F95" s="5"/>
+      <c r="A95" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C95" s="5"/>
+      <c r="E95" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="F96" s="5"/>
+      <c r="A96" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C96" s="5"/>
+      <c r="E96" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="F97" s="5"/>
+      <c r="A97" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C97" s="5"/>
+      <c r="E97" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>413</v>
+      </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
-      <c r="F98" s="5"/>
+      <c r="A98" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C98" s="5"/>
+      <c r="E98" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="F99" s="5"/>
+      <c r="A99" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C99" s="5"/>
+      <c r="E99" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="F100" s="5"/>
+      <c r="A100" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C100" s="5"/>
+      <c r="E100" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="F101" s="5"/>
+      <c r="A101" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C101" s="5"/>
+      <c r="E101" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="F102" s="5"/>
+      <c r="A102" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C102" s="5"/>
+      <c r="E102" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="F103" s="5"/>
+      <c r="A103" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B103" s="3"/>
+      <c r="C103" s="5"/>
+      <c r="E103" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="F104" s="5"/>
+      <c r="A104" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C104" s="5"/>
+      <c r="E104" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="F105" s="5"/>
+      <c r="A105" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C105" s="5"/>
+      <c r="E105" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>421</v>
+      </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6"/>
-      <c r="C106" s="6"/>
-      <c r="F106" s="5"/>
+      <c r="A106" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C106" s="5"/>
+      <c r="E106" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6"/>
-      <c r="F107" s="5"/>
+      <c r="A107" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C107" s="5"/>
+      <c r="E107" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
-      <c r="C108" s="6"/>
-      <c r="F108" s="5"/>
+      <c r="A108" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C108" s="5"/>
+      <c r="E108" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="F109" s="5"/>
+      <c r="A109" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C109" s="5"/>
+      <c r="E109" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="F110" s="5"/>
+      <c r="A110" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C110" s="5"/>
+      <c r="E110" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
-      <c r="C111" s="6"/>
-      <c r="F111" s="5"/>
+      <c r="A111" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C111" s="5"/>
+      <c r="E111" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
-      <c r="C112" s="6"/>
-      <c r="F112" s="5"/>
+      <c r="A112" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C112" s="5"/>
+      <c r="E112" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="F113" s="5"/>
+      <c r="A113" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C113" s="5"/>
+      <c r="E113" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
-      <c r="C114" s="6"/>
-      <c r="F114" s="5"/>
+      <c r="A114" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C114" s="5"/>
+      <c r="E114" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
-      <c r="C115" s="6"/>
-      <c r="F115" s="5"/>
+      <c r="A115" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C115" s="5"/>
+      <c r="E115" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
-      <c r="C116" s="6"/>
-      <c r="F116" s="5"/>
+      <c r="A116" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C116" s="5"/>
+      <c r="E116" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="6"/>
-      <c r="F117" s="5"/>
+      <c r="A117" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C117" s="5"/>
+      <c r="E117" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F118" s="5"/>
+      <c r="A118" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F119" s="5"/>
+      <c r="A119" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B119" s="3"/>
+      <c r="E119" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F120" s="5"/>
+      <c r="A120" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B120" s="3"/>
+      <c r="E120" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A188" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A194" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A195" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A196" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A197" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A198" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A199" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A200" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A201" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A202" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A203" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A204" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A205" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A206" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F206" s="4" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A208" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F208" s="4" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F209" s="4" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A210" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A211" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F211" s="4" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A212" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A213" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A214" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A215" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A216" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A217" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F217" s="4" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A218" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A219" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F219" s="4" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A220" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F220" s="4" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A221" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F221" s="4" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A222" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A223" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F223" s="4" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A224" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F224" s="4" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A225" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F225" s="4" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A226" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A227" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F227" s="4" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A228" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F228" s="4" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A229" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F229" s="4" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A230" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F230" s="4" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A231" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F231" s="4" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A232" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A233" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F233" s="4" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A234" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F234" s="4" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A235" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F235" s="4" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A236" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A237" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A238" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F238" s="4" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A239" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A240" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A241" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A242" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F242" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A243" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F243" s="4" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A244" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F244" s="4" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A245" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F245" s="4" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A246" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F246" s="4" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A247" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F247" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A248" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F248" s="4" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A249" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F249" s="4" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A250" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F250" s="4" t="s">
+        <v>753</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -2325,8 +6735,225 @@
     <hyperlink ref="F31" r:id="rId30" xr:uid="{1523BD83-3475-4F82-9FA4-7F71B4441700}"/>
     <hyperlink ref="F32" r:id="rId31" xr:uid="{D728978A-A248-4D67-80B0-20544CFFBFA6}"/>
     <hyperlink ref="F33" r:id="rId32" xr:uid="{25B7467E-E690-42A9-BC9A-6A48DBAB8914}"/>
+    <hyperlink ref="F34" r:id="rId33" xr:uid="{2F48726D-DE6A-4098-BE7D-5BACCC8FC40A}"/>
+    <hyperlink ref="F35" r:id="rId34" xr:uid="{F3DC5606-9A2B-4B27-888E-2418DBD63197}"/>
+    <hyperlink ref="F36" r:id="rId35" xr:uid="{1A77C4B1-3EBF-4996-8BA5-54115DCC6DB4}"/>
+    <hyperlink ref="F37" r:id="rId36" xr:uid="{DB555C1A-23E1-4927-9647-7C6892E4C9C7}"/>
+    <hyperlink ref="F38" r:id="rId37" xr:uid="{33661F8A-1BC9-417D-99B3-DC93198874DE}"/>
+    <hyperlink ref="F39" r:id="rId38" xr:uid="{192DE853-AD34-43CA-A63F-E85114AD4EA0}"/>
+    <hyperlink ref="F40" r:id="rId39" xr:uid="{120E2455-BB40-4E29-A234-A4B7E792FE52}"/>
+    <hyperlink ref="F41" r:id="rId40" xr:uid="{1443E8F9-88EF-4C2B-A276-23E530539E9E}"/>
+    <hyperlink ref="F42" r:id="rId41" xr:uid="{E7CEA036-13F4-4AAC-A555-2FFE21E0C2B8}"/>
+    <hyperlink ref="F43" r:id="rId42" xr:uid="{92496332-5A82-488E-A37E-5592FCE49A81}"/>
+    <hyperlink ref="F44" r:id="rId43" xr:uid="{A0653FC6-F81B-47CA-A38B-BB1D7D8780AB}"/>
+    <hyperlink ref="F45" r:id="rId44" xr:uid="{F5BF4D55-CEE6-4250-9B16-AC2891C0A711}"/>
+    <hyperlink ref="F46" r:id="rId45" xr:uid="{68E21E8B-2406-448E-BB39-B787D1282FA1}"/>
+    <hyperlink ref="F47" r:id="rId46" xr:uid="{C2C55E82-ED9F-4FFA-A073-7DC869302C16}"/>
+    <hyperlink ref="F48" r:id="rId47" xr:uid="{4EAD4B84-80BA-4CC7-BD19-A32B04E8286F}"/>
+    <hyperlink ref="F49" r:id="rId48" xr:uid="{71AC19CA-92E6-49F9-BED3-CA495F366A27}"/>
+    <hyperlink ref="F50" r:id="rId49" xr:uid="{00E6714E-2AC2-46E3-9D9F-9C8DCAFD8C22}"/>
+    <hyperlink ref="F51" r:id="rId50" xr:uid="{AB2C6C29-2033-4459-95EA-6131071555ED}"/>
+    <hyperlink ref="F52" r:id="rId51" xr:uid="{04FD38F5-886B-410E-8338-BE423E77A551}"/>
+    <hyperlink ref="F53" r:id="rId52" xr:uid="{46C219A9-8A37-4A38-8BE2-31449600C9CA}"/>
+    <hyperlink ref="F54" r:id="rId53" xr:uid="{A4FCB636-86E3-402A-87E0-87E9BA4AEB41}"/>
+    <hyperlink ref="F55" r:id="rId54" xr:uid="{D96AABDB-3F6C-4B7E-9065-4389E1536714}"/>
+    <hyperlink ref="F56" r:id="rId55" xr:uid="{775F3009-BB92-4337-B30F-6702A68EFCA3}"/>
+    <hyperlink ref="F57" r:id="rId56" xr:uid="{4052F6BF-CA0D-45FA-B208-BDE51EE65CB4}"/>
+    <hyperlink ref="F58" r:id="rId57" xr:uid="{CCDC01A5-FEA2-4076-85E1-6C44FBD6C90A}"/>
+    <hyperlink ref="F59" r:id="rId58" xr:uid="{D31553ED-97EA-4017-B69C-127C4E539342}"/>
+    <hyperlink ref="F60" r:id="rId59" xr:uid="{A34382CC-3807-4DAD-A391-229E3068D20E}"/>
+    <hyperlink ref="F61" r:id="rId60" xr:uid="{D5D838C4-84B9-4893-8081-FD076E65D42D}"/>
+    <hyperlink ref="F62" r:id="rId61" xr:uid="{372D6C7C-57A1-4E5A-8FCA-C2BD42179B4C}"/>
+    <hyperlink ref="F63" r:id="rId62" xr:uid="{26F4CB51-8E73-4DD6-B36B-7D9E3532FACA}"/>
+    <hyperlink ref="F64" r:id="rId63" xr:uid="{28E3DA9C-8B99-4871-9FD0-8DBA1F52D164}"/>
+    <hyperlink ref="F65" r:id="rId64" xr:uid="{F221B864-0319-4744-8F5C-74DFBBD9ECA7}"/>
+    <hyperlink ref="F66" r:id="rId65" xr:uid="{2D863332-43A9-4835-9018-6C6225BAD913}"/>
+    <hyperlink ref="F67" r:id="rId66" xr:uid="{8ABCCB9C-AB49-4FB0-B2C4-669FD2A169BF}"/>
+    <hyperlink ref="F68" r:id="rId67" xr:uid="{4EB52813-3D3C-4F1F-9712-9A07F774A538}"/>
+    <hyperlink ref="F69" r:id="rId68" xr:uid="{52D9EF13-2183-4310-8C32-B2C6A2C08567}"/>
+    <hyperlink ref="F70" r:id="rId69" xr:uid="{A4411235-2A13-4120-A1DD-E52352CFC475}"/>
+    <hyperlink ref="F71" r:id="rId70" xr:uid="{20112E1E-36A7-49B0-BC59-7AB1EF3FBB2A}"/>
+    <hyperlink ref="F72" r:id="rId71" xr:uid="{4E175341-6D90-4C16-9BD9-DD27F4F88C73}"/>
+    <hyperlink ref="F73" r:id="rId72" xr:uid="{834BAFD9-DA29-4D56-BC7B-97B850C5B365}"/>
+    <hyperlink ref="F74" r:id="rId73" xr:uid="{BD779373-AC8C-41E2-98ED-E8D18BBA663E}"/>
+    <hyperlink ref="F75" r:id="rId74" xr:uid="{24CF6F19-C969-4937-9966-220089144F6B}"/>
+    <hyperlink ref="F76" r:id="rId75" xr:uid="{7EABD7FB-999B-4734-B105-231100FF8189}"/>
+    <hyperlink ref="F77" r:id="rId76" xr:uid="{474F7FAB-D2DA-4694-99EE-DD8310E2F160}"/>
+    <hyperlink ref="F78" r:id="rId77" xr:uid="{8E164687-D84D-4A4D-AE50-E53CD426CA64}"/>
+    <hyperlink ref="F79" r:id="rId78" xr:uid="{57F15978-1279-4A0F-A215-4906CA1FD882}"/>
+    <hyperlink ref="F80" r:id="rId79" xr:uid="{67474A5D-2B34-4EE2-A19E-F5C77A48AD43}"/>
+    <hyperlink ref="F81" r:id="rId80" xr:uid="{1E95D132-2A35-447E-B877-2D34495278B4}"/>
+    <hyperlink ref="F82" r:id="rId81" xr:uid="{D34E7BDD-E93E-4C88-92F5-D432227DE455}"/>
+    <hyperlink ref="F83" r:id="rId82" xr:uid="{C12907DC-6C9E-4977-A538-A3F744F8AA91}"/>
+    <hyperlink ref="F84" r:id="rId83" xr:uid="{B245579F-EA5C-4935-830B-94FC23CDA18F}"/>
+    <hyperlink ref="F85" r:id="rId84" xr:uid="{073D4EE8-9D0C-40B6-9B55-B6B321685ECB}"/>
+    <hyperlink ref="F86" r:id="rId85" xr:uid="{90D65CD6-5064-4291-BBBA-5C4CF34FE6AA}"/>
+    <hyperlink ref="F87" r:id="rId86" xr:uid="{565A4BC8-05C2-4D02-9E36-A525DC8B4371}"/>
+    <hyperlink ref="F88" r:id="rId87" xr:uid="{CAC4DA50-1414-4CF6-910E-17B7F4957564}"/>
+    <hyperlink ref="F89" r:id="rId88" xr:uid="{B0B06E7D-1C7A-4D32-AE4D-3B0F535747CB}"/>
+    <hyperlink ref="F90" r:id="rId89" xr:uid="{79DF45D6-17D0-4232-B827-A280235FCB0C}"/>
+    <hyperlink ref="F91" r:id="rId90" xr:uid="{C60BCBA6-22A3-48C1-BFE2-E3F0ED653959}"/>
+    <hyperlink ref="F92" r:id="rId91" xr:uid="{C853EAE2-A438-476C-90F5-25B420A8A86D}"/>
+    <hyperlink ref="F93" r:id="rId92" xr:uid="{6C82A848-6525-40FB-8ADB-285CE48A1AB7}"/>
+    <hyperlink ref="F94" r:id="rId93" xr:uid="{8EE7636B-FABC-4742-A271-5F728084453A}"/>
+    <hyperlink ref="F95" r:id="rId94" xr:uid="{CD277124-F55B-4777-9862-62815F1551F6}"/>
+    <hyperlink ref="F96" r:id="rId95" xr:uid="{2660453A-EC81-4D4B-BB82-FE2575DD4D08}"/>
+    <hyperlink ref="F97" r:id="rId96" xr:uid="{D6DE224C-3DFC-4DB6-9E72-AED8D135744E}"/>
+    <hyperlink ref="F98" r:id="rId97" xr:uid="{9FE4B37A-FE6D-43DC-9BC1-0674858102FE}"/>
+    <hyperlink ref="F99" r:id="rId98" xr:uid="{79960E9B-8491-4402-A445-650D8E68D557}"/>
+    <hyperlink ref="F100" r:id="rId99" xr:uid="{6AFB45A0-94C5-440F-AC3F-5C0BD165713F}"/>
+    <hyperlink ref="F101" r:id="rId100" xr:uid="{AC182F64-B58D-4649-B586-DD25D6B8AB70}"/>
+    <hyperlink ref="F102" r:id="rId101" xr:uid="{ED0CA76E-024D-4110-92A9-DADE47BFA511}"/>
+    <hyperlink ref="F103" r:id="rId102" xr:uid="{6DCFAB94-BA9F-40A5-A808-75DA2DEFA78B}"/>
+    <hyperlink ref="F104" r:id="rId103" xr:uid="{04A820DE-27A6-4077-A1BC-F1489D91C678}"/>
+    <hyperlink ref="F105" r:id="rId104" xr:uid="{A7FB23AE-9EAF-466D-9C9B-4C63C6E8B587}"/>
+    <hyperlink ref="F106" r:id="rId105" xr:uid="{B2651A48-0C82-421B-8DE0-C278FF60782D}"/>
+    <hyperlink ref="F107" r:id="rId106" xr:uid="{EF79A0C3-F8C3-4ECC-8100-6EE743381321}"/>
+    <hyperlink ref="F108" r:id="rId107" xr:uid="{894CE4A4-1C3B-4B15-991E-70742A09B0A9}"/>
+    <hyperlink ref="F109" r:id="rId108" xr:uid="{673F837F-3E66-41A7-8DFA-55E662A307D5}"/>
+    <hyperlink ref="F110" r:id="rId109" xr:uid="{376798D5-9D4C-439A-95AD-8A2F58E096FA}"/>
+    <hyperlink ref="F111" r:id="rId110" xr:uid="{FCB5C10D-9DF6-4EAD-8A24-8085B2AB1902}"/>
+    <hyperlink ref="F112" r:id="rId111" xr:uid="{6AFE760A-F307-409C-97B0-CDE8A3C59495}"/>
+    <hyperlink ref="F113" r:id="rId112" xr:uid="{54659458-7B70-4EC9-B815-3A16C19E196B}"/>
+    <hyperlink ref="F114" r:id="rId113" xr:uid="{6F053C6C-B3D4-4A41-9217-5FAF77AE6A1A}"/>
+    <hyperlink ref="F115" r:id="rId114" xr:uid="{E576B781-8638-4C92-BD02-951F41BB4664}"/>
+    <hyperlink ref="F116" r:id="rId115" xr:uid="{C67FCD24-E533-4412-A030-8D39A6196BD9}"/>
+    <hyperlink ref="F117" r:id="rId116" xr:uid="{AF98D2CE-21E4-48AA-B0B7-5BFB84D0CD27}"/>
+    <hyperlink ref="F118" r:id="rId117" xr:uid="{1EFBA9D8-6EF6-4E36-AC19-3F1E94FFBD5C}"/>
+    <hyperlink ref="F119" r:id="rId118" xr:uid="{7DFB634A-C633-412E-AB19-B9E741BF15A1}"/>
+    <hyperlink ref="F120" r:id="rId119" xr:uid="{21E9EF23-E7B0-4F90-98E5-BF00B15C699E}"/>
+    <hyperlink ref="F121" r:id="rId120" xr:uid="{5D0474FF-F8D0-44CE-B562-5D3DE5097F07}"/>
+    <hyperlink ref="F122" r:id="rId121" xr:uid="{87DB5FA0-0F6D-4DDA-A0C0-3F34E2337811}"/>
+    <hyperlink ref="F123" r:id="rId122" xr:uid="{7CA1734E-C6E6-4235-BD40-38E98639969C}"/>
+    <hyperlink ref="F124" r:id="rId123" xr:uid="{8035C2CA-3121-4516-A913-D36D95D80FC2}"/>
+    <hyperlink ref="F125" r:id="rId124" xr:uid="{427BFDC4-758F-4CBD-AC38-48FDFC6B8782}"/>
+    <hyperlink ref="F126" r:id="rId125" xr:uid="{4EF54D50-D92A-4428-B208-DF661784CF2A}"/>
+    <hyperlink ref="F127" r:id="rId126" xr:uid="{427B2866-F97E-40AF-8EAE-36C946722B0F}"/>
+    <hyperlink ref="F128" r:id="rId127" xr:uid="{4DFCD947-F796-4C5B-BD1A-079267531E02}"/>
+    <hyperlink ref="F129" r:id="rId128" xr:uid="{8E1597CE-1816-47BE-B7B5-943A8F421A4F}"/>
+    <hyperlink ref="F130" r:id="rId129" xr:uid="{C68285FD-01EE-4655-8CA9-60671F061C24}"/>
+    <hyperlink ref="F131" r:id="rId130" xr:uid="{CF70BD50-C7E8-4F03-BF4F-98E015A7F17A}"/>
+    <hyperlink ref="F132" r:id="rId131" xr:uid="{0BCC3075-62FA-4725-80F1-81D892C3CB86}"/>
+    <hyperlink ref="F133" r:id="rId132" xr:uid="{F47CB5EC-A6C4-4151-9046-9E10ABD31858}"/>
+    <hyperlink ref="F134" r:id="rId133" xr:uid="{521B1029-2578-458B-BA12-FDC6F38187AF}"/>
+    <hyperlink ref="F135" r:id="rId134" xr:uid="{80F414A6-3271-460D-82A6-46367023FF83}"/>
+    <hyperlink ref="F136" r:id="rId135" xr:uid="{33E2E0E6-C569-4CA6-B6DD-B1F2438BCBB4}"/>
+    <hyperlink ref="F137" r:id="rId136" xr:uid="{07FDADF5-7345-4496-B61A-145238CFF866}"/>
+    <hyperlink ref="F138" r:id="rId137" xr:uid="{0C3A11F0-7C72-4FE3-BB86-177F71CB9FEA}"/>
+    <hyperlink ref="F139" r:id="rId138" xr:uid="{3CD6D2CA-24C3-45B6-9338-32F48A0AA42F}"/>
+    <hyperlink ref="F140" r:id="rId139" xr:uid="{37D0A8BA-E3EC-48E1-B100-35063468A95D}"/>
+    <hyperlink ref="F141" r:id="rId140" xr:uid="{D3300FE0-865D-4B4D-A315-9248CE02C337}"/>
+    <hyperlink ref="F142" r:id="rId141" xr:uid="{3B2DE658-7F84-4955-A68E-1C3EFE362F0E}"/>
+    <hyperlink ref="F143" r:id="rId142" xr:uid="{BCE7501F-A6E9-424D-91C2-E44AC4D57D3B}"/>
+    <hyperlink ref="F144" r:id="rId143" xr:uid="{0FDC7833-8E90-414D-A157-68729F82B1C7}"/>
+    <hyperlink ref="F145" r:id="rId144" xr:uid="{EF884925-7B16-4500-BE09-2FFDFA8AC1CB}"/>
+    <hyperlink ref="F146" r:id="rId145" xr:uid="{CE87711D-2A82-48A9-956E-A3C9D91E0185}"/>
+    <hyperlink ref="F147" r:id="rId146" xr:uid="{AD6F0A9F-F610-4AE9-B9D3-7ED94EBCCF9E}"/>
+    <hyperlink ref="F148" r:id="rId147" xr:uid="{687DCC77-3B1B-4F39-B294-80DE9ABCDB24}"/>
+    <hyperlink ref="F149" r:id="rId148" xr:uid="{6CBF01C8-EEC1-4BC6-8016-71E4117A25B9}"/>
+    <hyperlink ref="F150" r:id="rId149" xr:uid="{9A3D0D55-2C9F-4137-AB75-3B35BD4979E1}"/>
+    <hyperlink ref="F151" r:id="rId150" xr:uid="{EFCE480C-DB4B-4E96-9F58-E869B4ECF873}"/>
+    <hyperlink ref="F152" r:id="rId151" xr:uid="{58B23FCE-9BC1-4F23-9B05-2824F650EC0F}"/>
+    <hyperlink ref="F153" r:id="rId152" xr:uid="{26BC8ACE-DC52-475B-89E8-E4E039EFFCF6}"/>
+    <hyperlink ref="F182" r:id="rId153" xr:uid="{E37A36DF-D1AF-453C-82F9-FBFC43510412}"/>
+    <hyperlink ref="F183" r:id="rId154" xr:uid="{A25A7B15-4C6C-4160-8E47-7DE651721FE4}"/>
+    <hyperlink ref="F184" r:id="rId155" xr:uid="{C9489915-9EF1-44BD-A806-A028B02151ED}"/>
+    <hyperlink ref="F185" r:id="rId156" xr:uid="{258761DB-716F-4A17-BE5B-CC844D7DD14F}"/>
+    <hyperlink ref="F186" r:id="rId157" xr:uid="{F9321924-41F1-42E3-AA4E-9B5CD685CD0E}"/>
+    <hyperlink ref="F187" r:id="rId158" xr:uid="{08FA5984-728F-46B8-AE79-30B28EEECF4E}"/>
+    <hyperlink ref="F188" r:id="rId159" xr:uid="{86D1A466-FB24-420B-8879-7D4708FBBE3D}"/>
+    <hyperlink ref="F189" r:id="rId160" xr:uid="{F56F7F6B-40B8-4485-9DC4-AA952E7C3E7B}"/>
+    <hyperlink ref="F190" r:id="rId161" xr:uid="{8C33203A-C6C3-40C2-A250-65801466A870}"/>
+    <hyperlink ref="F191" r:id="rId162" xr:uid="{8AA3D53F-6CBF-4FD3-BFEF-6C20B75AF3BE}"/>
+    <hyperlink ref="F192" r:id="rId163" xr:uid="{4D3D3729-EC1A-4B2F-8EA0-54F051FC447D}"/>
+    <hyperlink ref="F193" r:id="rId164" xr:uid="{899EF0F7-9E7D-4D39-B34A-D0D4B761AF39}"/>
+    <hyperlink ref="F194" r:id="rId165" xr:uid="{A7586EBF-0881-492A-A4C3-9D9879811713}"/>
+    <hyperlink ref="F195" r:id="rId166" xr:uid="{C889668C-B3C2-4075-8EBE-DBC0AD30EAF1}"/>
+    <hyperlink ref="F196" r:id="rId167" xr:uid="{425CDFEE-B484-457C-9747-F9FCA52184BE}"/>
+    <hyperlink ref="F197" r:id="rId168" xr:uid="{D7753EDB-45E8-43D1-8680-2392AA44B24C}"/>
+    <hyperlink ref="F198" r:id="rId169" xr:uid="{B352F749-0293-4035-A128-C6E386790A64}"/>
+    <hyperlink ref="F199" r:id="rId170" xr:uid="{7CE09B0B-E674-47C0-9B72-0ED98F6891B8}"/>
+    <hyperlink ref="F200" r:id="rId171" xr:uid="{857E4CDE-5691-4C39-B1D6-17AB4B838871}"/>
+    <hyperlink ref="F201" r:id="rId172" xr:uid="{8A99BB89-D9E8-49EB-A81E-5BBAC4BA6DED}"/>
+    <hyperlink ref="F202" r:id="rId173" xr:uid="{E36FCD17-C042-4132-97F9-BBFF96F5EB64}"/>
+    <hyperlink ref="F203" r:id="rId174" xr:uid="{DDD2C1C6-AAFD-47A2-8674-79F7C17CC782}"/>
+    <hyperlink ref="F204" r:id="rId175" xr:uid="{35C40565-78C2-4D48-94E0-1E2EE403308A}"/>
+    <hyperlink ref="F205" r:id="rId176" xr:uid="{A2702FA7-102F-4206-82A4-32B082AA85B4}"/>
+    <hyperlink ref="F206" r:id="rId177" xr:uid="{DA3DF86D-5438-4439-BDBA-BBC3ECD5DD59}"/>
+    <hyperlink ref="F207" r:id="rId178" xr:uid="{9F1053DB-7530-4A63-B2C3-8A8A526CE542}"/>
+    <hyperlink ref="F208" r:id="rId179" xr:uid="{736C6C7D-A848-4E55-8160-310B3CBA73BD}"/>
+    <hyperlink ref="F209" r:id="rId180" xr:uid="{874E3559-BC95-4428-8742-F3E01BC5DBFD}"/>
+    <hyperlink ref="F210" r:id="rId181" xr:uid="{53366E4C-ADAD-42B3-8DD8-E133A852A4BD}"/>
+    <hyperlink ref="F211" r:id="rId182" xr:uid="{4876A31B-6F03-45CB-BA34-1B5442540DAD}"/>
+    <hyperlink ref="F212" r:id="rId183" xr:uid="{16BAE6F9-7239-4EFC-9767-A97CB78E48E8}"/>
+    <hyperlink ref="F213" r:id="rId184" xr:uid="{ECD6E617-7C11-49FA-B937-FD214D68BBAC}"/>
+    <hyperlink ref="F214" r:id="rId185" xr:uid="{21FAA203-7470-4D7D-A3BB-9933AFD1F367}"/>
+    <hyperlink ref="F215" r:id="rId186" xr:uid="{634A8180-B31B-4CA5-8F32-AA259024B14F}"/>
+    <hyperlink ref="F216" r:id="rId187" xr:uid="{D023B19B-7083-488A-A099-B6BE74A59D37}"/>
+    <hyperlink ref="F217" r:id="rId188" xr:uid="{B1578663-C3B6-4F2C-8B33-6DB282D6D290}"/>
+    <hyperlink ref="F218" r:id="rId189" xr:uid="{48C3EF64-5B2B-43CC-B616-6270C918BC85}"/>
+    <hyperlink ref="F219" r:id="rId190" xr:uid="{D077BC73-63F5-4D87-B80D-E15BEF4C45D2}"/>
+    <hyperlink ref="F220" r:id="rId191" xr:uid="{8D50E206-13C9-45A2-BBF8-487E5F645D84}"/>
+    <hyperlink ref="F221" r:id="rId192" xr:uid="{4BCDA111-C900-4761-9BCF-99F303DAAA2F}"/>
+    <hyperlink ref="F222" r:id="rId193" xr:uid="{A449B30C-1E02-4199-AB4B-EA7255E7674D}"/>
+    <hyperlink ref="F223" r:id="rId194" xr:uid="{9585EB03-5E7A-43F6-847A-842D6B45942D}"/>
+    <hyperlink ref="F224" r:id="rId195" xr:uid="{36C1A99F-715C-4A96-84B7-8BB9C85A1F00}"/>
+    <hyperlink ref="F225" r:id="rId196" xr:uid="{43BD1CFF-7742-4200-86A9-449C44F0752D}"/>
+    <hyperlink ref="F226" r:id="rId197" xr:uid="{24C4B9E9-0DF7-49DB-9491-5A252F19A39B}"/>
+    <hyperlink ref="F227" r:id="rId198" xr:uid="{5F149B2F-CB8F-4FA3-BD1E-54CFF9679374}"/>
+    <hyperlink ref="F228" r:id="rId199" xr:uid="{F5438FAA-650B-4B32-B574-29601D6CDCD8}"/>
+    <hyperlink ref="F229" r:id="rId200" xr:uid="{5AC2F776-6F39-4C81-A316-7099D77757F0}"/>
+    <hyperlink ref="F230" r:id="rId201" xr:uid="{1A31AFB3-387B-4CB2-B2E4-903A7CE35FCC}"/>
+    <hyperlink ref="F231" r:id="rId202" xr:uid="{642227BD-DF85-4E7F-BD78-19EE939C29F1}"/>
+    <hyperlink ref="F232" r:id="rId203" xr:uid="{7CF5547B-3B64-4174-AEF6-295A1ABBA36C}"/>
+    <hyperlink ref="F233" r:id="rId204" xr:uid="{DBEE7FA7-9C16-4667-90AB-E0DFF3B88DD3}"/>
+    <hyperlink ref="F154" r:id="rId205" xr:uid="{7554264D-2547-43E1-9770-446E2FD25BCC}"/>
+    <hyperlink ref="F155" r:id="rId206" xr:uid="{8A1BF691-1B25-4959-99AB-B66C11015F02}"/>
+    <hyperlink ref="F156" r:id="rId207" xr:uid="{B99F0CE7-5248-4F36-8870-267FE0980AA8}"/>
+    <hyperlink ref="F157" r:id="rId208" xr:uid="{1CBE6ACF-022E-4FF5-BA06-07F9F02FF319}"/>
+    <hyperlink ref="F158" r:id="rId209" xr:uid="{AB3C16DD-011F-485F-BDFF-B9564F28EFFA}"/>
+    <hyperlink ref="F159" r:id="rId210" xr:uid="{9C7370C2-3B97-406A-B993-9B320C170AF0}"/>
+    <hyperlink ref="F160" r:id="rId211" xr:uid="{5C5D84A2-C2ED-4CA3-AC5F-FB8260013B21}"/>
+    <hyperlink ref="F161" r:id="rId212" xr:uid="{7E86101D-E3B5-43E7-BB91-86F990AB576F}"/>
+    <hyperlink ref="F162" r:id="rId213" xr:uid="{86EF32D4-0787-4DEF-AF13-8D6989B5CEA6}"/>
+    <hyperlink ref="F163" r:id="rId214" xr:uid="{D94ACD25-749A-4CB1-8052-0A0AFE93780A}"/>
+    <hyperlink ref="F164" r:id="rId215" xr:uid="{2E00A680-64E9-407D-8E13-2F110618DF34}"/>
+    <hyperlink ref="F165" r:id="rId216" xr:uid="{5282E600-5DE5-40F4-ABBA-8BDF551E64C5}"/>
+    <hyperlink ref="F166" r:id="rId217" xr:uid="{1C04F383-D1C0-4924-BCA4-7D68BF4F2C8A}"/>
+    <hyperlink ref="F167" r:id="rId218" xr:uid="{DF7BF135-FF63-4E18-A7A5-FC4B58690512}"/>
+    <hyperlink ref="F168" r:id="rId219" xr:uid="{1DB2A338-6A2C-43A2-8EFC-188CA7D96DF3}"/>
+    <hyperlink ref="F169" r:id="rId220" xr:uid="{65DFDF8E-E514-4B91-8BEF-7DD72C911D4F}"/>
+    <hyperlink ref="F170" r:id="rId221" xr:uid="{A9D504BA-AD23-48E7-A473-E3FE0EC434F4}"/>
+    <hyperlink ref="F171" r:id="rId222" xr:uid="{7D5E334E-6CFD-4B49-94F8-1E5E7816CEF4}"/>
+    <hyperlink ref="F172" r:id="rId223" xr:uid="{81D56905-B982-4CBF-B952-F71944EA142A}"/>
+    <hyperlink ref="F173" r:id="rId224" xr:uid="{8B3CBB40-E4B6-4847-AFAA-F21B565F54DA}"/>
+    <hyperlink ref="F174" r:id="rId225" xr:uid="{8C47402A-5BE2-4D1B-8AB7-5CF16C4B84EB}"/>
+    <hyperlink ref="F175" r:id="rId226" xr:uid="{0088EA25-8E77-4132-90D8-5D0A3074B20F}"/>
+    <hyperlink ref="F176" r:id="rId227" xr:uid="{A61E9347-7C4E-41E4-A7E9-AA05313C5FC7}"/>
+    <hyperlink ref="F177" r:id="rId228" xr:uid="{5F690E95-E438-45DC-B54F-5EF7E7545176}"/>
+    <hyperlink ref="F178" r:id="rId229" xr:uid="{2DC5C43A-961D-4C73-8C18-D84597852CF5}"/>
+    <hyperlink ref="F179" r:id="rId230" xr:uid="{FF7475C9-D2DA-4B9A-A867-501EFEA3C7B8}"/>
+    <hyperlink ref="F180" r:id="rId231" xr:uid="{36B83677-8EFD-4D8E-A00C-384F0A81678E}"/>
+    <hyperlink ref="F181" r:id="rId232" xr:uid="{AEE3D4D7-55E2-4FED-8E53-EA1201972E3C}"/>
+    <hyperlink ref="F234" r:id="rId233" xr:uid="{2E12A770-0B07-45A2-A461-625EEEC258DA}"/>
+    <hyperlink ref="F235" r:id="rId234" xr:uid="{367DA9FF-A0AA-410B-9DDE-593EA3D8446D}"/>
+    <hyperlink ref="F236" r:id="rId235" xr:uid="{9D67B6DC-99F9-45B6-9FE8-29B117DACDAB}"/>
+    <hyperlink ref="F237" r:id="rId236" xr:uid="{33BF3254-CA00-424D-8085-B0F44D80A808}"/>
+    <hyperlink ref="F238" r:id="rId237" xr:uid="{1BFDA55B-31DA-4088-A658-B915DD35B6E6}"/>
+    <hyperlink ref="F239" r:id="rId238" xr:uid="{D43D5340-E0C4-4744-A915-1F7F8F01940D}"/>
+    <hyperlink ref="F240" r:id="rId239" xr:uid="{AD4A3C3C-86BA-4866-8A2F-8C5232523A8D}"/>
+    <hyperlink ref="F241" r:id="rId240" xr:uid="{56DA2C6E-BC11-4E19-AE22-03E1C6D1E3F4}"/>
+    <hyperlink ref="F242" r:id="rId241" xr:uid="{897E3D83-DF91-4892-908F-73E3E08048FA}"/>
+    <hyperlink ref="F243" r:id="rId242" xr:uid="{64F3AD1A-993F-4769-B58A-1F725E5CDA0E}"/>
+    <hyperlink ref="F244" r:id="rId243" xr:uid="{DC9B3EB8-B1EB-48AC-B2D7-969A79B67512}"/>
+    <hyperlink ref="F245" r:id="rId244" xr:uid="{EF941B07-8F2C-4D8F-8C29-2A61427B6A73}"/>
+    <hyperlink ref="F246" r:id="rId245" xr:uid="{7FB80983-CA7D-4D95-901D-55429CD5A532}"/>
+    <hyperlink ref="F247" r:id="rId246" xr:uid="{6F9BA08E-A1DC-4A8E-8685-CE73D5845A2E}"/>
+    <hyperlink ref="F248" r:id="rId247" xr:uid="{FA55C00A-55DC-4F39-8A25-8656B7712852}"/>
+    <hyperlink ref="F249" r:id="rId248" xr:uid="{BE915386-1311-4240-8C12-5E033381C471}"/>
+    <hyperlink ref="F250" r:id="rId249" xr:uid="{A73C957B-2CC3-40DB-B94C-95974BB536B9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId33"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId250"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia1-my.sharepoint.com/personal/icdide_ehwadia1_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C27B58C-80A5-4575-83E3-09779DE1B019}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B19CE665-2725-459D-BD7E-C8A3BB50D3FD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="1048">
   <si>
     <t>Package Code</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -43,14 +43,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>SKU/PART No.2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKU/PART No.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>File path</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2301,6 +2293,896 @@
   </si>
   <si>
     <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAJkyQIpQq4QYgSdnZk7BFlAVKwCUwQSrHIluAaB_x7GYc</t>
+  </si>
+  <si>
+    <t>SKU/PART</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCINTILLA</t>
+  </si>
+  <si>
+    <t>2608576669</t>
+  </si>
+  <si>
+    <t>P112705 SCINTILLA BEC-D25</t>
+  </si>
+  <si>
+    <t>P123939 SCINTILLA BEC-D25</t>
+  </si>
+  <si>
+    <t>2608587113</t>
+  </si>
+  <si>
+    <t>P123637 SCINTILLA PD-14</t>
+  </si>
+  <si>
+    <t>2608599058</t>
+  </si>
+  <si>
+    <t>P122271 SCINTILLA PD-14D</t>
+  </si>
+  <si>
+    <t>2608615210</t>
+  </si>
+  <si>
+    <t>DMADST0450 (US)</t>
+  </si>
+  <si>
+    <t>P102318 SCINTILLA LES-4.5</t>
+  </si>
+  <si>
+    <t>2608615211</t>
+  </si>
+  <si>
+    <t>DMADST0500(US)</t>
+  </si>
+  <si>
+    <t>P102350 SCINTILLA LES-5</t>
+  </si>
+  <si>
+    <t>2608615212</t>
+  </si>
+  <si>
+    <t>DMADST0600 (US)</t>
+  </si>
+  <si>
+    <t>P102319 SCINTILLA LES-6</t>
+  </si>
+  <si>
+    <t>2608615213</t>
+  </si>
+  <si>
+    <t>DMADST0700 (US)</t>
+  </si>
+  <si>
+    <t>P102320 SCINTILLA LES-7</t>
+  </si>
+  <si>
+    <t>2608615214</t>
+  </si>
+  <si>
+    <t>DMADS0400 (US)</t>
+  </si>
+  <si>
+    <t>P102363 SCINTILLA LES 4</t>
+  </si>
+  <si>
+    <t>2608615215</t>
+  </si>
+  <si>
+    <t>DMADS0450 (USA)</t>
+  </si>
+  <si>
+    <t>P102321 SCINTILLA LES-4.5</t>
+  </si>
+  <si>
+    <t>2608615218</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DMADS0700 (US)</t>
+  </si>
+  <si>
+    <t>P102324 SCINTILLA LES-7</t>
+  </si>
+  <si>
+    <t>2608615219</t>
+  </si>
+  <si>
+    <t>DMADS1000 (US)</t>
+  </si>
+  <si>
+    <t>P102403 SCINTILLA LES-10</t>
+  </si>
+  <si>
+    <t>2608615220</t>
+  </si>
+  <si>
+    <t>DMADS1200 (US)</t>
+  </si>
+  <si>
+    <t>P105649 SCINTILLA LES-12</t>
+  </si>
+  <si>
+    <t>2608615221</t>
+  </si>
+  <si>
+    <t>DMADS1400 (US)</t>
+  </si>
+  <si>
+    <t>P102327 SCINTILLA LES-14</t>
+  </si>
+  <si>
+    <t>2608900531</t>
+  </si>
+  <si>
+    <t>P101325 SCINTILLA BS-4</t>
+  </si>
+  <si>
+    <t>P119003 SCINTILLA BS-4</t>
+  </si>
+  <si>
+    <t>2608900532</t>
+  </si>
+  <si>
+    <t>P100203 SCINTILLA BS-4.5</t>
+  </si>
+  <si>
+    <t>2608900533</t>
+  </si>
+  <si>
+    <t>P100180 BS-5</t>
+  </si>
+  <si>
+    <t>2608900535</t>
+  </si>
+  <si>
+    <t>P101327 SCINTILLA BS-7</t>
+  </si>
+  <si>
+    <t>2608900536</t>
+  </si>
+  <si>
+    <t>P100181 SCINTILLA BS-9</t>
+  </si>
+  <si>
+    <t>2608900537</t>
+  </si>
+  <si>
+    <t>P111100 SCINTILLA BS-14</t>
+  </si>
+  <si>
+    <t>2608900659</t>
+  </si>
+  <si>
+    <t>P102337 SCINTILLA LES-4.5</t>
+  </si>
+  <si>
+    <t>2608900660</t>
+  </si>
+  <si>
+    <t>P102102 SCINTILLA LES-5</t>
+  </si>
+  <si>
+    <t>P124706 SCINTILLA LES-5 BOSCH EXPERT</t>
+  </si>
+  <si>
+    <t>2608900661</t>
+  </si>
+  <si>
+    <t>P102338 SCINTILLA 6inch</t>
+  </si>
+  <si>
+    <t>2608900662</t>
+  </si>
+  <si>
+    <t>P102339 SCINTILLA LES 7</t>
+  </si>
+  <si>
+    <t>2608900663</t>
+  </si>
+  <si>
+    <t>P102103 SCINTILLA LES-9</t>
+  </si>
+  <si>
+    <t>P124707 SCINTILLA LES-9 BOSCH EXPERT</t>
+  </si>
+  <si>
+    <t>2608900664</t>
+  </si>
+  <si>
+    <t>P102402 SCINTILLA LES-12</t>
+  </si>
+  <si>
+    <t>2608900665</t>
+  </si>
+  <si>
+    <t>P102340 SCINTILLA LES-12</t>
+  </si>
+  <si>
+    <t>P124708 SCINTILLA LES-12</t>
+  </si>
+  <si>
+    <t>2608900666</t>
+  </si>
+  <si>
+    <t>P102104 SCINTILLA LES-14</t>
+  </si>
+  <si>
+    <t>P124709 SCINTILLA LES-14 EXPERT</t>
+  </si>
+  <si>
+    <t>2608900667</t>
+  </si>
+  <si>
+    <t>P102341 SCINTILLA LES 16</t>
+  </si>
+  <si>
+    <t>2608900668</t>
+  </si>
+  <si>
+    <t>P102342 SCINTILLA LES-18</t>
+  </si>
+  <si>
+    <t>2608900669</t>
+  </si>
+  <si>
+    <t>P103894 SCINTILLA LES-4.5</t>
+  </si>
+  <si>
+    <t>2608901391</t>
+  </si>
+  <si>
+    <t>P106844 SCINTILLA BS-5 + WHEEL</t>
+  </si>
+  <si>
+    <t>2608901392</t>
+  </si>
+  <si>
+    <t>P109920 SCINTILLA BS-9+WHEEL</t>
+  </si>
+  <si>
+    <t>2608902380</t>
+  </si>
+  <si>
+    <t>P131335 SCINTILLA AG BS-4</t>
+  </si>
+  <si>
+    <t>2608902472</t>
+  </si>
+  <si>
+    <t>P131337 SCINTILLA AG BS-4.5</t>
+  </si>
+  <si>
+    <t>2608902473</t>
+  </si>
+  <si>
+    <t>P131338 SCINTILLA AG BS-5</t>
+  </si>
+  <si>
+    <t>2608902474</t>
+  </si>
+  <si>
+    <t>P131339 SCINTILLA AG BS-7</t>
+  </si>
+  <si>
+    <t>2608902475</t>
+  </si>
+  <si>
+    <t>P131340 SCINTILLA AG BS-9</t>
+  </si>
+  <si>
+    <t>2608902738</t>
+  </si>
+  <si>
+    <t>P131336 SCINTILLA AG BS-4</t>
+  </si>
+  <si>
+    <t>2608F01401</t>
+  </si>
+  <si>
+    <t>CDD045DIA101F</t>
+  </si>
+  <si>
+    <t>P114888 SCINTILLA BS-4.5</t>
+  </si>
+  <si>
+    <t>2608F01403</t>
+  </si>
+  <si>
+    <t>CANADA_CDD050DIA101F</t>
+  </si>
+  <si>
+    <t>P114889 SCINTILLA BS-5</t>
+  </si>
+  <si>
+    <t>2608F01466</t>
+  </si>
+  <si>
+    <t>DDD070DIA101F</t>
+  </si>
+  <si>
+    <t>P114886 SCINTILLA BS-7</t>
+  </si>
+  <si>
+    <t>2608F01467</t>
+  </si>
+  <si>
+    <t>CDD070DIA101F CANADA</t>
+  </si>
+  <si>
+    <t>P114891 SCINTILLA DIABLO BS-7</t>
+  </si>
+  <si>
+    <t>2608F01582</t>
+  </si>
+  <si>
+    <t>DDD045DIA101F</t>
+  </si>
+  <si>
+    <t>P114880 SCINTILLA BS-4.5</t>
+  </si>
+  <si>
+    <t>2608F01584</t>
+  </si>
+  <si>
+    <t>DDD050DIA101F</t>
+  </si>
+  <si>
+    <t>P114882 SCINTILLA BS-5</t>
+  </si>
+  <si>
+    <t>2608F01684</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DDD045DIA101F</t>
+  </si>
+  <si>
+    <t>P114887 SCINTILLA BS-4.5</t>
+  </si>
+  <si>
+    <t>2608F01767</t>
+  </si>
+  <si>
+    <t>DDX045DIA101F</t>
+  </si>
+  <si>
+    <t>P114881 BS-4.5</t>
+  </si>
+  <si>
+    <t>2608F01769</t>
+  </si>
+  <si>
+    <t>DDX050DIA101F</t>
+  </si>
+  <si>
+    <t>P114883 SCINTILLA BS-5</t>
+  </si>
+  <si>
+    <t>2608F02317</t>
+  </si>
+  <si>
+    <t>DMADS0900 (US)</t>
+  </si>
+  <si>
+    <t>P104097 SCINTILLA LES-9</t>
+  </si>
+  <si>
+    <t>2608F02318</t>
+  </si>
+  <si>
+    <t>DMADST0900 (US)</t>
+  </si>
+  <si>
+    <t>P104098 SCINTILLA LES-9</t>
+  </si>
+  <si>
+    <t>2608F02319</t>
+  </si>
+  <si>
+    <t>DMADST1000 (US)</t>
+  </si>
+  <si>
+    <t>P104922 SCINTILLA LES-10</t>
+  </si>
+  <si>
+    <t>2608F02320</t>
+  </si>
+  <si>
+    <t>DMADST1200 (US)</t>
+  </si>
+  <si>
+    <t>P102326 SCINTILLA LES-12</t>
+  </si>
+  <si>
+    <t>2608F02321</t>
+  </si>
+  <si>
+    <t>DMADST1400 (US)</t>
+  </si>
+  <si>
+    <t>P104923 SCINTILLA BS-14</t>
+  </si>
+  <si>
+    <t>2608F02460</t>
+  </si>
+  <si>
+    <t>P114892 SCINTILLA BS-4.5 đóng 2 PCS HỘP</t>
+  </si>
+  <si>
+    <t>2608F02525</t>
+  </si>
+  <si>
+    <t>DMADS0400 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106971 SCINTILLA LES-4</t>
+  </si>
+  <si>
+    <t>2608F02526</t>
+  </si>
+  <si>
+    <t>DMADS0450 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106972 SCINTILLA LES 4.5</t>
+  </si>
+  <si>
+    <t>2608F02528</t>
+  </si>
+  <si>
+    <t>DMADS0600 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106974 SCINTILLA LES-6</t>
+  </si>
+  <si>
+    <t>2608F02529</t>
+  </si>
+  <si>
+    <t>DMADS0700 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106975 SCINTILLA LES-7</t>
+  </si>
+  <si>
+    <t>2608F02532</t>
+  </si>
+  <si>
+    <t>DMADS1200 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106977 SCINTILLA LES-12</t>
+  </si>
+  <si>
+    <t>2608F02534</t>
+  </si>
+  <si>
+    <t>DMADST0400 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106962 SCINTILLA LES-4</t>
+  </si>
+  <si>
+    <t>2608F02535</t>
+  </si>
+  <si>
+    <t>DMADST0450 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106963 SCINTILLA LES 4.5</t>
+  </si>
+  <si>
+    <t>2608F02536</t>
+  </si>
+  <si>
+    <t>DMADST0500 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106964 SCINTILLA LES-5</t>
+  </si>
+  <si>
+    <t>2608F02538</t>
+  </si>
+  <si>
+    <t>DMADST0700 (CANADA)</t>
+  </si>
+  <si>
+    <t>P106968 SCINTILLA LES-7</t>
+  </si>
+  <si>
+    <t>2608F02539</t>
+  </si>
+  <si>
+    <t>DMADST0900 (CANADA)</t>
+  </si>
+  <si>
+    <t>P108429 SCINTILLA AG LES-9</t>
+  </si>
+  <si>
+    <t>2608F02540</t>
+  </si>
+  <si>
+    <t>DMADST1000 (CANADA)</t>
+  </si>
+  <si>
+    <t>P108138 SCINTILLA LES-10</t>
+  </si>
+  <si>
+    <t>2608F02541</t>
+  </si>
+  <si>
+    <t>DMADST1200 (CANADA)</t>
+  </si>
+  <si>
+    <t>P107871 SCINTILLA LES-12</t>
+  </si>
+  <si>
+    <t>2608F02542</t>
+  </si>
+  <si>
+    <t>DMADST1400 (CANADA)</t>
+  </si>
+  <si>
+    <t>P107872 SCINTILLA LES-14</t>
+  </si>
+  <si>
+    <t>2608F06256</t>
+  </si>
+  <si>
+    <t>DDSDI0450 (US)</t>
+  </si>
+  <si>
+    <t>P136591 SCINTILLA BS-4.5</t>
+  </si>
+  <si>
+    <t>2608F06257</t>
+  </si>
+  <si>
+    <t>DDSDI0900 (US)</t>
+  </si>
+  <si>
+    <t>P136593 SCINTILLA BS-9</t>
+  </si>
+  <si>
+    <t>2608F06258</t>
+  </si>
+  <si>
+    <t>DDSDI1400 (US)</t>
+  </si>
+  <si>
+    <t>P136595 SCINTILLA BS-14</t>
+  </si>
+  <si>
+    <t>2608F06259</t>
+  </si>
+  <si>
+    <t>DDSDI0450 (CA)</t>
+  </si>
+  <si>
+    <t>P136592 SCINTILLA BS-4.5</t>
+  </si>
+  <si>
+    <t>2608F06260</t>
+  </si>
+  <si>
+    <t>DDSDI0900 (CA)</t>
+  </si>
+  <si>
+    <t>P136594 SCINTILLA BS-9</t>
+  </si>
+  <si>
+    <t>2608F06261</t>
+  </si>
+  <si>
+    <t>DDSDI1400 (CA)</t>
+  </si>
+  <si>
+    <t>P136596 SCINTILLA BS-14</t>
+  </si>
+  <si>
+    <t>2610075118</t>
+  </si>
+  <si>
+    <t>P126084 SCINTILLA LES-12</t>
+  </si>
+  <si>
+    <t>2610075119</t>
+  </si>
+  <si>
+    <t>P126085 SCINTILLA LES-14</t>
+  </si>
+  <si>
+    <t>P004828 SCINTILLA PD-6D</t>
+  </si>
+  <si>
+    <t>P004832 SCINTILLA PD-8D</t>
+  </si>
+  <si>
+    <t>P004834 SCINTILLA PD-10D</t>
+  </si>
+  <si>
+    <t>P115095 SCINTILLA PD-7D</t>
+  </si>
+  <si>
+    <t>P119314 SCINTILLA EDS-524</t>
+  </si>
+  <si>
+    <t>P124601</t>
+  </si>
+  <si>
+    <t>LES-5 LAP RAP</t>
+  </si>
+  <si>
+    <t>TM 31094</t>
+  </si>
+  <si>
+    <t>P119646 SCINTILLA AG LES-4.5</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCqxH76KWXVSoWY8EDKL30QAWbI0hBeWa19EH3yjA_J7PM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQC-kOuZvcZPT601uADqX8CgAeDLriBnlaW7l6bfpWtnT8k</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAXHbEf-XD6Sb-s92tzOJXDAYZwu9t3Wo672m1bgL1h3G0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAym13ZJ--iRpNmxV3g1WiJAbVtMGsilwqp-xnuZuJxv00</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQB2-bAjYRNcS55hYoKSA9jNAePONQkQ1N-lGYFBoW_auK0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAh_RtmOJaDS4Yvy-j1ZDSPAdUyQxryZNwUSYcfOFQ6KzU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCk7r5rQzbXR4iqYR-zpMkmAU1TkzRZLG0tmaDAfBpGhzU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBfXzXoypH3TLLvbJlWclv1AVHYja7xNYPu5XygJw3kVvU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDj9rexOHV5SImbtJo4FNmwAZH5eu9B5P8LlRNF5SvPclA</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDMxyqbXaUFSa8IBbbEaaYqAYZGvK9g4oPxpPnAlxtojTM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA6FDvKhwnfRogdT1cmy7isATffZA0niG3-stTD_CLNFGM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDwm-XElWwoTq2Hcl4jhhTfARtmiura1QDLPNfup9hlT9U</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDKxs5hmdtJSp2rRKbwyJT5AVHdOSj1qKCR1OwoijUKdZQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCq-7mpVHJxS4hLwK45LLwhAZHR8wjpq2Byra2_MwIS82Q</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBqF3FDc5mUTpNHi8GE-_JRAbSNhXukzZuAigtG4gaJWjI</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQABXbpKJD5WTYsNMvwIso_gAeujPAHyvt03UEDegwjF5lo</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBPCa9XC_U9QbWvnO9-IMp-AbuWLAHq9Ttvr6lKZZ_WOXQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD2AdRPRFAhQohIEn2pnLgvAQ8wH_5N6LA6VBRqzzRjuso</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDHRQ2_pm5zRapkmteADg74AfbIzNWcAH91tNwsbiPzVxQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAVUp7nWh8GTqTfMyGPpjquATkzW6tyYzsOSkyqGTe-jL4</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA8mqghZgw7SYWMdQN9VNzXAXg3jjZMgoOjDzP5Jp7juWQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDSMKvrMCPzQKqjrarhj3GrAZKpc5zQu5f6pDgAyanpQE8</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQC4dSR90YVbTKNQSyUWSr83AR3677Z7omvISoboepRI5TI</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAi1KRVBw-cT6yXofoMu_z4AWCtts6MlV_mAuELePjGp0U</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCkaahVt-E2Q64fhpBMXbk6AX3H_BazMfX7F4of4P8mfkw</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA-gsSre0j6S6hXw4AzqkkMAdgGPzeAFP6MdPw6c12t9SQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCeyEfVQdbMTJK3qyrL0iVbAVBC9sT-VUnCuIU-LqqEHqU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCjmoXsR4GrSaitii0krWLmAZhi_Qu4KogetH2Is07MjFw</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAaftMuI0sXT5N2JAwtWiNoAWonOC9l8GkwIM-KAKwnPYM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA09BHrziySTbapVPalhfArAdJIuP9I9N4VMLr4LszW4QY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD5dOD8rc7wS7f6tPIa8LcWAcW7IxknwFGI9QH0CpSTVJo</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAjoZDL_EAOTr72R_bcx-ktAdszEjll_fHnZBfbsxVnXWM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAN-u2gi8tCSYI7Likk1kWWAQ2uIVucnssoCmyrg3Wjw2Y</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCnQhYOgVxXSbtMb22SfTrUASiOQluGRSAnvORbo56JSc0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDyqrIgckL1SK12g7jeCNZ-AXO_hQb8YHjo8t3THp8-gvk</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDpiriEvLe7SZ-a4TO01YFvAS0GnVgWv80WTsc4iVRnzxA</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCFXmI7pvMMR424fIFS2KqwAeYxR6CTpE6ima9PqGBvoxs</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBZaHyPHgY7QIekKB6h1pgCAQlNa5BbewsUXZYlQEmAKT4</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDqGR5RZF7CTYDTVJF5tnm8AacAvoPCvi3K8NlklsjhYbU</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBaKxUbsY0eR6qigkf_OqNAAZz9khVR3f58g2DtX2l3lJo</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD0aZpCfoweRaNfxAxsf9LVAWysLcfnZsnZUCQE1U2tJgI</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCxMI7SdUDBRpQqKBgfhXYyATY6SaQLnsTdn_rK-2fvdXQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDZaMTgXbK-QI5eD_QRhuGRAdeKcn0Wo-KBOAx6naWLV6A</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQA5hI9UD4r5RojKjzyxSy_pAZvDq_xFoB2hRucWKH7e1gE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQB-J3Cit7ymQpAngXclzvP5AY45xCMcXE2xxBrpcRyKlUI</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD3uw-jJxLvSLd09rwxQbw2AXGEDsL1BX6q_xq7ogvslWw</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAEHIsrAh4IRYDulfhAj3uyAW9LjLJKknYK_43iwOBpvdM</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCRlL0Aq5Q9QabF_H0Db01oAbpLjpyhPjE8JYZqi2Mb5Zk</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQClPHUPV8oISr12Dh8H7RejAYhpm_iE4bvAFnRS7TDNLsc</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBofR8NLEaiQZ5HkCOJ3ssgAeyenAWDK08-AzmEOB7lP1I</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCZdOdZXf4pT7T-VQPoLV8GAY6biwEI6NVDXEiAFaoemHg</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAziVodvsqIS7e6Ft9yjKuvAfGZnI_syP-Ki0XeFp_eLcE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBag_T4yEu7RLdpIasBIrUOAUf-oGTgxZ930jVOzggWW3E</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQB6ClXj6Z3VQKnScPRQnMw6AZE4jlL9nDVbclEdWX6x1Us</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQARhkGixrfoTbrL_Gy1ZjdkATZ0S9tOy5N5pVgruetlFiQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQALmWNNkJ8FSoPw0yMRg-YdAdiZmknmz0BGP68c_16B0-U</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD-skuks4vISZF_V4axgHf1ATr0-ekRAGReysNtNNqpT1Y</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBTUnEWZZ0qSotDxsA0tQMNAWKOGvCCkCIZCVGRqY3FZIs</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBCjlbcbHIkQ4pG1QXxfUQwAS39E4g5x_vtlCDEes4MJQ4</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD-3u3pv3kZRbv1l-oaHs9iAf247OMffH86YpJBJa9PuoY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCGVhxJ9XnoTZNR40cm2W3NAZE55ybT2hv6DrbyritT5HE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCeZmy71Nj5TaTsocaQaYIfAVGcuChs08WRi96ytf8J4JI</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCrhfqQ0NGDS7Gdi39cmgl9AVV-M7aZ2TBEiffrlRLRO0A</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDqBVk5juDSRrspdNQqsufkAaMPTV6qfUVewiaXVSXstWI</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQD5OmOXXdUgTo0zg4HPW7FWAbDYY5yy3XTtwN3LJITwZys</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDFS0ZtLyJmT5Z-OQBGEhf3AYiw92VgA76RTwfTaNPtx9M</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQANvX9TuMvjSIkFdJ6DjKpPAf7v_pNjSOVxzxPwuMu5aqc</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBXZEhth-9JRr37I68QkTKvAY43jDTLKJYh2J1blL6OyMk</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCG7jqk6t4-TLa4ZVhjnVULATdh85FLNnWRHzgLVONF5TA</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAJc0TDWPsSSL6CLX3AjfA0Aef9RMx2PNnAOIAXP6KGNLg</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAqFTicQ0_wSqyqea4cX1ehAdJREInPui4l2vsRYQG_aVE</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCo3ZokzO_mSKp0E-WlL2Y0Ac7XvVOO4N7vYHQ_DJZhVH8</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCEvj5SVp0AS7ISqbILnbL6AZnET39EKfc6cW3a7GCOCrY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDcrLU7C-loSJA7_Y6214qzAaxeyYKcIanR80WSGylbx3A</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCxk9KarlRlSKjLnRvVVqzkATsFWGschcC8EDsVU_KCzgo</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBqws46MPjjQ5dKGborxsabAWKDdxSO9ec6PHJlh_uNStk</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBDP-aTe7ZKSa-5xQAL9dYVAX6F4ejIV5slSck0G7XtCzw</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQALaGekZgIZSYJ480D2noL5AU0hiM9vyMC_kO4Pp9VGe1w</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBqLS-O1AXOTYxJcY90RBgbAZGJHHFDfdQf6RDZMTk07XY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCcHgFb0RM9Qa0We_sanWmaAY4dkmp_iraH1h3OBKrG1bQ</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCF6SMi8v8MRoH0qdxLSRleAYqB7JLaOekQAUTJOdl20E0</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCLwMp6IStjRrI1HITtxOPrAT8FDD7wGmvxl6Y5Pl8Q-TY</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQCvpA7bmReRR56Witmr-q05AZb7adUCxGywlnagxZkje0Y</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAgWHFZdJ1uQoPrYYC9DwXNAUh9ActXR68Bh6u_y4sRZ5U</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBRM7AvzUVLQJ6AkLzqx5w5ATGvpFcS8_c2WampuZixvkk</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQBXFeg7XYB8TZQ-bdB4ywEyAWVPS1FWUpZ8vP0Nf8-Fl78</t>
+  </si>
+  <si>
+    <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQAxh0lmiYyvQIt0yfcNqbEpAffTRZI0y33LiRiI-lAx3-k</t>
+  </si>
+  <si>
+    <t>HILTI</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3301,7 +4183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:F250"/>
+  <dimension ref="A1:F337"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="21.875" style="1" customWidth="1"/>
@@ -3311,10 +4193,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>752</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
@@ -3323,3637 +4205,5327 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="C13" s="3"/>
+      <c r="E13" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="C14" s="3"/>
+      <c r="E14" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="C15" s="3"/>
+      <c r="E15" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="C16" s="3"/>
+      <c r="E16" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="F13" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="C17" s="3"/>
+      <c r="E17" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="F14" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="C18" s="3"/>
+      <c r="E18" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="F15" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="C19" s="3"/>
+      <c r="E19" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="F16" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="C20" s="3"/>
+      <c r="E20" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="F17" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="C21" s="3"/>
+      <c r="E21" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="F18" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="C22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="F19" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="C23" s="3"/>
+      <c r="E23" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="F20" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="C24" s="3"/>
+      <c r="E24" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="F21" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="C25" s="3"/>
+      <c r="E25" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="F22" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="C26" s="3"/>
+      <c r="E26" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="F23" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="C27" s="3"/>
+      <c r="E27" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="F24" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="C28" s="3"/>
+      <c r="E28" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="F25" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="C29" s="3"/>
+      <c r="E29" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="F26" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="C30" s="3"/>
+      <c r="E30" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C31" s="3"/>
+      <c r="E31" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="F27" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="F28" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+      <c r="C32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="F29" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="F30" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="F31" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" s="5"/>
-      <c r="F32" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C33" s="5"/>
+      <c r="C33" s="3"/>
+      <c r="E33" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F33" s="4" t="s">
-        <v>37</v>
+        <v>991</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" s="5"/>
+        <v>94</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="E34" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F34" s="4" t="s">
-        <v>186</v>
+        <v>992</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C35" s="5"/>
+        <v>96</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="E35" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F35" s="4" t="s">
-        <v>187</v>
+        <v>993</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C36" s="5"/>
+        <v>98</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="E36" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F36" s="4" t="s">
-        <v>188</v>
+        <v>994</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>107</v>
+        <v>759</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C37" s="5"/>
+        <v>760</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="E37" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F37" s="4" t="s">
-        <v>189</v>
+        <v>995</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>109</v>
+        <v>761</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C38" s="5"/>
+        <v>762</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F38" s="4" t="s">
-        <v>190</v>
+        <v>996</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>111</v>
+        <v>764</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C39" s="5"/>
+        <v>765</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F39" s="4" t="s">
-        <v>191</v>
+        <v>997</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>113</v>
+        <v>767</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C40" s="5"/>
+        <v>768</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F40" s="4" t="s">
-        <v>192</v>
+        <v>998</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>115</v>
+        <v>770</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C41" s="5"/>
+        <v>771</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F41" s="4" t="s">
-        <v>193</v>
+        <v>999</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>117</v>
+        <v>773</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C42" s="5"/>
+        <v>774</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F42" s="4" t="s">
-        <v>194</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>119</v>
+        <v>776</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C43" s="5"/>
+        <v>777</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F43" s="4" t="s">
-        <v>195</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>121</v>
+        <v>779</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C44" s="5"/>
+        <v>780</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F44" s="4" t="s">
-        <v>196</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>123</v>
+        <v>782</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C45" s="5"/>
+        <v>783</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F45" s="4" t="s">
-        <v>197</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>125</v>
+        <v>785</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C46" s="5"/>
+        <v>786</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F46" s="4" t="s">
-        <v>198</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>127</v>
+        <v>788</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C47" s="5"/>
+        <v>789</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F47" s="4" t="s">
-        <v>199</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>129</v>
+        <v>791</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C48" s="5"/>
+        <v>792</v>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="E48" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F48" s="4" t="s">
-        <v>200</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>131</v>
+        <v>791</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C49" s="5"/>
+        <v>793</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="E49" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F49" s="4" t="s">
-        <v>201</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>133</v>
+        <v>794</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C50" s="5"/>
+        <v>795</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="E50" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F50" s="4" t="s">
-        <v>202</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>135</v>
+        <v>796</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C51" s="5"/>
+        <v>797</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="E51" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F51" s="4" t="s">
-        <v>203</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>137</v>
+        <v>798</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C52" s="5"/>
+        <v>799</v>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="E52" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F52" s="4" t="s">
-        <v>204</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>139</v>
+        <v>800</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C53" s="5"/>
+        <v>801</v>
+      </c>
+      <c r="C53" s="3"/>
+      <c r="E53" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F53" s="4" t="s">
-        <v>205</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>141</v>
+        <v>802</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C54" s="5"/>
+        <v>803</v>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="E54" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F54" s="4" t="s">
-        <v>206</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>143</v>
+        <v>804</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C55" s="5"/>
+        <v>805</v>
+      </c>
+      <c r="C55" s="3"/>
+      <c r="E55" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F55" s="4" t="s">
-        <v>207</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>145</v>
+        <v>806</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C56" s="5"/>
+        <v>807</v>
+      </c>
+      <c r="C56" s="3"/>
+      <c r="E56" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F56" s="4" t="s">
-        <v>208</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>147</v>
+        <v>806</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C57" s="5"/>
+        <v>808</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="E57" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F57" s="4" t="s">
-        <v>209</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>149</v>
+        <v>809</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C58" s="5"/>
+        <v>810</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="E58" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F58" s="4" t="s">
-        <v>210</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>151</v>
+        <v>811</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C59" s="5"/>
+        <v>812</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="E59" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F59" s="4" t="s">
-        <v>211</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>153</v>
+        <v>813</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C60" s="5"/>
+        <v>814</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="E60" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F60" s="4" t="s">
-        <v>212</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>155</v>
+        <v>813</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C61" s="5"/>
+        <v>815</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="E61" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F61" s="4" t="s">
-        <v>213</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>157</v>
+        <v>816</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C62" s="5"/>
+        <v>817</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="E62" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F62" s="4" t="s">
-        <v>214</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>159</v>
+        <v>818</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C63" s="5"/>
+        <v>819</v>
+      </c>
+      <c r="C63" s="3"/>
+      <c r="E63" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F63" s="4" t="s">
-        <v>215</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>161</v>
+        <v>818</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C64" s="5"/>
+        <v>820</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="E64" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F64" s="4" t="s">
-        <v>216</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>163</v>
+        <v>821</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C65" s="5"/>
+        <v>822</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="E65" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F65" s="4" t="s">
-        <v>217</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>165</v>
+        <v>821</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C66" s="5"/>
+        <v>823</v>
+      </c>
+      <c r="C66" s="3"/>
+      <c r="E66" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F66" s="4" t="s">
-        <v>218</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>167</v>
+        <v>824</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C67" s="5"/>
+        <v>825</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="E67" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F67" s="4" t="s">
-        <v>219</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>169</v>
+        <v>826</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C68" s="5"/>
+        <v>827</v>
+      </c>
+      <c r="C68" s="3"/>
+      <c r="E68" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F68" s="4" t="s">
-        <v>220</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>171</v>
+        <v>828</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C69" s="5"/>
+        <v>829</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="E69" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F69" s="4" t="s">
-        <v>221</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>173</v>
+        <v>830</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C70" s="5"/>
+        <v>831</v>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="E70" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F70" s="4" t="s">
-        <v>222</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>175</v>
+        <v>832</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C71" s="5"/>
+        <v>833</v>
+      </c>
+      <c r="C71" s="3"/>
+      <c r="E71" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F71" s="4" t="s">
-        <v>223</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>177</v>
+        <v>834</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C72" s="5"/>
+        <v>835</v>
+      </c>
+      <c r="C72" s="3"/>
+      <c r="E72" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F72" s="4" t="s">
-        <v>224</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>179</v>
+        <v>836</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C73" s="5"/>
+        <v>837</v>
+      </c>
+      <c r="C73" s="3"/>
+      <c r="E73" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F73" s="4" t="s">
-        <v>225</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="5"/>
+        <v>838</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="E74" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F74" s="4" t="s">
-        <v>226</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="5"/>
+        <v>840</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="C75" s="3"/>
+      <c r="E75" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F75" s="4" t="s">
-        <v>227</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B76" s="3"/>
-      <c r="C76" s="5"/>
+        <v>842</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="E76" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F76" s="4" t="s">
-        <v>228</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B77" s="3"/>
-      <c r="C77" s="5"/>
+        <v>844</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="E77" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F77" s="4" t="s">
-        <v>229</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B78" s="3"/>
-      <c r="C78" s="5"/>
+        <v>846</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>753</v>
+      </c>
       <c r="F78" s="4" t="s">
-        <v>230</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B79" s="3"/>
-      <c r="C79" s="5"/>
+        <v>849</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>851</v>
+      </c>
       <c r="E79" s="3" t="s">
-        <v>342</v>
+        <v>753</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>395</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>232</v>
+        <v>852</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C80" s="5"/>
+        <v>853</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>854</v>
+      </c>
       <c r="E80" s="3" t="s">
-        <v>343</v>
+        <v>753</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>396</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>233</v>
+        <v>855</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C81" s="5"/>
+        <v>856</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>857</v>
+      </c>
       <c r="E81" s="3" t="s">
-        <v>343</v>
+        <v>753</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>397</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>234</v>
+        <v>858</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="C82" s="5"/>
+        <v>859</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>860</v>
+      </c>
       <c r="E82" s="3" t="s">
-        <v>343</v>
+        <v>753</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>398</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>235</v>
+        <v>861</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C83" s="5"/>
+        <v>862</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>863</v>
+      </c>
       <c r="E83" s="3" t="s">
-        <v>344</v>
+        <v>753</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>399</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>236</v>
+        <v>864</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C84" s="5"/>
+        <v>865</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>866</v>
+      </c>
       <c r="E84" s="3" t="s">
-        <v>345</v>
+        <v>753</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>400</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>237</v>
+        <v>867</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C85" s="5"/>
+        <v>868</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>869</v>
+      </c>
       <c r="E85" s="3" t="s">
-        <v>345</v>
+        <v>753</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>401</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>238</v>
+        <v>870</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C86" s="5"/>
+        <v>871</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>872</v>
+      </c>
       <c r="E86" s="3" t="s">
-        <v>346</v>
+        <v>753</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>402</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>239</v>
+        <v>873</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C87" s="5"/>
+        <v>874</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>875</v>
+      </c>
       <c r="E87" s="3" t="s">
-        <v>346</v>
+        <v>753</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>403</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>240</v>
+        <v>876</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C88" s="5"/>
+        <v>877</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>878</v>
+      </c>
       <c r="E88" s="3" t="s">
-        <v>347</v>
+        <v>753</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>404</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>241</v>
+        <v>879</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C89" s="5"/>
+        <v>880</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>881</v>
+      </c>
       <c r="E89" s="3" t="s">
-        <v>347</v>
+        <v>753</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>405</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>242</v>
+        <v>882</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C90" s="5"/>
+        <v>883</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>884</v>
+      </c>
       <c r="E90" s="3" t="s">
-        <v>347</v>
+        <v>753</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>406</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>243</v>
+        <v>885</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C91" s="5"/>
+        <v>886</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>887</v>
+      </c>
       <c r="E91" s="3" t="s">
-        <v>347</v>
+        <v>753</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>407</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>244</v>
+        <v>888</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C92" s="5"/>
+        <v>847</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>889</v>
+      </c>
       <c r="E92" s="3" t="s">
-        <v>347</v>
+        <v>753</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>408</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B93" s="3"/>
-      <c r="C93" s="5"/>
+        <v>890</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>892</v>
+      </c>
       <c r="E93" s="3" t="s">
-        <v>347</v>
+        <v>753</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>409</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B94" s="3"/>
-      <c r="C94" s="5"/>
+        <v>893</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>895</v>
+      </c>
       <c r="E94" s="3" t="s">
-        <v>347</v>
+        <v>753</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>410</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>247</v>
+        <v>896</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C95" s="5"/>
+        <v>897</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>898</v>
+      </c>
       <c r="E95" s="3" t="s">
-        <v>348</v>
+        <v>753</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>411</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>247</v>
+        <v>899</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C96" s="5"/>
+        <v>900</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>901</v>
+      </c>
       <c r="E96" s="3" t="s">
-        <v>349</v>
+        <v>753</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>412</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>248</v>
+        <v>902</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C97" s="5"/>
+        <v>903</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>904</v>
+      </c>
       <c r="E97" s="3" t="s">
-        <v>350</v>
+        <v>753</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>413</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>249</v>
+        <v>905</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="C98" s="5"/>
+        <v>906</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>907</v>
+      </c>
       <c r="E98" s="3" t="s">
-        <v>351</v>
+        <v>753</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>414</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>250</v>
+        <v>908</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C99" s="5"/>
+        <v>909</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>910</v>
+      </c>
       <c r="E99" s="3" t="s">
-        <v>352</v>
+        <v>753</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>415</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>251</v>
+        <v>911</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C100" s="5"/>
+        <v>912</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>913</v>
+      </c>
       <c r="E100" s="3" t="s">
-        <v>353</v>
+        <v>753</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>416</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>252</v>
+        <v>914</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="C101" s="5"/>
+        <v>915</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>916</v>
+      </c>
       <c r="E101" s="3" t="s">
-        <v>354</v>
+        <v>753</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>417</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>253</v>
+        <v>917</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C102" s="5"/>
+        <v>918</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>919</v>
+      </c>
       <c r="E102" s="3" t="s">
-        <v>354</v>
+        <v>753</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>418</v>
+        <v>17</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B103" s="3"/>
-      <c r="C103" s="5"/>
+        <v>920</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>922</v>
+      </c>
       <c r="E103" s="3" t="s">
-        <v>355</v>
+        <v>753</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>419</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>255</v>
+        <v>923</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="C104" s="5"/>
+        <v>924</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>925</v>
+      </c>
       <c r="E104" s="3" t="s">
-        <v>356</v>
+        <v>753</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>420</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>256</v>
+        <v>926</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C105" s="5"/>
+        <v>927</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>928</v>
+      </c>
       <c r="E105" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>421</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>250</v>
+        <v>929</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="C106" s="5"/>
+        <v>930</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>931</v>
+      </c>
       <c r="E106" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>422</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>257</v>
+        <v>932</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C107" s="5"/>
+        <v>933</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>934</v>
+      </c>
       <c r="E107" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>423</v>
+        <v>22</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>257</v>
+        <v>935</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="C108" s="5"/>
+        <v>936</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>937</v>
+      </c>
       <c r="E108" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>424</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>258</v>
+        <v>938</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="C109" s="5"/>
+        <v>939</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>940</v>
+      </c>
       <c r="E109" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>425</v>
+        <v>24</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>255</v>
+        <v>941</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="C110" s="5"/>
+        <v>942</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>943</v>
+      </c>
       <c r="E110" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>426</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>259</v>
+        <v>944</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C111" s="5"/>
+        <v>945</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>946</v>
+      </c>
       <c r="E111" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>427</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>260</v>
+        <v>947</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C112" s="5"/>
+        <v>948</v>
+      </c>
+      <c r="C112" s="3"/>
       <c r="E112" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>428</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>261</v>
+        <v>949</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C113" s="5"/>
+        <v>950</v>
+      </c>
+      <c r="C113" s="3"/>
       <c r="E113" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>429</v>
+        <v>28</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="C114" s="5"/>
+        <v>951</v>
+      </c>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
       <c r="E114" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>430</v>
+        <v>29</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="C115" s="5"/>
+        <v>952</v>
+      </c>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
       <c r="E115" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>431</v>
+        <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C116" s="5"/>
+        <v>953</v>
+      </c>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
       <c r="E116" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>432</v>
+        <v>31</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="C117" s="5"/>
+        <v>954</v>
+      </c>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
       <c r="E117" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>433</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>392</v>
-      </c>
+        <v>955</v>
+      </c>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
       <c r="E118" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>434</v>
+        <v>33</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B119" s="3"/>
+        <v>956</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="C119" s="3"/>
       <c r="E119" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>435</v>
+        <v>34</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B120" s="3"/>
+        <v>958</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="C120" s="3"/>
       <c r="E120" s="3" t="s">
-        <v>357</v>
+        <v>753</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>436</v>
+        <v>35</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>268</v>
+        <v>99</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>358</v>
+        <v>100</v>
+      </c>
+      <c r="C121" s="5"/>
+      <c r="E121" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>437</v>
+        <v>184</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>269</v>
+        <v>101</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>324</v>
+        <v>102</v>
+      </c>
+      <c r="C122" s="5"/>
+      <c r="E122" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>438</v>
+        <v>185</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>270</v>
+        <v>103</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>324</v>
+        <v>104</v>
+      </c>
+      <c r="C123" s="5"/>
+      <c r="E123" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>439</v>
+        <v>186</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>271</v>
+        <v>105</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>324</v>
+        <v>106</v>
+      </c>
+      <c r="C124" s="5"/>
+      <c r="E124" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>440</v>
+        <v>187</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>265</v>
+        <v>107</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>324</v>
+        <v>108</v>
+      </c>
+      <c r="C125" s="5"/>
+      <c r="E125" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>441</v>
+        <v>188</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
-        <v>272</v>
+        <v>109</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>325</v>
+        <v>110</v>
+      </c>
+      <c r="C126" s="5"/>
+      <c r="E126" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>442</v>
+        <v>189</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>273</v>
+        <v>111</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>325</v>
+        <v>112</v>
+      </c>
+      <c r="C127" s="5"/>
+      <c r="E127" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>443</v>
+        <v>190</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>274</v>
+        <v>113</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>325</v>
+        <v>114</v>
+      </c>
+      <c r="C128" s="5"/>
+      <c r="E128" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>444</v>
+        <v>191</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>275</v>
+        <v>115</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>326</v>
+        <v>116</v>
+      </c>
+      <c r="C129" s="5"/>
+      <c r="E129" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>445</v>
+        <v>192</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>276</v>
+        <v>117</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>327</v>
+        <v>118</v>
+      </c>
+      <c r="C130" s="5"/>
+      <c r="E130" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>446</v>
+        <v>193</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>328</v>
+        <v>120</v>
+      </c>
+      <c r="C131" s="5"/>
+      <c r="E131" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>447</v>
+        <v>194</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>269</v>
+        <v>121</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>328</v>
+        <v>122</v>
+      </c>
+      <c r="C132" s="5"/>
+      <c r="E132" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>448</v>
+        <v>195</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>240</v>
+        <v>123</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="E133" s="3" t="s">
-        <v>328</v>
+        <v>124</v>
+      </c>
+      <c r="C133" s="5"/>
+      <c r="E133" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>449</v>
+        <v>196</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>270</v>
+        <v>125</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E134" s="3" t="s">
-        <v>329</v>
+        <v>126</v>
+      </c>
+      <c r="C134" s="5"/>
+      <c r="E134" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>450</v>
+        <v>197</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>278</v>
+        <v>127</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>330</v>
+        <v>128</v>
+      </c>
+      <c r="C135" s="5"/>
+      <c r="E135" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>451</v>
+        <v>198</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>279</v>
+        <v>129</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E136" s="3" t="s">
-        <v>331</v>
+        <v>130</v>
+      </c>
+      <c r="C136" s="5"/>
+      <c r="E136" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>452</v>
+        <v>199</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>280</v>
+        <v>131</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>332</v>
+        <v>132</v>
+      </c>
+      <c r="C137" s="5"/>
+      <c r="E137" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>453</v>
+        <v>200</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>281</v>
+        <v>133</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>332</v>
+        <v>134</v>
+      </c>
+      <c r="C138" s="5"/>
+      <c r="E138" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>454</v>
+        <v>201</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>282</v>
+        <v>135</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="E139" s="3" t="s">
-        <v>333</v>
+        <v>136</v>
+      </c>
+      <c r="C139" s="5"/>
+      <c r="E139" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>455</v>
+        <v>202</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>283</v>
+        <v>137</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>333</v>
+        <v>138</v>
+      </c>
+      <c r="C140" s="5"/>
+      <c r="E140" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>456</v>
+        <v>203</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>284</v>
+        <v>139</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="E141" s="3" t="s">
-        <v>334</v>
+        <v>140</v>
+      </c>
+      <c r="C141" s="5"/>
+      <c r="E141" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>457</v>
+        <v>204</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>237</v>
+        <v>141</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="E142" s="3" t="s">
-        <v>334</v>
+        <v>142</v>
+      </c>
+      <c r="C142" s="5"/>
+      <c r="E142" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>458</v>
+        <v>205</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>285</v>
+        <v>143</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="E143" s="3" t="s">
-        <v>335</v>
+        <v>144</v>
+      </c>
+      <c r="C143" s="5"/>
+      <c r="E143" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>459</v>
+        <v>206</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>286</v>
+        <v>145</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="E144" s="3" t="s">
-        <v>335</v>
+        <v>146</v>
+      </c>
+      <c r="C144" s="5"/>
+      <c r="E144" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>460</v>
+        <v>207</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>287</v>
+        <v>147</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>336</v>
+        <v>148</v>
+      </c>
+      <c r="C145" s="5"/>
+      <c r="E145" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>461</v>
+        <v>208</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>288</v>
+        <v>149</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>337</v>
+        <v>150</v>
+      </c>
+      <c r="C146" s="5"/>
+      <c r="E146" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>462</v>
+        <v>209</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>289</v>
+        <v>151</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>338</v>
+        <v>152</v>
+      </c>
+      <c r="C147" s="5"/>
+      <c r="E147" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>463</v>
+        <v>210</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
-        <v>290</v>
+        <v>153</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="E148" s="3" t="s">
-        <v>339</v>
+        <v>154</v>
+      </c>
+      <c r="C148" s="5"/>
+      <c r="E148" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>464</v>
+        <v>211</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>291</v>
+        <v>155</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>339</v>
+        <v>156</v>
+      </c>
+      <c r="C149" s="5"/>
+      <c r="E149" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>465</v>
+        <v>212</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="E150" s="3" t="s">
-        <v>339</v>
+        <v>158</v>
+      </c>
+      <c r="C150" s="5"/>
+      <c r="E150" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>466</v>
+        <v>213</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>292</v>
+        <v>159</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E151" s="3" t="s">
-        <v>340</v>
+        <v>160</v>
+      </c>
+      <c r="C151" s="5"/>
+      <c r="E151" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>467</v>
+        <v>214</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
-        <v>278</v>
+        <v>161</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>340</v>
+        <v>162</v>
+      </c>
+      <c r="C152" s="5"/>
+      <c r="E152" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>468</v>
+        <v>215</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>293</v>
+        <v>163</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E153" s="3" t="s">
-        <v>341</v>
+        <v>164</v>
+      </c>
+      <c r="C153" s="5"/>
+      <c r="E153" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>469</v>
+        <v>216</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>470</v>
+        <v>165</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="E154" s="3" t="s">
-        <v>497</v>
+        <v>166</v>
+      </c>
+      <c r="C154" s="5"/>
+      <c r="E154" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>674</v>
+        <v>217</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>471</v>
+        <v>167</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>497</v>
+        <v>168</v>
+      </c>
+      <c r="C155" s="5"/>
+      <c r="E155" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>675</v>
+        <v>218</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>472</v>
+        <v>169</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>497</v>
+        <v>170</v>
+      </c>
+      <c r="C156" s="5"/>
+      <c r="E156" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>676</v>
+        <v>219</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>473</v>
+        <v>171</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="E157" s="3" t="s">
-        <v>497</v>
+        <v>172</v>
+      </c>
+      <c r="C157" s="5"/>
+      <c r="E157" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>677</v>
+        <v>220</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>474</v>
+        <v>173</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="E158" s="3" t="s">
-        <v>497</v>
+        <v>174</v>
+      </c>
+      <c r="C158" s="5"/>
+      <c r="E158" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>678</v>
+        <v>221</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>475</v>
+        <v>175</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="E159" s="3" t="s">
-        <v>497</v>
+        <v>176</v>
+      </c>
+      <c r="C159" s="5"/>
+      <c r="E159" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>679</v>
+        <v>222</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
-        <v>476</v>
+        <v>177</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="E160" s="3" t="s">
-        <v>497</v>
+        <v>178</v>
+      </c>
+      <c r="C160" s="5"/>
+      <c r="E160" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>680</v>
+        <v>223</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="E161" s="3" t="s">
-        <v>497</v>
+        <v>179</v>
+      </c>
+      <c r="B161" s="3"/>
+      <c r="C161" s="5"/>
+      <c r="E161" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>681</v>
+        <v>224</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="E162" s="3" t="s">
-        <v>497</v>
+        <v>180</v>
+      </c>
+      <c r="B162" s="3"/>
+      <c r="C162" s="5"/>
+      <c r="E162" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>682</v>
+        <v>225</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="E163" s="3" t="s">
-        <v>497</v>
+        <v>181</v>
+      </c>
+      <c r="B163" s="3"/>
+      <c r="C163" s="5"/>
+      <c r="E163" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>683</v>
+        <v>226</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="E164" s="3" t="s">
-        <v>497</v>
+        <v>182</v>
+      </c>
+      <c r="B164" s="3"/>
+      <c r="C164" s="5"/>
+      <c r="E164" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>684</v>
+        <v>227</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="E165" s="3" t="s">
-        <v>497</v>
+        <v>183</v>
+      </c>
+      <c r="B165" s="3"/>
+      <c r="C165" s="5"/>
+      <c r="E165" s="2" t="s">
+        <v>1047</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>685</v>
+        <v>228</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>511</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="B166" s="3"/>
+      <c r="C166" s="5"/>
       <c r="E166" s="3" t="s">
-        <v>497</v>
+        <v>340</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>686</v>
+        <v>393</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>483</v>
+        <v>230</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>512</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="C167" s="5"/>
       <c r="E167" s="3" t="s">
-        <v>497</v>
+        <v>341</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>687</v>
+        <v>394</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
-        <v>484</v>
+        <v>231</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>513</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="C168" s="5"/>
       <c r="E168" s="3" t="s">
-        <v>497</v>
+        <v>341</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>688</v>
+        <v>395</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>485</v>
+        <v>232</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>514</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="C169" s="5"/>
       <c r="E169" s="3" t="s">
-        <v>497</v>
+        <v>341</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>689</v>
+        <v>396</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
-        <v>486</v>
+        <v>233</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>515</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="C170" s="5"/>
       <c r="E170" s="3" t="s">
-        <v>497</v>
+        <v>342</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>690</v>
+        <v>397</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>487</v>
+        <v>234</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>516</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="C171" s="5"/>
       <c r="E171" s="3" t="s">
-        <v>497</v>
+        <v>343</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>691</v>
+        <v>398</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
-        <v>488</v>
+        <v>235</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>517</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="C172" s="5"/>
       <c r="E172" s="3" t="s">
-        <v>497</v>
+        <v>343</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>692</v>
+        <v>399</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>489</v>
+        <v>236</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>518</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="C173" s="5"/>
       <c r="E173" s="3" t="s">
-        <v>497</v>
+        <v>344</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>693</v>
+        <v>400</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
-        <v>490</v>
+        <v>237</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>519</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="C174" s="5"/>
       <c r="E174" s="3" t="s">
-        <v>497</v>
+        <v>344</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>694</v>
+        <v>401</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>491</v>
+        <v>238</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>520</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="C175" s="5"/>
       <c r="E175" s="3" t="s">
-        <v>497</v>
+        <v>345</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>695</v>
+        <v>402</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
-        <v>492</v>
+        <v>239</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>521</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="C176" s="5"/>
       <c r="E176" s="3" t="s">
-        <v>497</v>
+        <v>345</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>696</v>
+        <v>403</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>493</v>
+        <v>240</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>522</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="C177" s="5"/>
       <c r="E177" s="3" t="s">
-        <v>497</v>
+        <v>345</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>697</v>
+        <v>404</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>494</v>
+        <v>241</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>523</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="C178" s="5"/>
       <c r="E178" s="3" t="s">
-        <v>497</v>
+        <v>345</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>698</v>
+        <v>405</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>495</v>
+        <v>242</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>524</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="C179" s="5"/>
       <c r="E179" s="3" t="s">
-        <v>497</v>
+        <v>345</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>699</v>
+        <v>406</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>525</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="B180" s="3"/>
+      <c r="C180" s="5"/>
       <c r="E180" s="3" t="s">
-        <v>497</v>
+        <v>345</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>700</v>
+        <v>407</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>526</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="B181" s="3"/>
+      <c r="C181" s="5"/>
       <c r="E181" s="3" t="s">
-        <v>498</v>
+        <v>345</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>701</v>
+        <v>408</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>528</v>
+        <v>245</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>570</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="C182" s="5"/>
       <c r="E182" s="3" t="s">
-        <v>527</v>
+        <v>346</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>622</v>
+        <v>409</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>529</v>
+        <v>245</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>571</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="C183" s="5"/>
       <c r="E183" s="3" t="s">
-        <v>527</v>
+        <v>347</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>623</v>
+        <v>410</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>530</v>
+        <v>246</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>572</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="C184" s="5"/>
       <c r="E184" s="3" t="s">
-        <v>527</v>
+        <v>348</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>624</v>
+        <v>411</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>530</v>
+        <v>247</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>573</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="C185" s="5"/>
       <c r="E185" s="3" t="s">
-        <v>527</v>
+        <v>349</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>625</v>
+        <v>412</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>531</v>
+        <v>248</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>574</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="C186" s="5"/>
       <c r="E186" s="3" t="s">
-        <v>527</v>
+        <v>350</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>626</v>
+        <v>413</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>531</v>
+        <v>249</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>575</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="C187" s="5"/>
       <c r="E187" s="3" t="s">
-        <v>527</v>
+        <v>351</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>627</v>
+        <v>414</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
-        <v>532</v>
+        <v>250</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>576</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="C188" s="5"/>
       <c r="E188" s="3" t="s">
-        <v>527</v>
+        <v>352</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>628</v>
+        <v>415</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>533</v>
+        <v>251</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>577</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="C189" s="5"/>
       <c r="E189" s="3" t="s">
-        <v>527</v>
+        <v>352</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>629</v>
+        <v>416</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="B190" s="3" t="s">
-        <v>578</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="B190" s="3"/>
+      <c r="C190" s="5"/>
       <c r="E190" s="3" t="s">
-        <v>527</v>
+        <v>353</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>630</v>
+        <v>417</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>534</v>
+        <v>253</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>579</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="C191" s="5"/>
       <c r="E191" s="3" t="s">
-        <v>527</v>
+        <v>354</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>631</v>
+        <v>418</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
-        <v>535</v>
+        <v>254</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>580</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="C192" s="5"/>
       <c r="E192" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>632</v>
+        <v>419</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>536</v>
+        <v>248</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>581</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="C193" s="5"/>
       <c r="E193" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>633</v>
+        <v>420</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>537</v>
+        <v>255</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>582</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="C194" s="5"/>
       <c r="E194" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>634</v>
+        <v>421</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>538</v>
+        <v>255</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>583</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="C195" s="5"/>
       <c r="E195" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>635</v>
+        <v>422</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
-        <v>539</v>
+        <v>256</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>584</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="C196" s="5"/>
       <c r="E196" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>636</v>
+        <v>423</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>540</v>
+        <v>253</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>585</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="C197" s="5"/>
       <c r="E197" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>637</v>
+        <v>424</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
-        <v>540</v>
+        <v>257</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>586</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="C198" s="5"/>
       <c r="E198" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>638</v>
+        <v>425</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>541</v>
+        <v>258</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>587</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="C199" s="5"/>
       <c r="E199" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>639</v>
+        <v>426</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
-        <v>541</v>
+        <v>259</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>588</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="C200" s="5"/>
       <c r="E200" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>640</v>
+        <v>427</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>542</v>
+        <v>260</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>589</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="C201" s="5"/>
       <c r="E201" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>641</v>
+        <v>428</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
-        <v>543</v>
+        <v>261</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>590</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="C202" s="5"/>
       <c r="E202" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>642</v>
+        <v>429</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>544</v>
+        <v>262</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>591</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="C203" s="5"/>
       <c r="E203" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>643</v>
+        <v>430</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>545</v>
+        <v>263</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>592</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="C204" s="5"/>
       <c r="E204" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>644</v>
+        <v>431</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>545</v>
+        <v>247</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>593</v>
+        <v>390</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>645</v>
+        <v>432</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>594</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="B206" s="3"/>
       <c r="E206" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>646</v>
+        <v>433</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>595</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="B207" s="3"/>
       <c r="E207" s="3" t="s">
-        <v>527</v>
+        <v>355</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>647</v>
+        <v>434</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
-        <v>548</v>
+        <v>266</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>596</v>
+        <v>391</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>527</v>
+        <v>356</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>648</v>
+        <v>435</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>549</v>
+        <v>267</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>597</v>
+        <v>392</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>527</v>
+        <v>322</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>649</v>
+        <v>436</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
-        <v>550</v>
+        <v>268</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>598</v>
+        <v>292</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>527</v>
+        <v>322</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>650</v>
+        <v>437</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>551</v>
+        <v>269</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>599</v>
+        <v>293</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>527</v>
+        <v>322</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>651</v>
+        <v>438</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
-        <v>552</v>
+        <v>263</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>600</v>
+        <v>294</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>527</v>
+        <v>322</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>652</v>
+        <v>439</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>552</v>
+        <v>270</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>601</v>
+        <v>295</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>527</v>
+        <v>323</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>653</v>
+        <v>440</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
-        <v>553</v>
+        <v>271</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>602</v>
+        <v>296</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>527</v>
+        <v>323</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>654</v>
+        <v>441</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>554</v>
+        <v>272</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>603</v>
+        <v>297</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>527</v>
+        <v>323</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>655</v>
+        <v>442</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
-        <v>555</v>
+        <v>273</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>604</v>
+        <v>298</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>527</v>
+        <v>324</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>656</v>
+        <v>443</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>556</v>
+        <v>274</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>605</v>
+        <v>299</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>527</v>
+        <v>325</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>657</v>
+        <v>444</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
-        <v>557</v>
+        <v>275</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>606</v>
+        <v>300</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>527</v>
+        <v>326</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>658</v>
+        <v>445</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>557</v>
+        <v>267</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>607</v>
+        <v>301</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>527</v>
+        <v>326</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>659</v>
+        <v>446</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
-        <v>558</v>
+        <v>238</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>608</v>
+        <v>302</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>527</v>
+        <v>326</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>660</v>
+        <v>447</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>559</v>
+        <v>268</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>609</v>
+        <v>303</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>527</v>
+        <v>327</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>661</v>
+        <v>448</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
-        <v>560</v>
+        <v>276</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>610</v>
+        <v>304</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>527</v>
+        <v>328</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>662</v>
+        <v>449</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>561</v>
+        <v>277</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>611</v>
+        <v>305</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>527</v>
+        <v>329</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>663</v>
+        <v>450</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
-        <v>562</v>
+        <v>278</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>612</v>
+        <v>306</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>527</v>
+        <v>330</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>664</v>
+        <v>451</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>563</v>
+        <v>279</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>613</v>
+        <v>307</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>527</v>
+        <v>330</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>665</v>
+        <v>452</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
-        <v>564</v>
+        <v>280</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>614</v>
+        <v>308</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>527</v>
+        <v>331</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>666</v>
+        <v>453</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>565</v>
+        <v>281</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>615</v>
+        <v>309</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>527</v>
+        <v>331</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>667</v>
+        <v>454</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
-        <v>566</v>
+        <v>282</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>616</v>
+        <v>310</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>527</v>
+        <v>332</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>668</v>
+        <v>455</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>566</v>
+        <v>235</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>617</v>
+        <v>311</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>527</v>
+        <v>332</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>669</v>
+        <v>456</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
-        <v>567</v>
+        <v>283</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>618</v>
+        <v>312</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>527</v>
+        <v>333</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>670</v>
+        <v>457</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>568</v>
+        <v>284</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>619</v>
+        <v>313</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>527</v>
+        <v>333</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>671</v>
+        <v>458</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
-        <v>568</v>
+        <v>285</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>620</v>
+        <v>314</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>527</v>
+        <v>334</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>672</v>
+        <v>459</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>569</v>
+        <v>286</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>621</v>
+        <v>315</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>527</v>
+        <v>335</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>673</v>
+        <v>460</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
-        <v>703</v>
+        <v>287</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>704</v>
+        <v>316</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>702</v>
+        <v>336</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>737</v>
+        <v>461</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>705</v>
+        <v>288</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>706</v>
+        <v>317</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>702</v>
+        <v>337</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>738</v>
+        <v>462</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
-        <v>707</v>
+        <v>289</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>708</v>
+        <v>318</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>702</v>
+        <v>337</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>739</v>
+        <v>463</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>709</v>
+        <v>235</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>710</v>
+        <v>319</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>702</v>
+        <v>337</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>740</v>
+        <v>464</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
-        <v>711</v>
+        <v>290</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>712</v>
+        <v>320</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>702</v>
+        <v>338</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>741</v>
+        <v>465</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>713</v>
+        <v>276</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>714</v>
+        <v>304</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>702</v>
+        <v>338</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>742</v>
+        <v>466</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
-        <v>715</v>
+        <v>291</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>716</v>
+        <v>321</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>702</v>
+        <v>339</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>743</v>
+        <v>467</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>717</v>
+        <v>468</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>718</v>
+        <v>497</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>702</v>
+        <v>495</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>744</v>
+        <v>672</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
-        <v>719</v>
+        <v>469</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>720</v>
+        <v>498</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>702</v>
+        <v>495</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>745</v>
+        <v>673</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>721</v>
+        <v>470</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>722</v>
+        <v>499</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>702</v>
+        <v>495</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>746</v>
+        <v>674</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
-        <v>723</v>
+        <v>471</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>724</v>
+        <v>500</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>702</v>
+        <v>495</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>747</v>
+        <v>675</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>725</v>
+        <v>472</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>726</v>
+        <v>501</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>702</v>
+        <v>495</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>748</v>
+        <v>676</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
-        <v>727</v>
+        <v>473</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>728</v>
+        <v>502</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>702</v>
+        <v>495</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>749</v>
+        <v>677</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>729</v>
+        <v>474</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>730</v>
+        <v>503</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>702</v>
+        <v>495</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>750</v>
+        <v>678</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
-        <v>731</v>
+        <v>475</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>732</v>
+        <v>504</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>702</v>
+        <v>495</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>751</v>
+        <v>679</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>733</v>
+        <v>476</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>734</v>
+        <v>505</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>702</v>
+        <v>495</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>752</v>
+        <v>680</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F250" s="4" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A251" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F251" s="4" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A252" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F252" s="4" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A253" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A254" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F254" s="4" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A255" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F255" s="4" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A256" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F256" s="4" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A257" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F257" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A258" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F258" s="4" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A259" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F259" s="4" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A260" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F260" s="4" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A261" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F261" s="4" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A262" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="E262" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F262" s="4" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A263" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F263" s="4" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A264" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="E264" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A265" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A266" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="E266" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A267" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F267" s="4" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A268" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A269" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F269" s="4" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A270" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F270" s="4" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A271" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F271" s="4" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A272" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="E272" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F272" s="4" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A273" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="E273" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F273" s="4" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A274" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="E274" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A275" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F275" s="4" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A276" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="E276" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A277" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="E277" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F277" s="4" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A278" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="E278" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F278" s="4" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A279" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F279" s="4" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A280" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="E280" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F280" s="4" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A281" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="E281" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F281" s="4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A282" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F282" s="4" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A283" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="E283" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F283" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A284" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="E284" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F284" s="4" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A285" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="E285" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A286" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="B286" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="E286" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A287" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="B287" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="E287" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F287" s="4" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A288" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="E288" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F288" s="4" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A289" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B289" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="E289" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F289" s="4" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A290" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="B290" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="E290" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F290" s="4" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A291" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="E291" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F291" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A292" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="E292" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F292" s="4" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A293" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="E293" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F293" s="4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A294" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="E294" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F294" s="4" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A295" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="E295" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F295" s="4" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A296" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="E296" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F296" s="4" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A297" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="E297" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F297" s="4" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A298" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="B298" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="E298" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A299" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B299" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="E299" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A300" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="E300" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A301" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="E301" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F301" s="4" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A302" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="E302" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F302" s="4" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A303" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="B303" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F303" s="4" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A304" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B304" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="E304" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F304" s="4" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A305" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B305" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="E305" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F305" s="4" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A306" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B306" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="E306" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F306" s="4" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A307" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B307" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="E307" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A308" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="B308" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E308" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A309" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="B309" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="E309" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A310" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B310" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="E310" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A311" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="E311" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A312" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B312" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="E312" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A313" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B313" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="E313" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F313" s="4" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A314" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="B314" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="E314" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A315" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B315" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="E315" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F315" s="4" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A316" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B316" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="E316" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F316" s="4" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A317" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="B317" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="E317" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A318" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="E318" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A319" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B319" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="E319" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A320" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B320" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="E320" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A321" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="E321" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F321" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="B250" s="3" t="s">
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A322" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="B322" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="E322" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F322" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="E250" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="F250" s="4" t="s">
-        <v>753</v>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A323" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B323" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="E323" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F323" s="4" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A324" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B324" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E324" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F324" s="4" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A325" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="B325" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="E325" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F325" s="4" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A326" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="B326" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="E326" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F326" s="4" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A327" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B327" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="E327" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F327" s="4" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A328" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="B328" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="E328" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F328" s="4" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A329" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="B329" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="E329" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F329" s="4" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A330" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="B330" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="E330" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F330" s="4" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A331" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B331" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="E331" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F331" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A332" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="E332" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F332" s="4" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A333" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="B333" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="E333" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F333" s="4" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A334" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="B334" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="E334" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F334" s="4" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A335" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="B335" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="E335" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F335" s="4" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A336" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="B336" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="E336" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F336" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A337" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="E337" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F337" s="4" t="s">
+        <v>751</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{3C569D09-5588-464D-932A-F90D914FB1E6}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{8A47ACE0-4459-43D7-B248-DC0952C7CCAD}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{A45DDBB5-CDCB-46A8-B7FD-3E24C1A300C0}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{A1CACEA7-2AA1-44C9-AE24-6D34A45AB1CD}"/>
-    <hyperlink ref="F6" r:id="rId5" xr:uid="{C0B85810-8D6C-45C3-A57A-356ED0B708D6}"/>
-    <hyperlink ref="F7" r:id="rId6" xr:uid="{0C7BF2D6-DDCD-454F-B957-A08BF25DC8B6}"/>
-    <hyperlink ref="F8" r:id="rId7" xr:uid="{55B7B683-1C32-461A-A34A-23C7A6748DEA}"/>
-    <hyperlink ref="F9" r:id="rId8" xr:uid="{5B980215-3D0F-4DF5-8D18-18EDF6711C83}"/>
-    <hyperlink ref="F10" r:id="rId9" xr:uid="{D5ECFCAA-D658-4DFE-955E-C7505710FE78}"/>
-    <hyperlink ref="F11" r:id="rId10" xr:uid="{AA5E0DE8-2039-480E-91E9-A7AF75E52871}"/>
-    <hyperlink ref="F12" r:id="rId11" xr:uid="{85A1B8DF-2D7A-4AB5-BF3C-36F9D9CBF381}"/>
-    <hyperlink ref="F13" r:id="rId12" xr:uid="{7FD2E7F9-0D23-4D6F-9352-EFE08241791D}"/>
-    <hyperlink ref="F14" r:id="rId13" xr:uid="{B0963F97-B27F-4F33-A718-B882982852B8}"/>
-    <hyperlink ref="F15" r:id="rId14" xr:uid="{40C1EE79-996A-431B-A1D6-9EDF6F7B2DC1}"/>
-    <hyperlink ref="F16" r:id="rId15" xr:uid="{18A56014-556F-446E-A676-E76827381A96}"/>
-    <hyperlink ref="F17" r:id="rId16" xr:uid="{54AF9E8F-2D6F-48EC-BB9E-2988F8644546}"/>
-    <hyperlink ref="F18" r:id="rId17" xr:uid="{5272C369-CB65-4D1E-923C-C6400F3CDEB2}"/>
-    <hyperlink ref="F19" r:id="rId18" xr:uid="{FC8C68D0-0DF9-45A9-A844-6069766DA89B}"/>
-    <hyperlink ref="F20" r:id="rId19" xr:uid="{7BAF8941-74C4-4781-9D32-003C778939D9}"/>
-    <hyperlink ref="F21" r:id="rId20" xr:uid="{740428DA-E112-4D14-8C56-D64585D0C15B}"/>
-    <hyperlink ref="F22" r:id="rId21" xr:uid="{F59523AB-9DCC-4A5F-92FD-EE1B10E36E1B}"/>
-    <hyperlink ref="F23" r:id="rId22" xr:uid="{BE3E7FD9-BA16-491A-8385-64ACB882454D}"/>
-    <hyperlink ref="F24" r:id="rId23" xr:uid="{EF2E1B1F-F8F2-46F8-A45F-F6A2ED147DDE}"/>
-    <hyperlink ref="F25" r:id="rId24" xr:uid="{3555590B-1692-4285-A1E7-E345D9F63F69}"/>
-    <hyperlink ref="F26" r:id="rId25" xr:uid="{14B2A148-882A-45BA-A4BC-A7F5F8CF1B4E}"/>
-    <hyperlink ref="F27" r:id="rId26" xr:uid="{BA6AA541-C005-43D2-89AD-0F980522114A}"/>
-    <hyperlink ref="F28" r:id="rId27" xr:uid="{B531D9D9-BDE8-4BB7-B043-9DDAA3DCE3DB}"/>
-    <hyperlink ref="F29" r:id="rId28" xr:uid="{8D20F1AE-8716-43F2-8C96-DD450362E0F8}"/>
-    <hyperlink ref="F30" r:id="rId29" xr:uid="{7BB55D7E-FE12-4268-86F8-33E50C23CFE5}"/>
-    <hyperlink ref="F31" r:id="rId30" xr:uid="{1523BD83-3475-4F82-9FA4-7F71B4441700}"/>
-    <hyperlink ref="F32" r:id="rId31" xr:uid="{D728978A-A248-4D67-80B0-20544CFFBFA6}"/>
-    <hyperlink ref="F33" r:id="rId32" xr:uid="{25B7467E-E690-42A9-BC9A-6A48DBAB8914}"/>
-    <hyperlink ref="F34" r:id="rId33" xr:uid="{2F48726D-DE6A-4098-BE7D-5BACCC8FC40A}"/>
-    <hyperlink ref="F35" r:id="rId34" xr:uid="{F3DC5606-9A2B-4B27-888E-2418DBD63197}"/>
-    <hyperlink ref="F36" r:id="rId35" xr:uid="{1A77C4B1-3EBF-4996-8BA5-54115DCC6DB4}"/>
-    <hyperlink ref="F37" r:id="rId36" xr:uid="{DB555C1A-23E1-4927-9647-7C6892E4C9C7}"/>
-    <hyperlink ref="F38" r:id="rId37" xr:uid="{33661F8A-1BC9-417D-99B3-DC93198874DE}"/>
-    <hyperlink ref="F39" r:id="rId38" xr:uid="{192DE853-AD34-43CA-A63F-E85114AD4EA0}"/>
-    <hyperlink ref="F40" r:id="rId39" xr:uid="{120E2455-BB40-4E29-A234-A4B7E792FE52}"/>
-    <hyperlink ref="F41" r:id="rId40" xr:uid="{1443E8F9-88EF-4C2B-A276-23E530539E9E}"/>
-    <hyperlink ref="F42" r:id="rId41" xr:uid="{E7CEA036-13F4-4AAC-A555-2FFE21E0C2B8}"/>
-    <hyperlink ref="F43" r:id="rId42" xr:uid="{92496332-5A82-488E-A37E-5592FCE49A81}"/>
-    <hyperlink ref="F44" r:id="rId43" xr:uid="{A0653FC6-F81B-47CA-A38B-BB1D7D8780AB}"/>
-    <hyperlink ref="F45" r:id="rId44" xr:uid="{F5BF4D55-CEE6-4250-9B16-AC2891C0A711}"/>
-    <hyperlink ref="F46" r:id="rId45" xr:uid="{68E21E8B-2406-448E-BB39-B787D1282FA1}"/>
-    <hyperlink ref="F47" r:id="rId46" xr:uid="{C2C55E82-ED9F-4FFA-A073-7DC869302C16}"/>
-    <hyperlink ref="F48" r:id="rId47" xr:uid="{4EAD4B84-80BA-4CC7-BD19-A32B04E8286F}"/>
-    <hyperlink ref="F49" r:id="rId48" xr:uid="{71AC19CA-92E6-49F9-BED3-CA495F366A27}"/>
-    <hyperlink ref="F50" r:id="rId49" xr:uid="{00E6714E-2AC2-46E3-9D9F-9C8DCAFD8C22}"/>
-    <hyperlink ref="F51" r:id="rId50" xr:uid="{AB2C6C29-2033-4459-95EA-6131071555ED}"/>
-    <hyperlink ref="F52" r:id="rId51" xr:uid="{04FD38F5-886B-410E-8338-BE423E77A551}"/>
-    <hyperlink ref="F53" r:id="rId52" xr:uid="{46C219A9-8A37-4A38-8BE2-31449600C9CA}"/>
-    <hyperlink ref="F54" r:id="rId53" xr:uid="{A4FCB636-86E3-402A-87E0-87E9BA4AEB41}"/>
-    <hyperlink ref="F55" r:id="rId54" xr:uid="{D96AABDB-3F6C-4B7E-9065-4389E1536714}"/>
-    <hyperlink ref="F56" r:id="rId55" xr:uid="{775F3009-BB92-4337-B30F-6702A68EFCA3}"/>
-    <hyperlink ref="F57" r:id="rId56" xr:uid="{4052F6BF-CA0D-45FA-B208-BDE51EE65CB4}"/>
-    <hyperlink ref="F58" r:id="rId57" xr:uid="{CCDC01A5-FEA2-4076-85E1-6C44FBD6C90A}"/>
-    <hyperlink ref="F59" r:id="rId58" xr:uid="{D31553ED-97EA-4017-B69C-127C4E539342}"/>
-    <hyperlink ref="F60" r:id="rId59" xr:uid="{A34382CC-3807-4DAD-A391-229E3068D20E}"/>
-    <hyperlink ref="F61" r:id="rId60" xr:uid="{D5D838C4-84B9-4893-8081-FD076E65D42D}"/>
-    <hyperlink ref="F62" r:id="rId61" xr:uid="{372D6C7C-57A1-4E5A-8FCA-C2BD42179B4C}"/>
-    <hyperlink ref="F63" r:id="rId62" xr:uid="{26F4CB51-8E73-4DD6-B36B-7D9E3532FACA}"/>
-    <hyperlink ref="F64" r:id="rId63" xr:uid="{28E3DA9C-8B99-4871-9FD0-8DBA1F52D164}"/>
-    <hyperlink ref="F65" r:id="rId64" xr:uid="{F221B864-0319-4744-8F5C-74DFBBD9ECA7}"/>
-    <hyperlink ref="F66" r:id="rId65" xr:uid="{2D863332-43A9-4835-9018-6C6225BAD913}"/>
-    <hyperlink ref="F67" r:id="rId66" xr:uid="{8ABCCB9C-AB49-4FB0-B2C4-669FD2A169BF}"/>
-    <hyperlink ref="F68" r:id="rId67" xr:uid="{4EB52813-3D3C-4F1F-9712-9A07F774A538}"/>
-    <hyperlink ref="F69" r:id="rId68" xr:uid="{52D9EF13-2183-4310-8C32-B2C6A2C08567}"/>
-    <hyperlink ref="F70" r:id="rId69" xr:uid="{A4411235-2A13-4120-A1DD-E52352CFC475}"/>
-    <hyperlink ref="F71" r:id="rId70" xr:uid="{20112E1E-36A7-49B0-BC59-7AB1EF3FBB2A}"/>
-    <hyperlink ref="F72" r:id="rId71" xr:uid="{4E175341-6D90-4C16-9BD9-DD27F4F88C73}"/>
-    <hyperlink ref="F73" r:id="rId72" xr:uid="{834BAFD9-DA29-4D56-BC7B-97B850C5B365}"/>
-    <hyperlink ref="F74" r:id="rId73" xr:uid="{BD779373-AC8C-41E2-98ED-E8D18BBA663E}"/>
-    <hyperlink ref="F75" r:id="rId74" xr:uid="{24CF6F19-C969-4937-9966-220089144F6B}"/>
-    <hyperlink ref="F76" r:id="rId75" xr:uid="{7EABD7FB-999B-4734-B105-231100FF8189}"/>
-    <hyperlink ref="F77" r:id="rId76" xr:uid="{474F7FAB-D2DA-4694-99EE-DD8310E2F160}"/>
-    <hyperlink ref="F78" r:id="rId77" xr:uid="{8E164687-D84D-4A4D-AE50-E53CD426CA64}"/>
-    <hyperlink ref="F79" r:id="rId78" xr:uid="{57F15978-1279-4A0F-A215-4906CA1FD882}"/>
-    <hyperlink ref="F80" r:id="rId79" xr:uid="{67474A5D-2B34-4EE2-A19E-F5C77A48AD43}"/>
-    <hyperlink ref="F81" r:id="rId80" xr:uid="{1E95D132-2A35-447E-B877-2D34495278B4}"/>
-    <hyperlink ref="F82" r:id="rId81" xr:uid="{D34E7BDD-E93E-4C88-92F5-D432227DE455}"/>
-    <hyperlink ref="F83" r:id="rId82" xr:uid="{C12907DC-6C9E-4977-A538-A3F744F8AA91}"/>
-    <hyperlink ref="F84" r:id="rId83" xr:uid="{B245579F-EA5C-4935-830B-94FC23CDA18F}"/>
-    <hyperlink ref="F85" r:id="rId84" xr:uid="{073D4EE8-9D0C-40B6-9B55-B6B321685ECB}"/>
-    <hyperlink ref="F86" r:id="rId85" xr:uid="{90D65CD6-5064-4291-BBBA-5C4CF34FE6AA}"/>
-    <hyperlink ref="F87" r:id="rId86" xr:uid="{565A4BC8-05C2-4D02-9E36-A525DC8B4371}"/>
-    <hyperlink ref="F88" r:id="rId87" xr:uid="{CAC4DA50-1414-4CF6-910E-17B7F4957564}"/>
-    <hyperlink ref="F89" r:id="rId88" xr:uid="{B0B06E7D-1C7A-4D32-AE4D-3B0F535747CB}"/>
-    <hyperlink ref="F90" r:id="rId89" xr:uid="{79DF45D6-17D0-4232-B827-A280235FCB0C}"/>
-    <hyperlink ref="F91" r:id="rId90" xr:uid="{C60BCBA6-22A3-48C1-BFE2-E3F0ED653959}"/>
-    <hyperlink ref="F92" r:id="rId91" xr:uid="{C853EAE2-A438-476C-90F5-25B420A8A86D}"/>
-    <hyperlink ref="F93" r:id="rId92" xr:uid="{6C82A848-6525-40FB-8ADB-285CE48A1AB7}"/>
-    <hyperlink ref="F94" r:id="rId93" xr:uid="{8EE7636B-FABC-4742-A271-5F728084453A}"/>
-    <hyperlink ref="F95" r:id="rId94" xr:uid="{CD277124-F55B-4777-9862-62815F1551F6}"/>
-    <hyperlink ref="F96" r:id="rId95" xr:uid="{2660453A-EC81-4D4B-BB82-FE2575DD4D08}"/>
-    <hyperlink ref="F97" r:id="rId96" xr:uid="{D6DE224C-3DFC-4DB6-9E72-AED8D135744E}"/>
-    <hyperlink ref="F98" r:id="rId97" xr:uid="{9FE4B37A-FE6D-43DC-9BC1-0674858102FE}"/>
-    <hyperlink ref="F99" r:id="rId98" xr:uid="{79960E9B-8491-4402-A445-650D8E68D557}"/>
-    <hyperlink ref="F100" r:id="rId99" xr:uid="{6AFB45A0-94C5-440F-AC3F-5C0BD165713F}"/>
-    <hyperlink ref="F101" r:id="rId100" xr:uid="{AC182F64-B58D-4649-B586-DD25D6B8AB70}"/>
-    <hyperlink ref="F102" r:id="rId101" xr:uid="{ED0CA76E-024D-4110-92A9-DADE47BFA511}"/>
-    <hyperlink ref="F103" r:id="rId102" xr:uid="{6DCFAB94-BA9F-40A5-A808-75DA2DEFA78B}"/>
-    <hyperlink ref="F104" r:id="rId103" xr:uid="{04A820DE-27A6-4077-A1BC-F1489D91C678}"/>
-    <hyperlink ref="F105" r:id="rId104" xr:uid="{A7FB23AE-9EAF-466D-9C9B-4C63C6E8B587}"/>
-    <hyperlink ref="F106" r:id="rId105" xr:uid="{B2651A48-0C82-421B-8DE0-C278FF60782D}"/>
-    <hyperlink ref="F107" r:id="rId106" xr:uid="{EF79A0C3-F8C3-4ECC-8100-6EE743381321}"/>
-    <hyperlink ref="F108" r:id="rId107" xr:uid="{894CE4A4-1C3B-4B15-991E-70742A09B0A9}"/>
-    <hyperlink ref="F109" r:id="rId108" xr:uid="{673F837F-3E66-41A7-8DFA-55E662A307D5}"/>
-    <hyperlink ref="F110" r:id="rId109" xr:uid="{376798D5-9D4C-439A-95AD-8A2F58E096FA}"/>
-    <hyperlink ref="F111" r:id="rId110" xr:uid="{FCB5C10D-9DF6-4EAD-8A24-8085B2AB1902}"/>
-    <hyperlink ref="F112" r:id="rId111" xr:uid="{6AFE760A-F307-409C-97B0-CDE8A3C59495}"/>
-    <hyperlink ref="F113" r:id="rId112" xr:uid="{54659458-7B70-4EC9-B815-3A16C19E196B}"/>
-    <hyperlink ref="F114" r:id="rId113" xr:uid="{6F053C6C-B3D4-4A41-9217-5FAF77AE6A1A}"/>
-    <hyperlink ref="F115" r:id="rId114" xr:uid="{E576B781-8638-4C92-BD02-951F41BB4664}"/>
-    <hyperlink ref="F116" r:id="rId115" xr:uid="{C67FCD24-E533-4412-A030-8D39A6196BD9}"/>
-    <hyperlink ref="F117" r:id="rId116" xr:uid="{AF98D2CE-21E4-48AA-B0B7-5BFB84D0CD27}"/>
-    <hyperlink ref="F118" r:id="rId117" xr:uid="{1EFBA9D8-6EF6-4E36-AC19-3F1E94FFBD5C}"/>
-    <hyperlink ref="F119" r:id="rId118" xr:uid="{7DFB634A-C633-412E-AB19-B9E741BF15A1}"/>
-    <hyperlink ref="F120" r:id="rId119" xr:uid="{21E9EF23-E7B0-4F90-98E5-BF00B15C699E}"/>
-    <hyperlink ref="F121" r:id="rId120" xr:uid="{5D0474FF-F8D0-44CE-B562-5D3DE5097F07}"/>
-    <hyperlink ref="F122" r:id="rId121" xr:uid="{87DB5FA0-0F6D-4DDA-A0C0-3F34E2337811}"/>
-    <hyperlink ref="F123" r:id="rId122" xr:uid="{7CA1734E-C6E6-4235-BD40-38E98639969C}"/>
-    <hyperlink ref="F124" r:id="rId123" xr:uid="{8035C2CA-3121-4516-A913-D36D95D80FC2}"/>
-    <hyperlink ref="F125" r:id="rId124" xr:uid="{427BFDC4-758F-4CBD-AC38-48FDFC6B8782}"/>
-    <hyperlink ref="F126" r:id="rId125" xr:uid="{4EF54D50-D92A-4428-B208-DF661784CF2A}"/>
-    <hyperlink ref="F127" r:id="rId126" xr:uid="{427B2866-F97E-40AF-8EAE-36C946722B0F}"/>
-    <hyperlink ref="F128" r:id="rId127" xr:uid="{4DFCD947-F796-4C5B-BD1A-079267531E02}"/>
-    <hyperlink ref="F129" r:id="rId128" xr:uid="{8E1597CE-1816-47BE-B7B5-943A8F421A4F}"/>
-    <hyperlink ref="F130" r:id="rId129" xr:uid="{C68285FD-01EE-4655-8CA9-60671F061C24}"/>
-    <hyperlink ref="F131" r:id="rId130" xr:uid="{CF70BD50-C7E8-4F03-BF4F-98E015A7F17A}"/>
-    <hyperlink ref="F132" r:id="rId131" xr:uid="{0BCC3075-62FA-4725-80F1-81D892C3CB86}"/>
-    <hyperlink ref="F133" r:id="rId132" xr:uid="{F47CB5EC-A6C4-4151-9046-9E10ABD31858}"/>
-    <hyperlink ref="F134" r:id="rId133" xr:uid="{521B1029-2578-458B-BA12-FDC6F38187AF}"/>
-    <hyperlink ref="F135" r:id="rId134" xr:uid="{80F414A6-3271-460D-82A6-46367023FF83}"/>
-    <hyperlink ref="F136" r:id="rId135" xr:uid="{33E2E0E6-C569-4CA6-B6DD-B1F2438BCBB4}"/>
-    <hyperlink ref="F137" r:id="rId136" xr:uid="{07FDADF5-7345-4496-B61A-145238CFF866}"/>
-    <hyperlink ref="F138" r:id="rId137" xr:uid="{0C3A11F0-7C72-4FE3-BB86-177F71CB9FEA}"/>
-    <hyperlink ref="F139" r:id="rId138" xr:uid="{3CD6D2CA-24C3-45B6-9338-32F48A0AA42F}"/>
-    <hyperlink ref="F140" r:id="rId139" xr:uid="{37D0A8BA-E3EC-48E1-B100-35063468A95D}"/>
-    <hyperlink ref="F141" r:id="rId140" xr:uid="{D3300FE0-865D-4B4D-A315-9248CE02C337}"/>
-    <hyperlink ref="F142" r:id="rId141" xr:uid="{3B2DE658-7F84-4955-A68E-1C3EFE362F0E}"/>
-    <hyperlink ref="F143" r:id="rId142" xr:uid="{BCE7501F-A6E9-424D-91C2-E44AC4D57D3B}"/>
-    <hyperlink ref="F144" r:id="rId143" xr:uid="{0FDC7833-8E90-414D-A157-68729F82B1C7}"/>
-    <hyperlink ref="F145" r:id="rId144" xr:uid="{EF884925-7B16-4500-BE09-2FFDFA8AC1CB}"/>
-    <hyperlink ref="F146" r:id="rId145" xr:uid="{CE87711D-2A82-48A9-956E-A3C9D91E0185}"/>
-    <hyperlink ref="F147" r:id="rId146" xr:uid="{AD6F0A9F-F610-4AE9-B9D3-7ED94EBCCF9E}"/>
-    <hyperlink ref="F148" r:id="rId147" xr:uid="{687DCC77-3B1B-4F39-B294-80DE9ABCDB24}"/>
-    <hyperlink ref="F149" r:id="rId148" xr:uid="{6CBF01C8-EEC1-4BC6-8016-71E4117A25B9}"/>
-    <hyperlink ref="F150" r:id="rId149" xr:uid="{9A3D0D55-2C9F-4137-AB75-3B35BD4979E1}"/>
-    <hyperlink ref="F151" r:id="rId150" xr:uid="{EFCE480C-DB4B-4E96-9F58-E869B4ECF873}"/>
-    <hyperlink ref="F152" r:id="rId151" xr:uid="{58B23FCE-9BC1-4F23-9B05-2824F650EC0F}"/>
-    <hyperlink ref="F153" r:id="rId152" xr:uid="{26BC8ACE-DC52-475B-89E8-E4E039EFFCF6}"/>
-    <hyperlink ref="F182" r:id="rId153" xr:uid="{E37A36DF-D1AF-453C-82F9-FBFC43510412}"/>
-    <hyperlink ref="F183" r:id="rId154" xr:uid="{A25A7B15-4C6C-4160-8E47-7DE651721FE4}"/>
-    <hyperlink ref="F184" r:id="rId155" xr:uid="{C9489915-9EF1-44BD-A806-A028B02151ED}"/>
-    <hyperlink ref="F185" r:id="rId156" xr:uid="{258761DB-716F-4A17-BE5B-CC844D7DD14F}"/>
-    <hyperlink ref="F186" r:id="rId157" xr:uid="{F9321924-41F1-42E3-AA4E-9B5CD685CD0E}"/>
-    <hyperlink ref="F187" r:id="rId158" xr:uid="{08FA5984-728F-46B8-AE79-30B28EEECF4E}"/>
-    <hyperlink ref="F188" r:id="rId159" xr:uid="{86D1A466-FB24-420B-8879-7D4708FBBE3D}"/>
-    <hyperlink ref="F189" r:id="rId160" xr:uid="{F56F7F6B-40B8-4485-9DC4-AA952E7C3E7B}"/>
-    <hyperlink ref="F190" r:id="rId161" xr:uid="{8C33203A-C6C3-40C2-A250-65801466A870}"/>
-    <hyperlink ref="F191" r:id="rId162" xr:uid="{8AA3D53F-6CBF-4FD3-BFEF-6C20B75AF3BE}"/>
-    <hyperlink ref="F192" r:id="rId163" xr:uid="{4D3D3729-EC1A-4B2F-8EA0-54F051FC447D}"/>
-    <hyperlink ref="F193" r:id="rId164" xr:uid="{899EF0F7-9E7D-4D39-B34A-D0D4B761AF39}"/>
-    <hyperlink ref="F194" r:id="rId165" xr:uid="{A7586EBF-0881-492A-A4C3-9D9879811713}"/>
-    <hyperlink ref="F195" r:id="rId166" xr:uid="{C889668C-B3C2-4075-8EBE-DBC0AD30EAF1}"/>
-    <hyperlink ref="F196" r:id="rId167" xr:uid="{425CDFEE-B484-457C-9747-F9FCA52184BE}"/>
-    <hyperlink ref="F197" r:id="rId168" xr:uid="{D7753EDB-45E8-43D1-8680-2392AA44B24C}"/>
-    <hyperlink ref="F198" r:id="rId169" xr:uid="{B352F749-0293-4035-A128-C6E386790A64}"/>
-    <hyperlink ref="F199" r:id="rId170" xr:uid="{7CE09B0B-E674-47C0-9B72-0ED98F6891B8}"/>
-    <hyperlink ref="F200" r:id="rId171" xr:uid="{857E4CDE-5691-4C39-B1D6-17AB4B838871}"/>
-    <hyperlink ref="F201" r:id="rId172" xr:uid="{8A99BB89-D9E8-49EB-A81E-5BBAC4BA6DED}"/>
-    <hyperlink ref="F202" r:id="rId173" xr:uid="{E36FCD17-C042-4132-97F9-BBFF96F5EB64}"/>
-    <hyperlink ref="F203" r:id="rId174" xr:uid="{DDD2C1C6-AAFD-47A2-8674-79F7C17CC782}"/>
-    <hyperlink ref="F204" r:id="rId175" xr:uid="{35C40565-78C2-4D48-94E0-1E2EE403308A}"/>
-    <hyperlink ref="F205" r:id="rId176" xr:uid="{A2702FA7-102F-4206-82A4-32B082AA85B4}"/>
-    <hyperlink ref="F206" r:id="rId177" xr:uid="{DA3DF86D-5438-4439-BDBA-BBC3ECD5DD59}"/>
-    <hyperlink ref="F207" r:id="rId178" xr:uid="{9F1053DB-7530-4A63-B2C3-8A8A526CE542}"/>
-    <hyperlink ref="F208" r:id="rId179" xr:uid="{736C6C7D-A848-4E55-8160-310B3CBA73BD}"/>
-    <hyperlink ref="F209" r:id="rId180" xr:uid="{874E3559-BC95-4428-8742-F3E01BC5DBFD}"/>
-    <hyperlink ref="F210" r:id="rId181" xr:uid="{53366E4C-ADAD-42B3-8DD8-E133A852A4BD}"/>
-    <hyperlink ref="F211" r:id="rId182" xr:uid="{4876A31B-6F03-45CB-BA34-1B5442540DAD}"/>
-    <hyperlink ref="F212" r:id="rId183" xr:uid="{16BAE6F9-7239-4EFC-9767-A97CB78E48E8}"/>
-    <hyperlink ref="F213" r:id="rId184" xr:uid="{ECD6E617-7C11-49FA-B937-FD214D68BBAC}"/>
-    <hyperlink ref="F214" r:id="rId185" xr:uid="{21FAA203-7470-4D7D-A3BB-9933AFD1F367}"/>
-    <hyperlink ref="F215" r:id="rId186" xr:uid="{634A8180-B31B-4CA5-8F32-AA259024B14F}"/>
-    <hyperlink ref="F216" r:id="rId187" xr:uid="{D023B19B-7083-488A-A099-B6BE74A59D37}"/>
-    <hyperlink ref="F217" r:id="rId188" xr:uid="{B1578663-C3B6-4F2C-8B33-6DB282D6D290}"/>
-    <hyperlink ref="F218" r:id="rId189" xr:uid="{48C3EF64-5B2B-43CC-B616-6270C918BC85}"/>
-    <hyperlink ref="F219" r:id="rId190" xr:uid="{D077BC73-63F5-4D87-B80D-E15BEF4C45D2}"/>
-    <hyperlink ref="F220" r:id="rId191" xr:uid="{8D50E206-13C9-45A2-BBF8-487E5F645D84}"/>
-    <hyperlink ref="F221" r:id="rId192" xr:uid="{4BCDA111-C900-4761-9BCF-99F303DAAA2F}"/>
-    <hyperlink ref="F222" r:id="rId193" xr:uid="{A449B30C-1E02-4199-AB4B-EA7255E7674D}"/>
-    <hyperlink ref="F223" r:id="rId194" xr:uid="{9585EB03-5E7A-43F6-847A-842D6B45942D}"/>
-    <hyperlink ref="F224" r:id="rId195" xr:uid="{36C1A99F-715C-4A96-84B7-8BB9C85A1F00}"/>
-    <hyperlink ref="F225" r:id="rId196" xr:uid="{43BD1CFF-7742-4200-86A9-449C44F0752D}"/>
-    <hyperlink ref="F226" r:id="rId197" xr:uid="{24C4B9E9-0DF7-49DB-9491-5A252F19A39B}"/>
-    <hyperlink ref="F227" r:id="rId198" xr:uid="{5F149B2F-CB8F-4FA3-BD1E-54CFF9679374}"/>
-    <hyperlink ref="F228" r:id="rId199" xr:uid="{F5438FAA-650B-4B32-B574-29601D6CDCD8}"/>
-    <hyperlink ref="F229" r:id="rId200" xr:uid="{5AC2F776-6F39-4C81-A316-7099D77757F0}"/>
-    <hyperlink ref="F230" r:id="rId201" xr:uid="{1A31AFB3-387B-4CB2-B2E4-903A7CE35FCC}"/>
-    <hyperlink ref="F231" r:id="rId202" xr:uid="{642227BD-DF85-4E7F-BD78-19EE939C29F1}"/>
-    <hyperlink ref="F232" r:id="rId203" xr:uid="{7CF5547B-3B64-4174-AEF6-295A1ABBA36C}"/>
-    <hyperlink ref="F233" r:id="rId204" xr:uid="{DBEE7FA7-9C16-4667-90AB-E0DFF3B88DD3}"/>
-    <hyperlink ref="F154" r:id="rId205" xr:uid="{7554264D-2547-43E1-9770-446E2FD25BCC}"/>
-    <hyperlink ref="F155" r:id="rId206" xr:uid="{8A1BF691-1B25-4959-99AB-B66C11015F02}"/>
-    <hyperlink ref="F156" r:id="rId207" xr:uid="{B99F0CE7-5248-4F36-8870-267FE0980AA8}"/>
-    <hyperlink ref="F157" r:id="rId208" xr:uid="{1CBE6ACF-022E-4FF5-BA06-07F9F02FF319}"/>
-    <hyperlink ref="F158" r:id="rId209" xr:uid="{AB3C16DD-011F-485F-BDFF-B9564F28EFFA}"/>
-    <hyperlink ref="F159" r:id="rId210" xr:uid="{9C7370C2-3B97-406A-B993-9B320C170AF0}"/>
-    <hyperlink ref="F160" r:id="rId211" xr:uid="{5C5D84A2-C2ED-4CA3-AC5F-FB8260013B21}"/>
-    <hyperlink ref="F161" r:id="rId212" xr:uid="{7E86101D-E3B5-43E7-BB91-86F990AB576F}"/>
-    <hyperlink ref="F162" r:id="rId213" xr:uid="{86EF32D4-0787-4DEF-AF13-8D6989B5CEA6}"/>
-    <hyperlink ref="F163" r:id="rId214" xr:uid="{D94ACD25-749A-4CB1-8052-0A0AFE93780A}"/>
-    <hyperlink ref="F164" r:id="rId215" xr:uid="{2E00A680-64E9-407D-8E13-2F110618DF34}"/>
-    <hyperlink ref="F165" r:id="rId216" xr:uid="{5282E600-5DE5-40F4-ABBA-8BDF551E64C5}"/>
-    <hyperlink ref="F166" r:id="rId217" xr:uid="{1C04F383-D1C0-4924-BCA4-7D68BF4F2C8A}"/>
-    <hyperlink ref="F167" r:id="rId218" xr:uid="{DF7BF135-FF63-4E18-A7A5-FC4B58690512}"/>
-    <hyperlink ref="F168" r:id="rId219" xr:uid="{1DB2A338-6A2C-43A2-8EFC-188CA7D96DF3}"/>
-    <hyperlink ref="F169" r:id="rId220" xr:uid="{65DFDF8E-E514-4B91-8BEF-7DD72C911D4F}"/>
-    <hyperlink ref="F170" r:id="rId221" xr:uid="{A9D504BA-AD23-48E7-A473-E3FE0EC434F4}"/>
-    <hyperlink ref="F171" r:id="rId222" xr:uid="{7D5E334E-6CFD-4B49-94F8-1E5E7816CEF4}"/>
-    <hyperlink ref="F172" r:id="rId223" xr:uid="{81D56905-B982-4CBF-B952-F71944EA142A}"/>
-    <hyperlink ref="F173" r:id="rId224" xr:uid="{8B3CBB40-E4B6-4847-AFAA-F21B565F54DA}"/>
-    <hyperlink ref="F174" r:id="rId225" xr:uid="{8C47402A-5BE2-4D1B-8AB7-5CF16C4B84EB}"/>
-    <hyperlink ref="F175" r:id="rId226" xr:uid="{0088EA25-8E77-4132-90D8-5D0A3074B20F}"/>
-    <hyperlink ref="F176" r:id="rId227" xr:uid="{A61E9347-7C4E-41E4-A7E9-AA05313C5FC7}"/>
-    <hyperlink ref="F177" r:id="rId228" xr:uid="{5F690E95-E438-45DC-B54F-5EF7E7545176}"/>
-    <hyperlink ref="F178" r:id="rId229" xr:uid="{2DC5C43A-961D-4C73-8C18-D84597852CF5}"/>
-    <hyperlink ref="F179" r:id="rId230" xr:uid="{FF7475C9-D2DA-4B9A-A867-501EFEA3C7B8}"/>
-    <hyperlink ref="F180" r:id="rId231" xr:uid="{36B83677-8EFD-4D8E-A00C-384F0A81678E}"/>
-    <hyperlink ref="F181" r:id="rId232" xr:uid="{AEE3D4D7-55E2-4FED-8E53-EA1201972E3C}"/>
-    <hyperlink ref="F234" r:id="rId233" xr:uid="{2E12A770-0B07-45A2-A461-625EEEC258DA}"/>
-    <hyperlink ref="F235" r:id="rId234" xr:uid="{367DA9FF-A0AA-410B-9DDE-593EA3D8446D}"/>
-    <hyperlink ref="F236" r:id="rId235" xr:uid="{9D67B6DC-99F9-45B6-9FE8-29B117DACDAB}"/>
-    <hyperlink ref="F237" r:id="rId236" xr:uid="{33BF3254-CA00-424D-8085-B0F44D80A808}"/>
-    <hyperlink ref="F238" r:id="rId237" xr:uid="{1BFDA55B-31DA-4088-A658-B915DD35B6E6}"/>
-    <hyperlink ref="F239" r:id="rId238" xr:uid="{D43D5340-E0C4-4744-A915-1F7F8F01940D}"/>
-    <hyperlink ref="F240" r:id="rId239" xr:uid="{AD4A3C3C-86BA-4866-8A2F-8C5232523A8D}"/>
-    <hyperlink ref="F241" r:id="rId240" xr:uid="{56DA2C6E-BC11-4E19-AE22-03E1C6D1E3F4}"/>
-    <hyperlink ref="F242" r:id="rId241" xr:uid="{897E3D83-DF91-4892-908F-73E3E08048FA}"/>
-    <hyperlink ref="F243" r:id="rId242" xr:uid="{64F3AD1A-993F-4769-B58A-1F725E5CDA0E}"/>
-    <hyperlink ref="F244" r:id="rId243" xr:uid="{DC9B3EB8-B1EB-48AC-B2D7-969A79B67512}"/>
-    <hyperlink ref="F245" r:id="rId244" xr:uid="{EF941B07-8F2C-4D8F-8C29-2A61427B6A73}"/>
-    <hyperlink ref="F246" r:id="rId245" xr:uid="{7FB80983-CA7D-4D95-901D-55429CD5A532}"/>
-    <hyperlink ref="F247" r:id="rId246" xr:uid="{6F9BA08E-A1DC-4A8E-8685-CE73D5845A2E}"/>
-    <hyperlink ref="F248" r:id="rId247" xr:uid="{FA55C00A-55DC-4F39-8A25-8656B7712852}"/>
-    <hyperlink ref="F249" r:id="rId248" xr:uid="{BE915386-1311-4240-8C12-5E033381C471}"/>
-    <hyperlink ref="F250" r:id="rId249" xr:uid="{A73C957B-2CC3-40DB-B94C-95974BB536B9}"/>
+    <hyperlink ref="F121" r:id="rId1" xr:uid="{2F48726D-DE6A-4098-BE7D-5BACCC8FC40A}"/>
+    <hyperlink ref="F122" r:id="rId2" xr:uid="{F3DC5606-9A2B-4B27-888E-2418DBD63197}"/>
+    <hyperlink ref="F123" r:id="rId3" xr:uid="{1A77C4B1-3EBF-4996-8BA5-54115DCC6DB4}"/>
+    <hyperlink ref="F124" r:id="rId4" xr:uid="{DB555C1A-23E1-4927-9647-7C6892E4C9C7}"/>
+    <hyperlink ref="F125" r:id="rId5" xr:uid="{33661F8A-1BC9-417D-99B3-DC93198874DE}"/>
+    <hyperlink ref="F126" r:id="rId6" xr:uid="{192DE853-AD34-43CA-A63F-E85114AD4EA0}"/>
+    <hyperlink ref="F127" r:id="rId7" xr:uid="{120E2455-BB40-4E29-A234-A4B7E792FE52}"/>
+    <hyperlink ref="F128" r:id="rId8" xr:uid="{1443E8F9-88EF-4C2B-A276-23E530539E9E}"/>
+    <hyperlink ref="F129" r:id="rId9" xr:uid="{E7CEA036-13F4-4AAC-A555-2FFE21E0C2B8}"/>
+    <hyperlink ref="F130" r:id="rId10" xr:uid="{92496332-5A82-488E-A37E-5592FCE49A81}"/>
+    <hyperlink ref="F131" r:id="rId11" xr:uid="{A0653FC6-F81B-47CA-A38B-BB1D7D8780AB}"/>
+    <hyperlink ref="F132" r:id="rId12" xr:uid="{F5BF4D55-CEE6-4250-9B16-AC2891C0A711}"/>
+    <hyperlink ref="F133" r:id="rId13" xr:uid="{68E21E8B-2406-448E-BB39-B787D1282FA1}"/>
+    <hyperlink ref="F134" r:id="rId14" xr:uid="{C2C55E82-ED9F-4FFA-A073-7DC869302C16}"/>
+    <hyperlink ref="F135" r:id="rId15" xr:uid="{4EAD4B84-80BA-4CC7-BD19-A32B04E8286F}"/>
+    <hyperlink ref="F136" r:id="rId16" xr:uid="{71AC19CA-92E6-49F9-BED3-CA495F366A27}"/>
+    <hyperlink ref="F137" r:id="rId17" xr:uid="{00E6714E-2AC2-46E3-9D9F-9C8DCAFD8C22}"/>
+    <hyperlink ref="F138" r:id="rId18" xr:uid="{AB2C6C29-2033-4459-95EA-6131071555ED}"/>
+    <hyperlink ref="F139" r:id="rId19" xr:uid="{04FD38F5-886B-410E-8338-BE423E77A551}"/>
+    <hyperlink ref="F140" r:id="rId20" xr:uid="{46C219A9-8A37-4A38-8BE2-31449600C9CA}"/>
+    <hyperlink ref="F141" r:id="rId21" xr:uid="{A4FCB636-86E3-402A-87E0-87E9BA4AEB41}"/>
+    <hyperlink ref="F142" r:id="rId22" xr:uid="{D96AABDB-3F6C-4B7E-9065-4389E1536714}"/>
+    <hyperlink ref="F143" r:id="rId23" xr:uid="{775F3009-BB92-4337-B30F-6702A68EFCA3}"/>
+    <hyperlink ref="F144" r:id="rId24" xr:uid="{4052F6BF-CA0D-45FA-B208-BDE51EE65CB4}"/>
+    <hyperlink ref="F145" r:id="rId25" xr:uid="{CCDC01A5-FEA2-4076-85E1-6C44FBD6C90A}"/>
+    <hyperlink ref="F146" r:id="rId26" xr:uid="{D31553ED-97EA-4017-B69C-127C4E539342}"/>
+    <hyperlink ref="F147" r:id="rId27" xr:uid="{A34382CC-3807-4DAD-A391-229E3068D20E}"/>
+    <hyperlink ref="F148" r:id="rId28" xr:uid="{D5D838C4-84B9-4893-8081-FD076E65D42D}"/>
+    <hyperlink ref="F149" r:id="rId29" xr:uid="{372D6C7C-57A1-4E5A-8FCA-C2BD42179B4C}"/>
+    <hyperlink ref="F150" r:id="rId30" xr:uid="{26F4CB51-8E73-4DD6-B36B-7D9E3532FACA}"/>
+    <hyperlink ref="F151" r:id="rId31" xr:uid="{28E3DA9C-8B99-4871-9FD0-8DBA1F52D164}"/>
+    <hyperlink ref="F152" r:id="rId32" xr:uid="{F221B864-0319-4744-8F5C-74DFBBD9ECA7}"/>
+    <hyperlink ref="F153" r:id="rId33" xr:uid="{2D863332-43A9-4835-9018-6C6225BAD913}"/>
+    <hyperlink ref="F154" r:id="rId34" xr:uid="{8ABCCB9C-AB49-4FB0-B2C4-669FD2A169BF}"/>
+    <hyperlink ref="F155" r:id="rId35" xr:uid="{4EB52813-3D3C-4F1F-9712-9A07F774A538}"/>
+    <hyperlink ref="F156" r:id="rId36" xr:uid="{52D9EF13-2183-4310-8C32-B2C6A2C08567}"/>
+    <hyperlink ref="F157" r:id="rId37" xr:uid="{A4411235-2A13-4120-A1DD-E52352CFC475}"/>
+    <hyperlink ref="F158" r:id="rId38" xr:uid="{20112E1E-36A7-49B0-BC59-7AB1EF3FBB2A}"/>
+    <hyperlink ref="F159" r:id="rId39" xr:uid="{4E175341-6D90-4C16-9BD9-DD27F4F88C73}"/>
+    <hyperlink ref="F160" r:id="rId40" xr:uid="{834BAFD9-DA29-4D56-BC7B-97B850C5B365}"/>
+    <hyperlink ref="F161" r:id="rId41" xr:uid="{BD779373-AC8C-41E2-98ED-E8D18BBA663E}"/>
+    <hyperlink ref="F162" r:id="rId42" xr:uid="{24CF6F19-C969-4937-9966-220089144F6B}"/>
+    <hyperlink ref="F163" r:id="rId43" xr:uid="{7EABD7FB-999B-4734-B105-231100FF8189}"/>
+    <hyperlink ref="F164" r:id="rId44" xr:uid="{474F7FAB-D2DA-4694-99EE-DD8310E2F160}"/>
+    <hyperlink ref="F165" r:id="rId45" xr:uid="{8E164687-D84D-4A4D-AE50-E53CD426CA64}"/>
+    <hyperlink ref="F166" r:id="rId46" xr:uid="{57F15978-1279-4A0F-A215-4906CA1FD882}"/>
+    <hyperlink ref="F167" r:id="rId47" xr:uid="{67474A5D-2B34-4EE2-A19E-F5C77A48AD43}"/>
+    <hyperlink ref="F168" r:id="rId48" xr:uid="{1E95D132-2A35-447E-B877-2D34495278B4}"/>
+    <hyperlink ref="F169" r:id="rId49" xr:uid="{D34E7BDD-E93E-4C88-92F5-D432227DE455}"/>
+    <hyperlink ref="F170" r:id="rId50" xr:uid="{C12907DC-6C9E-4977-A538-A3F744F8AA91}"/>
+    <hyperlink ref="F171" r:id="rId51" xr:uid="{B245579F-EA5C-4935-830B-94FC23CDA18F}"/>
+    <hyperlink ref="F172" r:id="rId52" xr:uid="{073D4EE8-9D0C-40B6-9B55-B6B321685ECB}"/>
+    <hyperlink ref="F173" r:id="rId53" xr:uid="{90D65CD6-5064-4291-BBBA-5C4CF34FE6AA}"/>
+    <hyperlink ref="F174" r:id="rId54" xr:uid="{565A4BC8-05C2-4D02-9E36-A525DC8B4371}"/>
+    <hyperlink ref="F175" r:id="rId55" xr:uid="{CAC4DA50-1414-4CF6-910E-17B7F4957564}"/>
+    <hyperlink ref="F176" r:id="rId56" xr:uid="{B0B06E7D-1C7A-4D32-AE4D-3B0F535747CB}"/>
+    <hyperlink ref="F177" r:id="rId57" xr:uid="{79DF45D6-17D0-4232-B827-A280235FCB0C}"/>
+    <hyperlink ref="F178" r:id="rId58" xr:uid="{C60BCBA6-22A3-48C1-BFE2-E3F0ED653959}"/>
+    <hyperlink ref="F179" r:id="rId59" xr:uid="{C853EAE2-A438-476C-90F5-25B420A8A86D}"/>
+    <hyperlink ref="F180" r:id="rId60" xr:uid="{6C82A848-6525-40FB-8ADB-285CE48A1AB7}"/>
+    <hyperlink ref="F181" r:id="rId61" xr:uid="{8EE7636B-FABC-4742-A271-5F728084453A}"/>
+    <hyperlink ref="F182" r:id="rId62" xr:uid="{CD277124-F55B-4777-9862-62815F1551F6}"/>
+    <hyperlink ref="F183" r:id="rId63" xr:uid="{2660453A-EC81-4D4B-BB82-FE2575DD4D08}"/>
+    <hyperlink ref="F184" r:id="rId64" xr:uid="{D6DE224C-3DFC-4DB6-9E72-AED8D135744E}"/>
+    <hyperlink ref="F185" r:id="rId65" xr:uid="{9FE4B37A-FE6D-43DC-9BC1-0674858102FE}"/>
+    <hyperlink ref="F186" r:id="rId66" xr:uid="{79960E9B-8491-4402-A445-650D8E68D557}"/>
+    <hyperlink ref="F187" r:id="rId67" xr:uid="{6AFB45A0-94C5-440F-AC3F-5C0BD165713F}"/>
+    <hyperlink ref="F188" r:id="rId68" xr:uid="{AC182F64-B58D-4649-B586-DD25D6B8AB70}"/>
+    <hyperlink ref="F189" r:id="rId69" xr:uid="{ED0CA76E-024D-4110-92A9-DADE47BFA511}"/>
+    <hyperlink ref="F190" r:id="rId70" xr:uid="{6DCFAB94-BA9F-40A5-A808-75DA2DEFA78B}"/>
+    <hyperlink ref="F191" r:id="rId71" xr:uid="{04A820DE-27A6-4077-A1BC-F1489D91C678}"/>
+    <hyperlink ref="F192" r:id="rId72" xr:uid="{A7FB23AE-9EAF-466D-9C9B-4C63C6E8B587}"/>
+    <hyperlink ref="F193" r:id="rId73" xr:uid="{B2651A48-0C82-421B-8DE0-C278FF60782D}"/>
+    <hyperlink ref="F194" r:id="rId74" xr:uid="{EF79A0C3-F8C3-4ECC-8100-6EE743381321}"/>
+    <hyperlink ref="F195" r:id="rId75" xr:uid="{894CE4A4-1C3B-4B15-991E-70742A09B0A9}"/>
+    <hyperlink ref="F196" r:id="rId76" xr:uid="{673F837F-3E66-41A7-8DFA-55E662A307D5}"/>
+    <hyperlink ref="F197" r:id="rId77" xr:uid="{376798D5-9D4C-439A-95AD-8A2F58E096FA}"/>
+    <hyperlink ref="F198" r:id="rId78" xr:uid="{FCB5C10D-9DF6-4EAD-8A24-8085B2AB1902}"/>
+    <hyperlink ref="F199" r:id="rId79" xr:uid="{6AFE760A-F307-409C-97B0-CDE8A3C59495}"/>
+    <hyperlink ref="F200" r:id="rId80" xr:uid="{54659458-7B70-4EC9-B815-3A16C19E196B}"/>
+    <hyperlink ref="F201" r:id="rId81" xr:uid="{6F053C6C-B3D4-4A41-9217-5FAF77AE6A1A}"/>
+    <hyperlink ref="F202" r:id="rId82" xr:uid="{E576B781-8638-4C92-BD02-951F41BB4664}"/>
+    <hyperlink ref="F203" r:id="rId83" xr:uid="{C67FCD24-E533-4412-A030-8D39A6196BD9}"/>
+    <hyperlink ref="F204" r:id="rId84" xr:uid="{AF98D2CE-21E4-48AA-B0B7-5BFB84D0CD27}"/>
+    <hyperlink ref="F205" r:id="rId85" xr:uid="{1EFBA9D8-6EF6-4E36-AC19-3F1E94FFBD5C}"/>
+    <hyperlink ref="F206" r:id="rId86" xr:uid="{7DFB634A-C633-412E-AB19-B9E741BF15A1}"/>
+    <hyperlink ref="F207" r:id="rId87" xr:uid="{21E9EF23-E7B0-4F90-98E5-BF00B15C699E}"/>
+    <hyperlink ref="F208" r:id="rId88" xr:uid="{5D0474FF-F8D0-44CE-B562-5D3DE5097F07}"/>
+    <hyperlink ref="F209" r:id="rId89" xr:uid="{87DB5FA0-0F6D-4DDA-A0C0-3F34E2337811}"/>
+    <hyperlink ref="F210" r:id="rId90" xr:uid="{7CA1734E-C6E6-4235-BD40-38E98639969C}"/>
+    <hyperlink ref="F211" r:id="rId91" xr:uid="{8035C2CA-3121-4516-A913-D36D95D80FC2}"/>
+    <hyperlink ref="F212" r:id="rId92" xr:uid="{427BFDC4-758F-4CBD-AC38-48FDFC6B8782}"/>
+    <hyperlink ref="F213" r:id="rId93" xr:uid="{4EF54D50-D92A-4428-B208-DF661784CF2A}"/>
+    <hyperlink ref="F214" r:id="rId94" xr:uid="{427B2866-F97E-40AF-8EAE-36C946722B0F}"/>
+    <hyperlink ref="F215" r:id="rId95" xr:uid="{4DFCD947-F796-4C5B-BD1A-079267531E02}"/>
+    <hyperlink ref="F216" r:id="rId96" xr:uid="{8E1597CE-1816-47BE-B7B5-943A8F421A4F}"/>
+    <hyperlink ref="F217" r:id="rId97" xr:uid="{C68285FD-01EE-4655-8CA9-60671F061C24}"/>
+    <hyperlink ref="F218" r:id="rId98" xr:uid="{CF70BD50-C7E8-4F03-BF4F-98E015A7F17A}"/>
+    <hyperlink ref="F219" r:id="rId99" xr:uid="{0BCC3075-62FA-4725-80F1-81D892C3CB86}"/>
+    <hyperlink ref="F220" r:id="rId100" xr:uid="{F47CB5EC-A6C4-4151-9046-9E10ABD31858}"/>
+    <hyperlink ref="F221" r:id="rId101" xr:uid="{521B1029-2578-458B-BA12-FDC6F38187AF}"/>
+    <hyperlink ref="F222" r:id="rId102" xr:uid="{80F414A6-3271-460D-82A6-46367023FF83}"/>
+    <hyperlink ref="F223" r:id="rId103" xr:uid="{33E2E0E6-C569-4CA6-B6DD-B1F2438BCBB4}"/>
+    <hyperlink ref="F224" r:id="rId104" xr:uid="{07FDADF5-7345-4496-B61A-145238CFF866}"/>
+    <hyperlink ref="F225" r:id="rId105" xr:uid="{0C3A11F0-7C72-4FE3-BB86-177F71CB9FEA}"/>
+    <hyperlink ref="F226" r:id="rId106" xr:uid="{3CD6D2CA-24C3-45B6-9338-32F48A0AA42F}"/>
+    <hyperlink ref="F227" r:id="rId107" xr:uid="{37D0A8BA-E3EC-48E1-B100-35063468A95D}"/>
+    <hyperlink ref="F228" r:id="rId108" xr:uid="{D3300FE0-865D-4B4D-A315-9248CE02C337}"/>
+    <hyperlink ref="F229" r:id="rId109" xr:uid="{3B2DE658-7F84-4955-A68E-1C3EFE362F0E}"/>
+    <hyperlink ref="F230" r:id="rId110" xr:uid="{BCE7501F-A6E9-424D-91C2-E44AC4D57D3B}"/>
+    <hyperlink ref="F231" r:id="rId111" xr:uid="{0FDC7833-8E90-414D-A157-68729F82B1C7}"/>
+    <hyperlink ref="F232" r:id="rId112" xr:uid="{EF884925-7B16-4500-BE09-2FFDFA8AC1CB}"/>
+    <hyperlink ref="F233" r:id="rId113" xr:uid="{CE87711D-2A82-48A9-956E-A3C9D91E0185}"/>
+    <hyperlink ref="F234" r:id="rId114" xr:uid="{AD6F0A9F-F610-4AE9-B9D3-7ED94EBCCF9E}"/>
+    <hyperlink ref="F235" r:id="rId115" xr:uid="{687DCC77-3B1B-4F39-B294-80DE9ABCDB24}"/>
+    <hyperlink ref="F236" r:id="rId116" xr:uid="{6CBF01C8-EEC1-4BC6-8016-71E4117A25B9}"/>
+    <hyperlink ref="F237" r:id="rId117" xr:uid="{9A3D0D55-2C9F-4137-AB75-3B35BD4979E1}"/>
+    <hyperlink ref="F238" r:id="rId118" xr:uid="{EFCE480C-DB4B-4E96-9F58-E869B4ECF873}"/>
+    <hyperlink ref="F239" r:id="rId119" xr:uid="{58B23FCE-9BC1-4F23-9B05-2824F650EC0F}"/>
+    <hyperlink ref="F240" r:id="rId120" xr:uid="{26BC8ACE-DC52-475B-89E8-E4E039EFFCF6}"/>
+    <hyperlink ref="F269" r:id="rId121" xr:uid="{E37A36DF-D1AF-453C-82F9-FBFC43510412}"/>
+    <hyperlink ref="F270" r:id="rId122" xr:uid="{A25A7B15-4C6C-4160-8E47-7DE651721FE4}"/>
+    <hyperlink ref="F271" r:id="rId123" xr:uid="{C9489915-9EF1-44BD-A806-A028B02151ED}"/>
+    <hyperlink ref="F272" r:id="rId124" xr:uid="{258761DB-716F-4A17-BE5B-CC844D7DD14F}"/>
+    <hyperlink ref="F273" r:id="rId125" xr:uid="{F9321924-41F1-42E3-AA4E-9B5CD685CD0E}"/>
+    <hyperlink ref="F274" r:id="rId126" xr:uid="{08FA5984-728F-46B8-AE79-30B28EEECF4E}"/>
+    <hyperlink ref="F275" r:id="rId127" xr:uid="{86D1A466-FB24-420B-8879-7D4708FBBE3D}"/>
+    <hyperlink ref="F276" r:id="rId128" xr:uid="{F56F7F6B-40B8-4485-9DC4-AA952E7C3E7B}"/>
+    <hyperlink ref="F277" r:id="rId129" xr:uid="{8C33203A-C6C3-40C2-A250-65801466A870}"/>
+    <hyperlink ref="F278" r:id="rId130" xr:uid="{8AA3D53F-6CBF-4FD3-BFEF-6C20B75AF3BE}"/>
+    <hyperlink ref="F279" r:id="rId131" xr:uid="{4D3D3729-EC1A-4B2F-8EA0-54F051FC447D}"/>
+    <hyperlink ref="F280" r:id="rId132" xr:uid="{899EF0F7-9E7D-4D39-B34A-D0D4B761AF39}"/>
+    <hyperlink ref="F281" r:id="rId133" xr:uid="{A7586EBF-0881-492A-A4C3-9D9879811713}"/>
+    <hyperlink ref="F282" r:id="rId134" xr:uid="{C889668C-B3C2-4075-8EBE-DBC0AD30EAF1}"/>
+    <hyperlink ref="F283" r:id="rId135" xr:uid="{425CDFEE-B484-457C-9747-F9FCA52184BE}"/>
+    <hyperlink ref="F284" r:id="rId136" xr:uid="{D7753EDB-45E8-43D1-8680-2392AA44B24C}"/>
+    <hyperlink ref="F285" r:id="rId137" xr:uid="{B352F749-0293-4035-A128-C6E386790A64}"/>
+    <hyperlink ref="F286" r:id="rId138" xr:uid="{7CE09B0B-E674-47C0-9B72-0ED98F6891B8}"/>
+    <hyperlink ref="F287" r:id="rId139" xr:uid="{857E4CDE-5691-4C39-B1D6-17AB4B838871}"/>
+    <hyperlink ref="F288" r:id="rId140" xr:uid="{8A99BB89-D9E8-49EB-A81E-5BBAC4BA6DED}"/>
+    <hyperlink ref="F289" r:id="rId141" xr:uid="{E36FCD17-C042-4132-97F9-BBFF96F5EB64}"/>
+    <hyperlink ref="F290" r:id="rId142" xr:uid="{DDD2C1C6-AAFD-47A2-8674-79F7C17CC782}"/>
+    <hyperlink ref="F291" r:id="rId143" xr:uid="{35C40565-78C2-4D48-94E0-1E2EE403308A}"/>
+    <hyperlink ref="F292" r:id="rId144" xr:uid="{A2702FA7-102F-4206-82A4-32B082AA85B4}"/>
+    <hyperlink ref="F293" r:id="rId145" xr:uid="{DA3DF86D-5438-4439-BDBA-BBC3ECD5DD59}"/>
+    <hyperlink ref="F294" r:id="rId146" xr:uid="{9F1053DB-7530-4A63-B2C3-8A8A526CE542}"/>
+    <hyperlink ref="F295" r:id="rId147" xr:uid="{736C6C7D-A848-4E55-8160-310B3CBA73BD}"/>
+    <hyperlink ref="F296" r:id="rId148" xr:uid="{874E3559-BC95-4428-8742-F3E01BC5DBFD}"/>
+    <hyperlink ref="F297" r:id="rId149" xr:uid="{53366E4C-ADAD-42B3-8DD8-E133A852A4BD}"/>
+    <hyperlink ref="F298" r:id="rId150" xr:uid="{4876A31B-6F03-45CB-BA34-1B5442540DAD}"/>
+    <hyperlink ref="F299" r:id="rId151" xr:uid="{16BAE6F9-7239-4EFC-9767-A97CB78E48E8}"/>
+    <hyperlink ref="F300" r:id="rId152" xr:uid="{ECD6E617-7C11-49FA-B937-FD214D68BBAC}"/>
+    <hyperlink ref="F301" r:id="rId153" xr:uid="{21FAA203-7470-4D7D-A3BB-9933AFD1F367}"/>
+    <hyperlink ref="F302" r:id="rId154" xr:uid="{634A8180-B31B-4CA5-8F32-AA259024B14F}"/>
+    <hyperlink ref="F303" r:id="rId155" xr:uid="{D023B19B-7083-488A-A099-B6BE74A59D37}"/>
+    <hyperlink ref="F304" r:id="rId156" xr:uid="{B1578663-C3B6-4F2C-8B33-6DB282D6D290}"/>
+    <hyperlink ref="F305" r:id="rId157" xr:uid="{48C3EF64-5B2B-43CC-B616-6270C918BC85}"/>
+    <hyperlink ref="F306" r:id="rId158" xr:uid="{D077BC73-63F5-4D87-B80D-E15BEF4C45D2}"/>
+    <hyperlink ref="F307" r:id="rId159" xr:uid="{8D50E206-13C9-45A2-BBF8-487E5F645D84}"/>
+    <hyperlink ref="F308" r:id="rId160" xr:uid="{4BCDA111-C900-4761-9BCF-99F303DAAA2F}"/>
+    <hyperlink ref="F309" r:id="rId161" xr:uid="{A449B30C-1E02-4199-AB4B-EA7255E7674D}"/>
+    <hyperlink ref="F310" r:id="rId162" xr:uid="{9585EB03-5E7A-43F6-847A-842D6B45942D}"/>
+    <hyperlink ref="F311" r:id="rId163" xr:uid="{36C1A99F-715C-4A96-84B7-8BB9C85A1F00}"/>
+    <hyperlink ref="F312" r:id="rId164" xr:uid="{43BD1CFF-7742-4200-86A9-449C44F0752D}"/>
+    <hyperlink ref="F313" r:id="rId165" xr:uid="{24C4B9E9-0DF7-49DB-9491-5A252F19A39B}"/>
+    <hyperlink ref="F314" r:id="rId166" xr:uid="{5F149B2F-CB8F-4FA3-BD1E-54CFF9679374}"/>
+    <hyperlink ref="F315" r:id="rId167" xr:uid="{F5438FAA-650B-4B32-B574-29601D6CDCD8}"/>
+    <hyperlink ref="F316" r:id="rId168" xr:uid="{5AC2F776-6F39-4C81-A316-7099D77757F0}"/>
+    <hyperlink ref="F317" r:id="rId169" xr:uid="{1A31AFB3-387B-4CB2-B2E4-903A7CE35FCC}"/>
+    <hyperlink ref="F318" r:id="rId170" xr:uid="{642227BD-DF85-4E7F-BD78-19EE939C29F1}"/>
+    <hyperlink ref="F319" r:id="rId171" xr:uid="{7CF5547B-3B64-4174-AEF6-295A1ABBA36C}"/>
+    <hyperlink ref="F320" r:id="rId172" xr:uid="{DBEE7FA7-9C16-4667-90AB-E0DFF3B88DD3}"/>
+    <hyperlink ref="F241" r:id="rId173" xr:uid="{7554264D-2547-43E1-9770-446E2FD25BCC}"/>
+    <hyperlink ref="F242" r:id="rId174" xr:uid="{8A1BF691-1B25-4959-99AB-B66C11015F02}"/>
+    <hyperlink ref="F243" r:id="rId175" xr:uid="{B99F0CE7-5248-4F36-8870-267FE0980AA8}"/>
+    <hyperlink ref="F244" r:id="rId176" xr:uid="{1CBE6ACF-022E-4FF5-BA06-07F9F02FF319}"/>
+    <hyperlink ref="F245" r:id="rId177" xr:uid="{AB3C16DD-011F-485F-BDFF-B9564F28EFFA}"/>
+    <hyperlink ref="F246" r:id="rId178" xr:uid="{9C7370C2-3B97-406A-B993-9B320C170AF0}"/>
+    <hyperlink ref="F247" r:id="rId179" xr:uid="{5C5D84A2-C2ED-4CA3-AC5F-FB8260013B21}"/>
+    <hyperlink ref="F248" r:id="rId180" xr:uid="{7E86101D-E3B5-43E7-BB91-86F990AB576F}"/>
+    <hyperlink ref="F249" r:id="rId181" xr:uid="{86EF32D4-0787-4DEF-AF13-8D6989B5CEA6}"/>
+    <hyperlink ref="F250" r:id="rId182" xr:uid="{D94ACD25-749A-4CB1-8052-0A0AFE93780A}"/>
+    <hyperlink ref="F251" r:id="rId183" xr:uid="{2E00A680-64E9-407D-8E13-2F110618DF34}"/>
+    <hyperlink ref="F252" r:id="rId184" xr:uid="{5282E600-5DE5-40F4-ABBA-8BDF551E64C5}"/>
+    <hyperlink ref="F253" r:id="rId185" xr:uid="{1C04F383-D1C0-4924-BCA4-7D68BF4F2C8A}"/>
+    <hyperlink ref="F254" r:id="rId186" xr:uid="{DF7BF135-FF63-4E18-A7A5-FC4B58690512}"/>
+    <hyperlink ref="F255" r:id="rId187" xr:uid="{1DB2A338-6A2C-43A2-8EFC-188CA7D96DF3}"/>
+    <hyperlink ref="F256" r:id="rId188" xr:uid="{65DFDF8E-E514-4B91-8BEF-7DD72C911D4F}"/>
+    <hyperlink ref="F257" r:id="rId189" xr:uid="{A9D504BA-AD23-48E7-A473-E3FE0EC434F4}"/>
+    <hyperlink ref="F258" r:id="rId190" xr:uid="{7D5E334E-6CFD-4B49-94F8-1E5E7816CEF4}"/>
+    <hyperlink ref="F259" r:id="rId191" xr:uid="{81D56905-B982-4CBF-B952-F71944EA142A}"/>
+    <hyperlink ref="F260" r:id="rId192" xr:uid="{8B3CBB40-E4B6-4847-AFAA-F21B565F54DA}"/>
+    <hyperlink ref="F261" r:id="rId193" xr:uid="{8C47402A-5BE2-4D1B-8AB7-5CF16C4B84EB}"/>
+    <hyperlink ref="F262" r:id="rId194" xr:uid="{0088EA25-8E77-4132-90D8-5D0A3074B20F}"/>
+    <hyperlink ref="F263" r:id="rId195" xr:uid="{A61E9347-7C4E-41E4-A7E9-AA05313C5FC7}"/>
+    <hyperlink ref="F264" r:id="rId196" xr:uid="{5F690E95-E438-45DC-B54F-5EF7E7545176}"/>
+    <hyperlink ref="F265" r:id="rId197" xr:uid="{2DC5C43A-961D-4C73-8C18-D84597852CF5}"/>
+    <hyperlink ref="F266" r:id="rId198" xr:uid="{FF7475C9-D2DA-4B9A-A867-501EFEA3C7B8}"/>
+    <hyperlink ref="F267" r:id="rId199" xr:uid="{36B83677-8EFD-4D8E-A00C-384F0A81678E}"/>
+    <hyperlink ref="F268" r:id="rId200" xr:uid="{AEE3D4D7-55E2-4FED-8E53-EA1201972E3C}"/>
+    <hyperlink ref="F321" r:id="rId201" xr:uid="{2E12A770-0B07-45A2-A461-625EEEC258DA}"/>
+    <hyperlink ref="F322" r:id="rId202" xr:uid="{367DA9FF-A0AA-410B-9DDE-593EA3D8446D}"/>
+    <hyperlink ref="F323" r:id="rId203" xr:uid="{9D67B6DC-99F9-45B6-9FE8-29B117DACDAB}"/>
+    <hyperlink ref="F324" r:id="rId204" xr:uid="{33BF3254-CA00-424D-8085-B0F44D80A808}"/>
+    <hyperlink ref="F325" r:id="rId205" xr:uid="{1BFDA55B-31DA-4088-A658-B915DD35B6E6}"/>
+    <hyperlink ref="F326" r:id="rId206" xr:uid="{D43D5340-E0C4-4744-A915-1F7F8F01940D}"/>
+    <hyperlink ref="F327" r:id="rId207" xr:uid="{AD4A3C3C-86BA-4866-8A2F-8C5232523A8D}"/>
+    <hyperlink ref="F328" r:id="rId208" xr:uid="{56DA2C6E-BC11-4E19-AE22-03E1C6D1E3F4}"/>
+    <hyperlink ref="F329" r:id="rId209" xr:uid="{897E3D83-DF91-4892-908F-73E3E08048FA}"/>
+    <hyperlink ref="F330" r:id="rId210" xr:uid="{64F3AD1A-993F-4769-B58A-1F725E5CDA0E}"/>
+    <hyperlink ref="F331" r:id="rId211" xr:uid="{DC9B3EB8-B1EB-48AC-B2D7-969A79B67512}"/>
+    <hyperlink ref="F332" r:id="rId212" xr:uid="{EF941B07-8F2C-4D8F-8C29-2A61427B6A73}"/>
+    <hyperlink ref="F333" r:id="rId213" xr:uid="{7FB80983-CA7D-4D95-901D-55429CD5A532}"/>
+    <hyperlink ref="F334" r:id="rId214" xr:uid="{6F9BA08E-A1DC-4A8E-8685-CE73D5845A2E}"/>
+    <hyperlink ref="F335" r:id="rId215" xr:uid="{FA55C00A-55DC-4F39-8A25-8656B7712852}"/>
+    <hyperlink ref="F336" r:id="rId216" xr:uid="{BE915386-1311-4240-8C12-5E033381C471}"/>
+    <hyperlink ref="F337" r:id="rId217" xr:uid="{A73C957B-2CC3-40DB-B94C-95974BB536B9}"/>
+    <hyperlink ref="F2" r:id="rId218" xr:uid="{D08AC91E-AA68-4F5C-83D1-BF5CA9574C21}"/>
+    <hyperlink ref="F3" r:id="rId219" xr:uid="{8EE149F6-2BD7-4D7B-8B24-77C1921F16A6}"/>
+    <hyperlink ref="F4" r:id="rId220" xr:uid="{06B8D5C2-8CCC-451F-9D0A-BC171EAC23F0}"/>
+    <hyperlink ref="F5" r:id="rId221" xr:uid="{D3742A08-24F7-438D-AA95-3B49E077EC2B}"/>
+    <hyperlink ref="F6" r:id="rId222" xr:uid="{BC571E5B-0BBC-44EB-84B1-7296FDBFD736}"/>
+    <hyperlink ref="F7" r:id="rId223" xr:uid="{C1384BC2-F2CA-41B3-8E2F-E4D5E485EBB4}"/>
+    <hyperlink ref="F8" r:id="rId224" xr:uid="{F13E6B0C-7CE0-4FD7-968C-2A36F8EB79C0}"/>
+    <hyperlink ref="F9" r:id="rId225" xr:uid="{B6C9F997-41ED-45EA-9786-17CBB301C4D8}"/>
+    <hyperlink ref="F10" r:id="rId226" xr:uid="{44D2EA56-2589-4F71-9EF7-257F864C51C8}"/>
+    <hyperlink ref="F11" r:id="rId227" xr:uid="{0A5434E5-2BB9-4B7E-B4C1-DA770400FFD4}"/>
+    <hyperlink ref="F12" r:id="rId228" xr:uid="{9053E71A-3393-46B6-BB19-8AB0B408203B}"/>
+    <hyperlink ref="F13" r:id="rId229" xr:uid="{5193139C-4500-4AEC-B9DB-FBEAE155683F}"/>
+    <hyperlink ref="F14" r:id="rId230" xr:uid="{A92F1138-3EF8-4C51-9EEC-BECE875A0B46}"/>
+    <hyperlink ref="F15" r:id="rId231" xr:uid="{C69557EF-B5CF-4A99-9421-6F7367756A2C}"/>
+    <hyperlink ref="F16" r:id="rId232" xr:uid="{71FF94BA-8393-4155-A684-0406202CF1D1}"/>
+    <hyperlink ref="F17" r:id="rId233" xr:uid="{6E3F7141-7A8A-4BFB-8C31-4696C5C628C7}"/>
+    <hyperlink ref="F18" r:id="rId234" xr:uid="{A3C21D40-7CF2-49DA-ACD1-D4D58D24ABC8}"/>
+    <hyperlink ref="F19" r:id="rId235" xr:uid="{A086619D-FCB1-4146-990F-079DB299F966}"/>
+    <hyperlink ref="F20" r:id="rId236" xr:uid="{58A1AFBC-493C-4BC1-9736-B70C90CE1562}"/>
+    <hyperlink ref="F21" r:id="rId237" xr:uid="{A2DAC5DC-2F55-47C6-B477-7C17F6E97839}"/>
+    <hyperlink ref="F22" r:id="rId238" xr:uid="{43EE1564-AAA3-4030-9FE4-6EB7510B30B5}"/>
+    <hyperlink ref="F23" r:id="rId239" xr:uid="{39E9DE08-14BE-4DE8-8BB8-ADCBA260120A}"/>
+    <hyperlink ref="F24" r:id="rId240" xr:uid="{93760355-53D3-4FC7-ADEC-78B74704C174}"/>
+    <hyperlink ref="F25" r:id="rId241" xr:uid="{42C4C1A9-6CF5-43E4-A0D0-BC8E69A054DC}"/>
+    <hyperlink ref="F26" r:id="rId242" xr:uid="{65E8F6EF-5A69-4422-AF97-20580D2037D2}"/>
+    <hyperlink ref="F27" r:id="rId243" xr:uid="{3BDD5CB2-2B57-4B3B-BC2C-4F9FB6C0F36D}"/>
+    <hyperlink ref="F28" r:id="rId244" xr:uid="{846C2CF0-ED2A-46F6-9231-EBA2DA925AC4}"/>
+    <hyperlink ref="F29" r:id="rId245" xr:uid="{C63C3C44-D329-45BC-84EA-8B318526A279}"/>
+    <hyperlink ref="F30" r:id="rId246" xr:uid="{E670855D-7A51-4ED3-8B8B-D0A3DB95EB95}"/>
+    <hyperlink ref="F31" r:id="rId247" xr:uid="{834A8702-B421-42BD-979A-D834EAE63EC7}"/>
+    <hyperlink ref="F32" r:id="rId248" xr:uid="{D1120622-92E0-4C32-97FC-56593D261A5A}"/>
+    <hyperlink ref="F33" r:id="rId249" xr:uid="{FCAB1519-0EC7-4C77-AD92-A7B6B13AEEC6}"/>
+    <hyperlink ref="F34" r:id="rId250" xr:uid="{A8924D60-55AE-495A-98D2-8403A19EC5AD}"/>
+    <hyperlink ref="F35" r:id="rId251" xr:uid="{67C6888A-D982-426D-9F32-EFE71305107C}"/>
+    <hyperlink ref="F36" r:id="rId252" xr:uid="{799378B2-E343-4120-8B1E-DC0BF74061A8}"/>
+    <hyperlink ref="F37" r:id="rId253" xr:uid="{4D27D309-58AA-4DBB-A69A-741CD7DC35EC}"/>
+    <hyperlink ref="F38" r:id="rId254" xr:uid="{677374A0-3A01-4689-9730-A12AAC3D394D}"/>
+    <hyperlink ref="F39" r:id="rId255" xr:uid="{FAC3B59A-1B7E-4D16-B22B-F9C4B26E3EC3}"/>
+    <hyperlink ref="F40" r:id="rId256" xr:uid="{6CD6B06A-34E5-458A-BA7B-F1FB0B02EC62}"/>
+    <hyperlink ref="F41" r:id="rId257" xr:uid="{AEEBDE04-6D41-4EAB-B1C2-19A47FDD9D78}"/>
+    <hyperlink ref="F42" r:id="rId258" xr:uid="{96854AB4-BFA8-4CA8-939B-2E09DB48BB9D}"/>
+    <hyperlink ref="F43" r:id="rId259" xr:uid="{2B7EEF55-F9D2-4910-857D-13FFCF693B0F}"/>
+    <hyperlink ref="F44" r:id="rId260" xr:uid="{763CC920-53A6-47D3-950E-A04B02733FDB}"/>
+    <hyperlink ref="F45" r:id="rId261" xr:uid="{AE12CFC5-0393-421C-8D70-DB45ABFBFCA5}"/>
+    <hyperlink ref="F46" r:id="rId262" xr:uid="{724CCB2D-2234-420D-9D44-FE75730F20AB}"/>
+    <hyperlink ref="F47" r:id="rId263" xr:uid="{0A3F5EF8-331C-48F4-80B9-E4F808740FE2}"/>
+    <hyperlink ref="F48" r:id="rId264" xr:uid="{EE027446-E7B8-4BDB-81FA-F36A3D9BB507}"/>
+    <hyperlink ref="F49" r:id="rId265" xr:uid="{60093486-FBA1-4977-B3C1-29D43241DF25}"/>
+    <hyperlink ref="F50" r:id="rId266" xr:uid="{5B083843-DF0D-4DA2-B639-633788A4B194}"/>
+    <hyperlink ref="F51" r:id="rId267" xr:uid="{05CF2809-7D41-4EA2-B099-E387FF5D59B1}"/>
+    <hyperlink ref="F52" r:id="rId268" xr:uid="{911E8DE0-2E6D-4EC1-8F8A-49899C87F87E}"/>
+    <hyperlink ref="F53" r:id="rId269" xr:uid="{50571FC8-A00C-4836-B4FE-2F750FE9A53D}"/>
+    <hyperlink ref="F54" r:id="rId270" xr:uid="{BA582508-C41B-4344-9383-E0F2F28507BC}"/>
+    <hyperlink ref="F55" r:id="rId271" xr:uid="{681AC8BF-33C4-45EE-8608-459E9E02649D}"/>
+    <hyperlink ref="F56" r:id="rId272" xr:uid="{A99B3135-4B2F-447C-AB42-399833C4165F}"/>
+    <hyperlink ref="F57" r:id="rId273" xr:uid="{39A34D51-5B53-4499-8230-6FEB3C573E51}"/>
+    <hyperlink ref="F58" r:id="rId274" xr:uid="{E4D789DC-0F1D-4193-A1AE-B5F430444482}"/>
+    <hyperlink ref="F59" r:id="rId275" xr:uid="{4DACCB98-E77D-4535-8599-F09B4D9FBDDC}"/>
+    <hyperlink ref="F60" r:id="rId276" xr:uid="{4A5B0CB3-05AD-4837-91B5-303FA31D8F9B}"/>
+    <hyperlink ref="F61" r:id="rId277" xr:uid="{68DC13E9-4FB7-484D-934B-353840C3A2A4}"/>
+    <hyperlink ref="F62" r:id="rId278" xr:uid="{E79DAAEF-5500-46C0-BD77-94F84D20FA5D}"/>
+    <hyperlink ref="F63" r:id="rId279" xr:uid="{C46B0EDE-781C-4F47-AFC6-E06F77F15CE1}"/>
+    <hyperlink ref="F64" r:id="rId280" xr:uid="{E5ED138A-A0BF-4D67-AAB8-529F18DB4DFC}"/>
+    <hyperlink ref="F65" r:id="rId281" xr:uid="{DF9EC1F2-954A-43CE-9B83-2CF0ED3B3DBF}"/>
+    <hyperlink ref="F66" r:id="rId282" xr:uid="{CFB74C3F-7214-4AE7-A347-3BCEAAEA66BC}"/>
+    <hyperlink ref="F67" r:id="rId283" xr:uid="{7C2F2339-A77D-4671-848C-E67FD5748883}"/>
+    <hyperlink ref="F68" r:id="rId284" xr:uid="{BADD3EFC-9213-4BF2-A3DA-D24D91B8C68E}"/>
+    <hyperlink ref="F69" r:id="rId285" xr:uid="{DE887B60-9216-43D3-8467-A0D89C6672F5}"/>
+    <hyperlink ref="F70" r:id="rId286" xr:uid="{51ED9530-3E2A-4655-9713-720C1734E394}"/>
+    <hyperlink ref="F71" r:id="rId287" xr:uid="{9066F7CD-777D-4608-B847-63F5CD4BE8D7}"/>
+    <hyperlink ref="F72" r:id="rId288" xr:uid="{174BD2A1-9D7C-4B6E-8BDB-83BF89B1CA51}"/>
+    <hyperlink ref="F73" r:id="rId289" xr:uid="{E54A152D-CBB2-4D5E-B550-BBBAC6DB5036}"/>
+    <hyperlink ref="F74" r:id="rId290" xr:uid="{67007BA5-C86D-449C-8231-14E4DAA56A2B}"/>
+    <hyperlink ref="F75" r:id="rId291" xr:uid="{1C6EAA42-1808-4039-B753-9E9EA4704888}"/>
+    <hyperlink ref="F76" r:id="rId292" xr:uid="{0D41BD61-584D-407C-8DF8-6522DDACE435}"/>
+    <hyperlink ref="F77" r:id="rId293" xr:uid="{417C72A6-7A0E-4D21-ABFF-70AC60C3E995}"/>
+    <hyperlink ref="F78" r:id="rId294" xr:uid="{76A4474D-FFA4-4018-97EE-19C89C2452E9}"/>
+    <hyperlink ref="F79" r:id="rId295" xr:uid="{A230C6B3-DB91-483B-9AC7-B69ED7E3F419}"/>
+    <hyperlink ref="F80" r:id="rId296" xr:uid="{DCC42248-54A8-4406-8F15-0749E4DEED8B}"/>
+    <hyperlink ref="F81" r:id="rId297" xr:uid="{93344D47-522B-47C8-B9AF-E478FF087611}"/>
+    <hyperlink ref="F82" r:id="rId298" xr:uid="{0E8DFFAD-A136-41FF-85C6-0CCF0BA08E3D}"/>
+    <hyperlink ref="F83" r:id="rId299" xr:uid="{E4B5D767-1153-4404-987D-27CB99DB60CD}"/>
+    <hyperlink ref="F84" r:id="rId300" xr:uid="{B6EEE53A-E02E-4F19-B925-92A3970111F6}"/>
+    <hyperlink ref="F85" r:id="rId301" xr:uid="{58BBD42F-B675-496F-8FB0-5A2CC7DFC735}"/>
+    <hyperlink ref="F86" r:id="rId302" xr:uid="{1F3564F2-DF77-405A-8CA7-54FE5A87A3A6}"/>
+    <hyperlink ref="F87" r:id="rId303" xr:uid="{75AF9393-7D3C-4642-9CC2-24C12DD4572C}"/>
+    <hyperlink ref="F88" r:id="rId304" xr:uid="{83B57D80-6178-4071-9B1F-FBA131D90274}"/>
+    <hyperlink ref="F89" r:id="rId305" xr:uid="{F11F766A-1E52-4A74-8239-27F30044E11D}"/>
+    <hyperlink ref="F90" r:id="rId306" xr:uid="{318F8F77-8409-4A91-942F-1D11A50BD1DC}"/>
+    <hyperlink ref="F91" r:id="rId307" xr:uid="{BE5B1612-CA26-40D9-BEC1-611CF067C05D}"/>
+    <hyperlink ref="F92" r:id="rId308" xr:uid="{8EEE0EEC-92C7-4352-B6DC-C94DE0ECAE10}"/>
+    <hyperlink ref="F93" r:id="rId309" xr:uid="{740ECDD5-404B-4CDC-A08D-6316A3B7D802}"/>
+    <hyperlink ref="F94" r:id="rId310" xr:uid="{4F4AB154-37FB-42B1-BB01-85D5FAD0CAAE}"/>
+    <hyperlink ref="F95" r:id="rId311" xr:uid="{95795C52-92E9-4D0A-8E3D-20B4E1C80AB0}"/>
+    <hyperlink ref="F96" r:id="rId312" xr:uid="{256924FB-B556-46D9-A34D-45F1F13D1260}"/>
+    <hyperlink ref="F97" r:id="rId313" xr:uid="{5FF7B8E5-DCEC-4E3C-9339-CDA1D83434BB}"/>
+    <hyperlink ref="F98" r:id="rId314" xr:uid="{6D868149-20B8-48F1-806B-0FAB30A48E4F}"/>
+    <hyperlink ref="F99" r:id="rId315" xr:uid="{3CD62805-F022-4C7A-9E84-05BE8E00542D}"/>
+    <hyperlink ref="F100" r:id="rId316" xr:uid="{FE2C2E4D-8666-4448-8526-9B1A98D0B405}"/>
+    <hyperlink ref="F101" r:id="rId317" xr:uid="{BCD271E6-BF9D-4212-B338-E58EF1D634F9}"/>
+    <hyperlink ref="F102" r:id="rId318" xr:uid="{62F6E8F5-2DE6-4505-8062-4DC2F7531E01}"/>
+    <hyperlink ref="F103" r:id="rId319" xr:uid="{57DE0F5A-7E5C-45E1-8940-518DE0CDF9D2}"/>
+    <hyperlink ref="F104" r:id="rId320" xr:uid="{06C180A0-2DAF-4508-A14D-C4723FF51BD9}"/>
+    <hyperlink ref="F105" r:id="rId321" xr:uid="{9AEF236C-5016-42C1-BF3F-C526759F4D03}"/>
+    <hyperlink ref="F106" r:id="rId322" xr:uid="{FF387627-9BE5-48FD-936C-7277CB54071D}"/>
+    <hyperlink ref="F107" r:id="rId323" xr:uid="{24592328-5B8A-42E6-AA9F-E442AD4E8A6B}"/>
+    <hyperlink ref="F108" r:id="rId324" xr:uid="{EEBB93C7-4E80-47EF-8213-CCF1E1D4EFCB}"/>
+    <hyperlink ref="F109" r:id="rId325" xr:uid="{414262C2-63D9-486A-BF90-C996B5BE2A10}"/>
+    <hyperlink ref="F110" r:id="rId326" xr:uid="{75083ABB-C9DB-41B5-8175-F0A10A0E1247}"/>
+    <hyperlink ref="F111" r:id="rId327" xr:uid="{F8338081-8413-464A-9866-39ECE511C5B6}"/>
+    <hyperlink ref="F112" r:id="rId328" xr:uid="{3B0EFFA9-0C00-43ED-BBE0-6976A9D3A81F}"/>
+    <hyperlink ref="F113" r:id="rId329" xr:uid="{CFEA4852-668B-4596-99D5-C98561C0F25D}"/>
+    <hyperlink ref="F114" r:id="rId330" xr:uid="{49C8F1BB-158C-4277-95C9-DEFA6E127CD5}"/>
+    <hyperlink ref="F115" r:id="rId331" xr:uid="{7BF2129D-1299-4427-B3BC-A23ABA2F0917}"/>
+    <hyperlink ref="F116" r:id="rId332" xr:uid="{3A29036D-17DD-4BE6-BC19-8F0E33EB9AC7}"/>
+    <hyperlink ref="F117" r:id="rId333" xr:uid="{E26F1D2F-F9ED-4626-99F0-9E09AF92E13A}"/>
+    <hyperlink ref="F118" r:id="rId334" xr:uid="{3E0C8FEF-8948-4E69-899D-765AA6F38863}"/>
+    <hyperlink ref="F119" r:id="rId335" xr:uid="{EC80C8F5-18C5-4F10-BA8C-63126A8703B2}"/>
+    <hyperlink ref="F120" r:id="rId336" xr:uid="{C0EA6A34-393A-49BF-B0A7-D9A4F4070887}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId250"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId337"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia1-my.sharepoint.com/personal/icdide_ehwadia1_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B19CE665-2725-459D-BD7E-C8A3BB50D3FD}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C970EC9B-0BE1-4211-868F-0BAB64AA825B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -47,10 +47,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>File name</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>https://ehwadia1-my.sharepoint.com/:b:/g/personal/icdide_ehwadia1_onmicrosoft_com/IQDQcDKfOpdbToBg3hFZdMqyAeYCp1pZ2Sxe8aWYdGdV5-s</t>
   </si>
   <si>
@@ -3182,6 +3178,10 @@
   </si>
   <si>
     <t>HILTI</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Customer</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -4193,7 +4193,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>1047</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
@@ -4213,4976 +4213,4976 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>754</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>755</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>757</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>758</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="C13" s="3"/>
       <c r="E13" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="C14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="C15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="C16" s="3"/>
       <c r="E16" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="C17" s="3"/>
       <c r="E17" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="C18" s="3"/>
       <c r="E18" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="C19" s="3"/>
       <c r="E19" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="C20" s="3"/>
       <c r="E20" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="C21" s="3"/>
       <c r="E21" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="C22" s="3"/>
       <c r="E22" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="C23" s="3"/>
       <c r="E23" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C24" s="3"/>
       <c r="E24" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="C25" s="3"/>
       <c r="E25" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="C26" s="3"/>
       <c r="E26" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="C27" s="3"/>
       <c r="E27" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="C28" s="3"/>
       <c r="E28" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="C29" s="3"/>
       <c r="E29" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="C30" s="3"/>
       <c r="E30" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C31" s="3"/>
       <c r="E31" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="C32" s="3"/>
       <c r="E32" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="C33" s="3"/>
       <c r="E33" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="C34" s="3"/>
       <c r="E34" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="C35" s="3"/>
       <c r="E35" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="C36" s="3"/>
       <c r="E36" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>759</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>760</v>
       </c>
       <c r="C37" s="3"/>
       <c r="E37" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>763</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>766</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>767</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>768</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>769</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>772</v>
-      </c>
       <c r="E41" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>773</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>775</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>776</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>778</v>
-      </c>
       <c r="E43" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>781</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>784</v>
-      </c>
       <c r="E45" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>787</v>
-      </c>
       <c r="E46" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>790</v>
-      </c>
       <c r="E47" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>791</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>792</v>
       </c>
       <c r="C48" s="3"/>
       <c r="E48" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C49" s="3"/>
       <c r="E49" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>794</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>795</v>
       </c>
       <c r="C50" s="3"/>
       <c r="E50" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>796</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>797</v>
       </c>
       <c r="C51" s="3"/>
       <c r="E51" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>798</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>799</v>
       </c>
       <c r="C52" s="3"/>
       <c r="E52" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>800</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>801</v>
       </c>
       <c r="C53" s="3"/>
       <c r="E53" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>802</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>803</v>
       </c>
       <c r="C54" s="3"/>
       <c r="E54" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>804</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>805</v>
       </c>
       <c r="C55" s="3"/>
       <c r="E55" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>806</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>807</v>
       </c>
       <c r="C56" s="3"/>
       <c r="E56" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C57" s="3"/>
       <c r="E57" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>809</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>810</v>
       </c>
       <c r="C58" s="3"/>
       <c r="E58" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>811</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>812</v>
       </c>
       <c r="C59" s="3"/>
       <c r="E59" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>813</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>814</v>
       </c>
       <c r="C60" s="3"/>
       <c r="E60" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C61" s="3"/>
       <c r="E61" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>816</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>817</v>
       </c>
       <c r="C62" s="3"/>
       <c r="E62" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>818</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>819</v>
       </c>
       <c r="C63" s="3"/>
       <c r="E63" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C64" s="3"/>
       <c r="E64" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>821</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>822</v>
       </c>
       <c r="C65" s="3"/>
       <c r="E65" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C66" s="3"/>
       <c r="E66" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>824</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>825</v>
       </c>
       <c r="C67" s="3"/>
       <c r="E67" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>826</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>827</v>
       </c>
       <c r="C68" s="3"/>
       <c r="E68" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>828</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>829</v>
       </c>
       <c r="C69" s="3"/>
       <c r="E69" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>830</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>831</v>
       </c>
       <c r="C70" s="3"/>
       <c r="E70" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>832</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>833</v>
       </c>
       <c r="C71" s="3"/>
       <c r="E71" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>834</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>835</v>
       </c>
       <c r="C72" s="3"/>
       <c r="E72" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>836</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>837</v>
       </c>
       <c r="C73" s="3"/>
       <c r="E73" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>838</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>839</v>
       </c>
       <c r="C74" s="3"/>
       <c r="E74" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>840</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>841</v>
       </c>
       <c r="C75" s="3"/>
       <c r="E75" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>842</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>843</v>
       </c>
       <c r="C76" s="3"/>
       <c r="E76" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>844</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>845</v>
       </c>
       <c r="C77" s="3"/>
       <c r="E77" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>847</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>848</v>
-      </c>
       <c r="E78" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>850</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>851</v>
-      </c>
       <c r="E79" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>854</v>
-      </c>
       <c r="E80" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>857</v>
-      </c>
       <c r="E81" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>859</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>860</v>
-      </c>
       <c r="E82" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>861</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>862</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>863</v>
-      </c>
       <c r="E83" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>864</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>865</v>
       </c>
-      <c r="C84" s="3" t="s">
-        <v>866</v>
-      </c>
       <c r="E84" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>867</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="C85" s="3" t="s">
-        <v>869</v>
-      </c>
       <c r="E85" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>870</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>871</v>
       </c>
-      <c r="C86" s="3" t="s">
-        <v>872</v>
-      </c>
       <c r="E86" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>873</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="C87" s="3" t="s">
         <v>874</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>875</v>
-      </c>
       <c r="E87" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>876</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>877</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>878</v>
-      </c>
       <c r="E88" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>879</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>881</v>
-      </c>
       <c r="E89" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>882</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>883</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>884</v>
-      </c>
       <c r="E90" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>885</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="C91" s="3" t="s">
         <v>886</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>887</v>
-      </c>
       <c r="E91" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>888</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>847</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>889</v>
-      </c>
       <c r="E92" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>890</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="C93" s="3" t="s">
         <v>891</v>
       </c>
-      <c r="C93" s="3" t="s">
-        <v>892</v>
-      </c>
       <c r="E93" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>893</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>894</v>
       </c>
-      <c r="C94" s="3" t="s">
-        <v>895</v>
-      </c>
       <c r="E94" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>896</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="C95" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="C95" s="3" t="s">
-        <v>898</v>
-      </c>
       <c r="E95" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>899</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="C96" s="3" t="s">
         <v>900</v>
       </c>
-      <c r="C96" s="3" t="s">
-        <v>901</v>
-      </c>
       <c r="E96" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>902</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>903</v>
       </c>
-      <c r="C97" s="3" t="s">
-        <v>904</v>
-      </c>
       <c r="E97" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>905</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="C98" s="3" t="s">
         <v>906</v>
       </c>
-      <c r="C98" s="3" t="s">
-        <v>907</v>
-      </c>
       <c r="E98" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>908</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="C99" s="3" t="s">
         <v>909</v>
       </c>
-      <c r="C99" s="3" t="s">
-        <v>910</v>
-      </c>
       <c r="E99" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>911</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="C100" s="3" t="s">
         <v>912</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>913</v>
-      </c>
       <c r="E100" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>914</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="C101" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="C101" s="3" t="s">
-        <v>916</v>
-      </c>
       <c r="E101" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>917</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="C102" s="3" t="s">
         <v>918</v>
       </c>
-      <c r="C102" s="3" t="s">
-        <v>919</v>
-      </c>
       <c r="E102" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>920</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="C103" s="3" t="s">
         <v>921</v>
       </c>
-      <c r="C103" s="3" t="s">
-        <v>922</v>
-      </c>
       <c r="E103" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="B104" s="3" t="s">
         <v>923</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="C104" s="3" t="s">
         <v>924</v>
       </c>
-      <c r="C104" s="3" t="s">
-        <v>925</v>
-      </c>
       <c r="E104" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="B105" s="3" t="s">
         <v>926</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="C105" s="3" t="s">
         <v>927</v>
       </c>
-      <c r="C105" s="3" t="s">
-        <v>928</v>
-      </c>
       <c r="E105" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>929</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="C106" s="3" t="s">
         <v>930</v>
       </c>
-      <c r="C106" s="3" t="s">
-        <v>931</v>
-      </c>
       <c r="E106" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="B107" s="3" t="s">
         <v>932</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="C107" s="3" t="s">
         <v>933</v>
       </c>
-      <c r="C107" s="3" t="s">
-        <v>934</v>
-      </c>
       <c r="E107" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>935</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="C108" s="3" t="s">
         <v>936</v>
       </c>
-      <c r="C108" s="3" t="s">
-        <v>937</v>
-      </c>
       <c r="E108" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="B109" s="3" t="s">
         <v>938</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="C109" s="3" t="s">
         <v>939</v>
       </c>
-      <c r="C109" s="3" t="s">
-        <v>940</v>
-      </c>
       <c r="E109" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>941</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="C110" s="3" t="s">
         <v>942</v>
       </c>
-      <c r="C110" s="3" t="s">
-        <v>943</v>
-      </c>
       <c r="E110" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="B111" s="3" t="s">
         <v>944</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="C111" s="3" t="s">
         <v>945</v>
       </c>
-      <c r="C111" s="3" t="s">
-        <v>946</v>
-      </c>
       <c r="E111" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>947</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>948</v>
       </c>
       <c r="C112" s="3"/>
       <c r="E112" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="B113" s="3" t="s">
         <v>949</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>950</v>
       </c>
       <c r="C113" s="3"/>
       <c r="E113" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="E114" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="E115" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="E116" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="E117" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
       <c r="E118" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>956</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>957</v>
       </c>
       <c r="C119" s="3"/>
       <c r="E119" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>958</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>959</v>
       </c>
       <c r="C120" s="3"/>
       <c r="E120" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B121" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="C121" s="5"/>
       <c r="E121" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B122" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="C122" s="5"/>
       <c r="E122" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B123" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="C123" s="5"/>
       <c r="E123" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B124" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="C124" s="5"/>
       <c r="E124" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B125" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="C125" s="5"/>
       <c r="E125" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B126" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="C126" s="5"/>
       <c r="E126" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B127" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="C127" s="5"/>
       <c r="E127" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B128" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="C128" s="5"/>
       <c r="E128" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B129" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="C129" s="5"/>
       <c r="E129" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B130" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="C130" s="5"/>
       <c r="E130" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B131" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="C131" s="5"/>
       <c r="E131" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B132" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="C132" s="5"/>
       <c r="E132" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B133" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="C133" s="5"/>
       <c r="E133" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B134" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="C134" s="5"/>
       <c r="E134" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B135" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="C135" s="5"/>
       <c r="E135" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B136" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="C136" s="5"/>
       <c r="E136" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B137" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="C137" s="5"/>
       <c r="E137" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B138" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="C138" s="5"/>
       <c r="E138" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B139" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="C139" s="5"/>
       <c r="E139" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B140" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="C140" s="5"/>
       <c r="E140" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B141" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="C141" s="5"/>
       <c r="E141" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B142" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="C142" s="5"/>
       <c r="E142" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B143" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="C143" s="5"/>
       <c r="E143" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B144" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="C144" s="5"/>
       <c r="E144" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B145" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>148</v>
       </c>
       <c r="C145" s="5"/>
       <c r="E145" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B146" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="C146" s="5"/>
       <c r="E146" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B147" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="C147" s="5"/>
       <c r="E147" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B148" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="C148" s="5"/>
       <c r="E148" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B149" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="C149" s="5"/>
       <c r="E149" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B150" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="C150" s="5"/>
       <c r="E150" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B151" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="C151" s="5"/>
       <c r="E151" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B152" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="C152" s="5"/>
       <c r="E152" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B153" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="C153" s="5"/>
       <c r="E153" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B154" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="C154" s="5"/>
       <c r="E154" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B155" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="C155" s="5"/>
       <c r="E155" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B156" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="C156" s="5"/>
       <c r="E156" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B157" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="C157" s="5"/>
       <c r="E157" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B158" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="C158" s="5"/>
       <c r="E158" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B159" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="C159" s="5"/>
       <c r="E159" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B160" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="C160" s="5"/>
       <c r="E160" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B161" s="3"/>
       <c r="C161" s="5"/>
       <c r="E161" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B162" s="3"/>
       <c r="C162" s="5"/>
       <c r="E162" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B163" s="3"/>
       <c r="C163" s="5"/>
       <c r="E163" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B164" s="3"/>
       <c r="C164" s="5"/>
       <c r="E164" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B165" s="3"/>
       <c r="C165" s="5"/>
       <c r="E165" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B166" s="3"/>
       <c r="C166" s="5"/>
       <c r="E166" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C167" s="5"/>
       <c r="E167" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C168" s="5"/>
       <c r="E168" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C169" s="5"/>
       <c r="E169" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C170" s="5"/>
       <c r="E170" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C171" s="5"/>
       <c r="E171" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C172" s="5"/>
       <c r="E172" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C173" s="5"/>
       <c r="E173" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C174" s="5"/>
       <c r="E174" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C175" s="5"/>
       <c r="E175" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C176" s="5"/>
       <c r="E176" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C177" s="5"/>
       <c r="E177" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C178" s="5"/>
       <c r="E178" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C179" s="5"/>
       <c r="E179" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B180" s="3"/>
       <c r="C180" s="5"/>
       <c r="E180" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B181" s="3"/>
       <c r="C181" s="5"/>
       <c r="E181" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C182" s="5"/>
       <c r="E182" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C183" s="5"/>
       <c r="E183" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C184" s="5"/>
       <c r="E184" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C185" s="5"/>
       <c r="E185" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C186" s="5"/>
       <c r="E186" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C187" s="5"/>
       <c r="E187" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C188" s="5"/>
       <c r="E188" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C189" s="5"/>
       <c r="E189" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B190" s="3"/>
       <c r="C190" s="5"/>
       <c r="E190" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C191" s="5"/>
       <c r="E191" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C192" s="5"/>
       <c r="E192" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C193" s="5"/>
       <c r="E193" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C194" s="5"/>
       <c r="E194" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C195" s="5"/>
       <c r="E195" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C196" s="5"/>
       <c r="E196" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C197" s="5"/>
       <c r="E197" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C198" s="5"/>
       <c r="E198" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C199" s="5"/>
       <c r="E199" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C200" s="5"/>
       <c r="E200" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C201" s="5"/>
       <c r="E201" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C202" s="5"/>
       <c r="E202" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C203" s="5"/>
       <c r="E203" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C204" s="5"/>
       <c r="E204" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B206" s="3"/>
       <c r="E206" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B207" s="3"/>
       <c r="E207" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="E267" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="B267" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="E267" s="3" t="s">
-        <v>495</v>
-      </c>
       <c r="F267" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F270" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F272" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F273" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F274" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F275" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F276" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F277" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F278" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F279" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F280" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F281" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F282" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F284" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F286" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F288" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F289" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F290" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F291" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F292" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F293" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F294" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F295" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F296" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F297" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F298" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F299" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F300" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F301" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F302" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F303" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F304" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F305" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F306" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F307" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F308" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F309" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F310" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F311" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F312" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F313" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F314" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F315" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F316" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F317" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F318" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F319" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F320" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="B321" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="B321" s="3" t="s">
-        <v>702</v>
-      </c>
       <c r="E321" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F321" s="4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="B322" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="B322" s="3" t="s">
-        <v>704</v>
-      </c>
       <c r="E322" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F322" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="B323" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="B323" s="3" t="s">
-        <v>706</v>
-      </c>
       <c r="E323" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F323" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="B324" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="B324" s="3" t="s">
-        <v>708</v>
-      </c>
       <c r="E324" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F324" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="B325" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="B325" s="3" t="s">
-        <v>710</v>
-      </c>
       <c r="E325" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F325" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="B326" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="B326" s="3" t="s">
-        <v>712</v>
-      </c>
       <c r="E326" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F326" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="B327" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="B327" s="3" t="s">
-        <v>714</v>
-      </c>
       <c r="E327" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F327" s="4" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="B328" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="B328" s="3" t="s">
-        <v>716</v>
-      </c>
       <c r="E328" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F328" s="4" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="B329" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="B329" s="3" t="s">
-        <v>718</v>
-      </c>
       <c r="E329" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F329" s="4" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="B330" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="B330" s="3" t="s">
-        <v>720</v>
-      </c>
       <c r="E330" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F330" s="4" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="B331" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="B331" s="3" t="s">
-        <v>722</v>
-      </c>
       <c r="E331" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F331" s="4" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="B332" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="B332" s="3" t="s">
-        <v>724</v>
-      </c>
       <c r="E332" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F332" s="4" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="B333" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="B333" s="3" t="s">
-        <v>726</v>
-      </c>
       <c r="E333" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="B334" s="3" t="s">
         <v>727</v>
       </c>
-      <c r="B334" s="3" t="s">
-        <v>728</v>
-      </c>
       <c r="E334" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F334" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B335" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="B335" s="3" t="s">
-        <v>730</v>
-      </c>
       <c r="E335" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F335" s="4" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="B336" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="B336" s="3" t="s">
-        <v>732</v>
-      </c>
       <c r="E336" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F336" s="4" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="B337" s="3" t="s">
         <v>733</v>
       </c>
-      <c r="B337" s="3" t="s">
-        <v>734</v>
-      </c>
       <c r="E337" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F337" s="4" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
   </sheetData>
